--- a/VerveStacks_NGA_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_NGA_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NGA_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9D6A16C9-695A-462E-8B08-D0FFC544A8B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{396EF01A-5D55-4676-94A9-B6AFF19FB766}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -993,72 +993,192 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_036</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_034</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_033</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_035</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_032</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_004</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 4</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_003</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 3</t>
   </si>
   <si>
-    <t>distr_solelc_spv_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_036</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_030</t>
   </si>
   <si>
@@ -1071,96 +1191,12 @@
     <t>connecting solar to buses in cluster 11</t>
   </si>
   <si>
-    <t>distr_solelc_spv_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_033</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_032</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_006</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 6</t>
   </si>
   <si>
-    <t>distr_solelc_spv_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_001</t>
   </si>
   <si>
@@ -1179,126 +1215,105 @@
     <t>connecting solar to buses in cluster 14</t>
   </si>
   <si>
-    <t>distr_solelc_spv_034</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_035</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_NG18-330,e_w746582404-330,e_NG17-330</t>
+  </si>
+  <si>
+    <t>e_w564430566-330,e_w564429999-330</t>
+  </si>
+  <si>
+    <t>e_w1328602766-330,e_NG6-330</t>
+  </si>
+  <si>
+    <t>e_w746582404-330,e_w563732518-330,e_NG20-330,e_NG21-330,e_w334825256-330,e_w564429999-330</t>
+  </si>
+  <si>
+    <t>e_w564430566-330</t>
+  </si>
+  <si>
+    <t>e_NG2-330,e_NG1-330,e_w395182311-330,e_w563723584-330</t>
+  </si>
+  <si>
+    <t>e_w1328602766-330,e_w695826179-330,e_w540463591-330,e_w481286430-330</t>
+  </si>
+  <si>
+    <t>e_w565847437-330,e_w565081403-330,e_w266617120-330</t>
+  </si>
+  <si>
+    <t>e_w565081403-330</t>
+  </si>
+  <si>
+    <t>e_w266617120-330,e_w395182311-330,e_w266712817-330,e_w563723584-330</t>
+  </si>
+  <si>
+    <t>e_w267122040-330</t>
+  </si>
+  <si>
+    <t>e_w565866986-330,e_NG11-330,e_w574152484-330</t>
+  </si>
+  <si>
+    <t>e_w565081403-330,e_w267122040-330</t>
+  </si>
+  <si>
+    <t>e_w565081403-330,e_w266617120-330,e_w266712817-330,e_w267122040-330</t>
+  </si>
+  <si>
+    <t>e_NG6-330,e_NG7-330,e_NG3-330,e_w565486405-330</t>
+  </si>
+  <si>
+    <t>e_w1226249784-330,e_NG1-330,e_NG2-330,e_w395182311-330</t>
+  </si>
+  <si>
+    <t>e_w266712817-330,e_w563723584-330,e_w267122040-330,e_w655273140-330</t>
+  </si>
+  <si>
+    <t>e_w563723584-330,e_w655273140-330</t>
+  </si>
+  <si>
+    <t>e_w564410486-330,e_w695826179-330,e_w39469643-330,e_w1226249784-330</t>
+  </si>
+  <si>
+    <t>e_w565486405-330,e_NG3-330,e_NG4-330,e_NG5-330,e_w565847437-330</t>
+  </si>
+  <si>
+    <t>e_w563715917-330,e_NG5-330,e_w565081403-330</t>
+  </si>
+  <si>
+    <t>e_w556550171-330,e_w39469643-330,e_w266617120-330</t>
+  </si>
+  <si>
+    <t>e_w695826179-330</t>
+  </si>
+  <si>
+    <t>e_w695826179-330,e_w564410486-330,e_NG3-330,e_w556550171-330,e_w39469643-330</t>
+  </si>
+  <si>
+    <t>e_w546666333-330,e_NG17-330,e_w575706869-330</t>
+  </si>
+  <si>
+    <t>e_w215459565-330,e_w563715917-330,e_w548724506-330,e_w565081403-330</t>
+  </si>
+  <si>
     <t>e_w108020974-330,e_w836122563-330,e_w559542338-330,e_NG9-330,e_w669957212-330,e_w1324578567-330,e_w565866986-330</t>
   </si>
   <si>
     <t>e_NG8-330,e_w564445207-330,e_w1328602766-330</t>
   </si>
   <si>
-    <t>e_w215459565-330,e_w563715917-330,e_w548724506-330,e_w565081403-330</t>
-  </si>
-  <si>
-    <t>e_w1328602766-330,e_w695826179-330,e_w540463591-330,e_w481286430-330</t>
-  </si>
-  <si>
-    <t>e_w565847437-330,e_w565081403-330,e_w266617120-330</t>
-  </si>
-  <si>
-    <t>e_w565081403-330</t>
-  </si>
-  <si>
-    <t>e_w266617120-330,e_w395182311-330,e_w266712817-330,e_w563723584-330</t>
-  </si>
-  <si>
-    <t>e_w267122040-330</t>
-  </si>
-  <si>
-    <t>e_w564430566-330</t>
-  </si>
-  <si>
-    <t>e_NG2-330,e_NG1-330,e_w395182311-330,e_w563723584-330</t>
-  </si>
-  <si>
     <t>e_w564410486-330,e_w1226249784-330</t>
   </si>
   <si>
     <t>e_NG13-330,e_NG15-330,e_w1057700475-330,e_w215459565-330,e_w671893504-330,e_w548724506-330,e_NG12-330</t>
   </si>
   <si>
-    <t>e_w564410486-330,e_w695826179-330,e_w39469643-330,e_w1226249784-330</t>
-  </si>
-  <si>
-    <t>e_w565486405-330,e_NG3-330,e_NG4-330,e_NG5-330,e_w565847437-330</t>
-  </si>
-  <si>
-    <t>e_w563715917-330,e_NG5-330,e_w565081403-330</t>
-  </si>
-  <si>
-    <t>e_w556550171-330,e_w39469643-330,e_w266617120-330</t>
-  </si>
-  <si>
-    <t>e_w565866986-330,e_NG11-330,e_w574152484-330</t>
-  </si>
-  <si>
-    <t>e_w565081403-330,e_w267122040-330</t>
-  </si>
-  <si>
-    <t>e_w565081403-330,e_w266617120-330,e_w266712817-330,e_w267122040-330</t>
-  </si>
-  <si>
-    <t>e_w695826179-330,e_w564410486-330,e_NG3-330,e_w556550171-330,e_w39469643-330</t>
-  </si>
-  <si>
-    <t>e_w546666333-330,e_NG17-330,e_w575706869-330</t>
-  </si>
-  <si>
-    <t>e_w1328602766-330,e_NG6-330</t>
-  </si>
-  <si>
-    <t>e_w746582404-330,e_w563732518-330,e_NG20-330,e_NG21-330,e_w334825256-330,e_w564429999-330</t>
-  </si>
-  <si>
     <t>e_w546666333-330,e_w565866986-330,e_NG18-330</t>
   </si>
   <si>
-    <t>e_NG18-330,e_w746582404-330,e_NG17-330</t>
-  </si>
-  <si>
-    <t>e_w564430566-330,e_w564429999-330</t>
-  </si>
-  <si>
     <t>e_w564445207-330,e_w477596994-330,e_w565866986-330,e_NG11-330,e_w574152484-330,e_w215459565-330</t>
   </si>
   <si>
@@ -1308,19 +1323,22 @@
     <t>e_NG12-330,e_w565081403-330,e_w564429999-330</t>
   </si>
   <si>
-    <t>e_NG6-330,e_NG7-330,e_NG3-330,e_w565486405-330</t>
-  </si>
-  <si>
-    <t>e_w1226249784-330,e_NG1-330,e_NG2-330,e_w395182311-330</t>
-  </si>
-  <si>
-    <t>e_w266712817-330,e_w563723584-330,e_w267122040-330,e_w655273140-330</t>
-  </si>
-  <si>
-    <t>e_w563723584-330,e_w655273140-330</t>
-  </si>
-  <si>
-    <t>e_w695826179-330</t>
+    <t>distr_wonelc_won_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
   </si>
   <si>
     <t>distr_wonelc_won_002</t>
@@ -1329,6 +1347,60 @@
     <t>connecting wind onshore to buses in cluster 2</t>
   </si>
   <si>
+    <t>distr_wonelc_won_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_013</t>
   </si>
   <si>
@@ -1353,6 +1425,42 @@
     <t>connecting wind onshore to buses in cluster 16</t>
   </si>
   <si>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_011</t>
   </si>
   <si>
@@ -1377,117 +1485,72 @@
     <t>connecting wind onshore to buses in cluster 17</t>
   </si>
   <si>
-    <t>distr_wonelc_won_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
+    <t>elc_won_007</t>
+  </si>
+  <si>
+    <t>e_w1328602766-330,e_w540463591-330,e_NG6-330,e_w477596994-330,e_NG7-330</t>
+  </si>
+  <si>
+    <t>elc_won_012</t>
+  </si>
+  <si>
+    <t>e_w564410486-330,e_w695826179-330</t>
+  </si>
+  <si>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>e_w695826179-330,e_w1328602766-330,e_w540463591-330</t>
   </si>
   <si>
     <t>elc_won_002</t>
   </si>
   <si>
+    <t>elc_won_018</t>
+  </si>
+  <si>
+    <t>e_w395182311-330,e_w563723584-330</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>e_w548724506-330,e_w563715917-330,e_w565081403-330</t>
+  </si>
+  <si>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>e_w564410486-330</t>
+  </si>
+  <si>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>e_NG3-330,e_w556550171-330,e_w39469643-330,e_w266617120-330</t>
+  </si>
+  <si>
+    <t>elc_won_019</t>
+  </si>
+  <si>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>e_w108020974-330</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>elc_won_021</t>
+  </si>
+  <si>
+    <t>e_w266617120-330,e_w266712817-330</t>
+  </si>
+  <si>
     <t>elc_won_013</t>
   </si>
   <si>
@@ -1509,6 +1572,33 @@
     <t>elc_won_016</t>
   </si>
   <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>e_NG3-330,e_w556550171-330,e_w39469643-330</t>
+  </si>
+  <si>
+    <t>elc_won_022</t>
+  </si>
+  <si>
+    <t>elc_won_027</t>
+  </si>
+  <si>
+    <t>e_w266617120-330,e_w266712817-330,e_w267122040-330</t>
+  </si>
+  <si>
+    <t>elc_won_026</t>
+  </si>
+  <si>
+    <t>e_w266712817-330,e_w267122040-330,e_w655273140-330</t>
+  </si>
+  <si>
     <t>elc_won_011</t>
   </si>
   <si>
@@ -1533,94 +1623,34 @@
     <t>e_w266712817-330,e_w563723584-330,e_w655273140-330</t>
   </si>
   <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>e_w108020974-330</t>
-  </si>
-  <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>e_w564410486-330</t>
-  </si>
-  <si>
-    <t>elc_won_021</t>
-  </si>
-  <si>
-    <t>e_w266617120-330,e_w266712817-330</t>
-  </si>
-  <si>
-    <t>elc_won_018</t>
-  </si>
-  <si>
-    <t>e_w395182311-330,e_w563723584-330</t>
-  </si>
-  <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>elc_won_010</t>
-  </si>
-  <si>
-    <t>e_NG3-330,e_w556550171-330,e_w39469643-330,e_w266617120-330</t>
-  </si>
-  <si>
-    <t>elc_won_019</t>
-  </si>
-  <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
-    <t>e_w1328602766-330,e_w540463591-330,e_NG6-330,e_w477596994-330,e_NG7-330</t>
-  </si>
-  <si>
-    <t>elc_won_012</t>
-  </si>
-  <si>
-    <t>e_w564410486-330,e_w695826179-330</t>
-  </si>
-  <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>elc_won_003</t>
-  </si>
-  <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>e_NG3-330,e_w556550171-330,e_w39469643-330</t>
-  </si>
-  <si>
-    <t>elc_won_022</t>
-  </si>
-  <si>
-    <t>elc_won_027</t>
-  </si>
-  <si>
-    <t>e_w266617120-330,e_w266712817-330,e_w267122040-330</t>
-  </si>
-  <si>
-    <t>elc_won_026</t>
-  </si>
-  <si>
-    <t>e_w266712817-330,e_w267122040-330,e_w655273140-330</t>
-  </si>
-  <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
-    <t>e_w695826179-330,e_w1328602766-330,e_w540463591-330</t>
-  </si>
-  <si>
-    <t>elc_won_005</t>
-  </si>
-  <si>
-    <t>e_w548724506-330,e_w563715917-330,e_w565081403-330</t>
+    <t>distr_wofelc_wof_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
   </si>
   <si>
     <t>distr_wofelc_wof_008</t>
@@ -1629,36 +1659,18 @@
     <t>connecting wind offshore to buses in cluster 8</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_009</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 9</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_005</t>
   </si>
   <si>
@@ -1671,67 +1683,55 @@
     <t>connecting wind offshore to buses in cluster 6</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
+    <t>elc_wof_004</t>
+  </si>
+  <si>
+    <t>e_NG18-330,e_w559542338-330</t>
+  </si>
+  <si>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>e_w746582404-330,e_w564430566-330</t>
+  </si>
+  <si>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
+    <t>e_NG18-330</t>
+  </si>
+  <si>
+    <t>elc_wof_001</t>
+  </si>
+  <si>
+    <t>e_NG9-330,e_w1324578567-330,e_w565866986-330</t>
+  </si>
+  <si>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>e_w706082453-330,e_w108020974-330,e_w559542338-330,e_w565866986-330,e_w546666333-330</t>
   </si>
   <si>
     <t>elc_wof_008</t>
   </si>
   <si>
-    <t>elc_wof_002</t>
-  </si>
-  <si>
-    <t>e_w706082453-330,e_w108020974-330,e_w559542338-330,e_w565866986-330,e_w546666333-330</t>
-  </si>
-  <si>
-    <t>elc_wof_001</t>
-  </si>
-  <si>
-    <t>e_NG9-330,e_w1324578567-330,e_w565866986-330</t>
-  </si>
-  <si>
-    <t>elc_wof_004</t>
-  </si>
-  <si>
-    <t>e_NG18-330,e_w559542338-330</t>
-  </si>
-  <si>
-    <t>elc_wof_007</t>
-  </si>
-  <si>
-    <t>e_w746582404-330,e_w564430566-330</t>
-  </si>
-  <si>
     <t>elc_wof_009</t>
   </si>
   <si>
     <t>e_w746582404-330</t>
   </si>
   <si>
+    <t>elc_wof_010</t>
+  </si>
+  <si>
+    <t>e_NG18-330,e_w746582404-330</t>
+  </si>
+  <si>
     <t>elc_wof_005</t>
   </si>
   <si>
-    <t>e_NG18-330,e_w746582404-330</t>
-  </si>
-  <si>
     <t>elc_wof_006</t>
-  </si>
-  <si>
-    <t>elc_wof_010</t>
-  </si>
-  <si>
-    <t>elc_wof_003</t>
-  </si>
-  <si>
-    <t>e_NG18-330</t>
   </si>
   <si>
     <t>e_won_001</t>
@@ -6755,7 +6755,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34A67737-7045-4C3E-BF77-E56715CCCBD6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EB6375C-E804-4453-90D9-50E27C892516}">
   <dimension ref="B9:BD46"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6993,16 +6993,16 @@
         <v>288</v>
       </c>
       <c r="Y11" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="Z11" t="s">
         <v>364</v>
       </c>
       <c r="AA11">
-        <v>0.99802162515875081</v>
+        <v>0.99884992726149324</v>
       </c>
       <c r="AB11">
-        <v>36.270205422902137</v>
+        <v>21.084666872623977</v>
       </c>
       <c r="AD11" t="s">
         <v>287</v>
@@ -7032,13 +7032,13 @@
         <v>452</v>
       </c>
       <c r="AN11" t="s">
-        <v>371</v>
+        <v>453</v>
       </c>
       <c r="AO11">
-        <v>0.99537626424805781</v>
+        <v>0.99740664776461363</v>
       </c>
       <c r="AP11">
-        <v>84.768488785605911</v>
+        <v>47.544790982083583</v>
       </c>
       <c r="AR11" t="s">
         <v>287</v>
@@ -7068,13 +7068,13 @@
         <v>518</v>
       </c>
       <c r="BB11" t="s">
-        <v>372</v>
+        <v>519</v>
       </c>
       <c r="BC11">
-        <v>0.99337755486839363</v>
+        <v>0.99246115999793105</v>
       </c>
       <c r="BD11">
-        <v>121.41149407945062</v>
+        <v>138.21206670459694</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7139,16 +7139,16 @@
         <v>292</v>
       </c>
       <c r="Y12" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="Z12" t="s">
         <v>365</v>
       </c>
       <c r="AA12">
-        <v>0.99631349511992195</v>
+        <v>0.99882431199806432</v>
       </c>
       <c r="AB12">
-        <v>67.585922801431252</v>
+        <v>21.554280035486567</v>
       </c>
       <c r="AD12" t="s">
         <v>287</v>
@@ -7175,16 +7175,16 @@
         <v>400</v>
       </c>
       <c r="AM12" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AN12" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AO12">
-        <v>0.99207403494667001</v>
+        <v>0.9913636988912532</v>
       </c>
       <c r="AP12">
-        <v>145.30935931104892</v>
+        <v>158.33218699369189</v>
       </c>
       <c r="AR12" t="s">
         <v>287</v>
@@ -7211,16 +7211,16 @@
         <v>500</v>
       </c>
       <c r="BA12" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="BB12" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="BC12">
-        <v>0.9962053430710629</v>
+        <v>0.99268778174342398</v>
       </c>
       <c r="BD12">
-        <v>69.568710363846861</v>
+        <v>134.05733470389279</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -7285,16 +7285,16 @@
         <v>294</v>
       </c>
       <c r="Y13" t="s">
-        <v>272</v>
+        <v>251</v>
       </c>
       <c r="Z13" t="s">
         <v>366</v>
       </c>
       <c r="AA13">
-        <v>0.99655017109874156</v>
+        <v>0.99723470592138874</v>
       </c>
       <c r="AB13">
-        <v>63.246863189739024</v>
+        <v>50.697058107873339</v>
       </c>
       <c r="AD13" t="s">
         <v>287</v>
@@ -7321,16 +7321,16 @@
         <v>402</v>
       </c>
       <c r="AM13" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AN13" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AO13">
-        <v>0.99637613831578808</v>
+        <v>0.99429686126958916</v>
       </c>
       <c r="AP13">
-        <v>66.437464210551497</v>
+        <v>104.55754339086491</v>
       </c>
       <c r="AR13" t="s">
         <v>287</v>
@@ -7357,16 +7357,16 @@
         <v>502</v>
       </c>
       <c r="BA13" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="BB13" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="BC13">
-        <v>0.99794494286432878</v>
+        <v>0.99174031680019514</v>
       </c>
       <c r="BD13">
-        <v>37.67604748730637</v>
+        <v>151.42752532975524</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -7431,16 +7431,16 @@
         <v>296</v>
       </c>
       <c r="Y14" t="s">
-        <v>285</v>
+        <v>257</v>
       </c>
       <c r="Z14" t="s">
         <v>367</v>
       </c>
       <c r="AA14">
-        <v>0.996629171401053</v>
+        <v>0.99750455285561002</v>
       </c>
       <c r="AB14">
-        <v>61.798524314027716</v>
+        <v>45.749864313816033</v>
       </c>
       <c r="AD14" t="s">
         <v>287</v>
@@ -7467,16 +7467,16 @@
         <v>404</v>
       </c>
       <c r="AM14" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AN14" t="s">
-        <v>458</v>
+        <v>374</v>
       </c>
       <c r="AO14">
-        <v>0.99501745221162918</v>
+        <v>0.99537626424805781</v>
       </c>
       <c r="AP14">
-        <v>91.346709453464783</v>
+        <v>84.768488785605911</v>
       </c>
       <c r="AR14" t="s">
         <v>287</v>
@@ -7503,16 +7503,16 @@
         <v>504</v>
       </c>
       <c r="BA14" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="BB14" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="BC14">
-        <v>0.99246115999793105</v>
+        <v>0.99794494286432878</v>
       </c>
       <c r="BD14">
-        <v>138.21206670459694</v>
+        <v>37.67604748730637</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7577,16 +7577,16 @@
         <v>298</v>
       </c>
       <c r="Y15" t="s">
-        <v>275</v>
+        <v>256</v>
       </c>
       <c r="Z15" t="s">
         <v>368</v>
       </c>
       <c r="AA15">
-        <v>0.9940266623681554</v>
+        <v>0.99605704806429607</v>
       </c>
       <c r="AB15">
-        <v>109.51118991715018</v>
+        <v>72.28745215457208</v>
       </c>
       <c r="AD15" t="s">
         <v>287</v>
@@ -7616,13 +7616,13 @@
         <v>459</v>
       </c>
       <c r="AN15" t="s">
-        <v>396</v>
+        <v>460</v>
       </c>
       <c r="AO15">
-        <v>0.99698529931119073</v>
+        <v>0.98839759805196303</v>
       </c>
       <c r="AP15">
-        <v>55.269512628170503</v>
+        <v>212.71070238067816</v>
       </c>
       <c r="AR15" t="s">
         <v>287</v>
@@ -7649,16 +7649,16 @@
         <v>506</v>
       </c>
       <c r="BA15" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="BB15" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="BC15">
-        <v>0.99268778174342398</v>
+        <v>0.9962053430710629</v>
       </c>
       <c r="BD15">
-        <v>134.05733470389279</v>
+        <v>69.568710363846861</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -7723,16 +7723,16 @@
         <v>300</v>
       </c>
       <c r="Y16" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="Z16" t="s">
         <v>369</v>
       </c>
       <c r="AA16">
-        <v>0.99629635001073991</v>
+        <v>0.99167914755584141</v>
       </c>
       <c r="AB16">
-        <v>67.900249803101318</v>
+        <v>152.54896147624135</v>
       </c>
       <c r="AD16" t="s">
         <v>287</v>
@@ -7759,16 +7759,16 @@
         <v>408</v>
       </c>
       <c r="AM16" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AN16" t="s">
-        <v>461</v>
+        <v>374</v>
       </c>
       <c r="AO16">
-        <v>0.99178855761800622</v>
+        <v>0.99671794291781168</v>
       </c>
       <c r="AP16">
-        <v>150.54311033655213</v>
+        <v>60.171046506785672</v>
       </c>
       <c r="AR16" t="s">
         <v>287</v>
@@ -7795,16 +7795,16 @@
         <v>508</v>
       </c>
       <c r="BA16" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="BB16" t="s">
-        <v>528</v>
+        <v>368</v>
       </c>
       <c r="BC16">
-        <v>0.99755731205629283</v>
+        <v>0.99337755486839363</v>
       </c>
       <c r="BD16">
-        <v>44.782612301298634</v>
+        <v>121.41149407945062</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -7869,16 +7869,16 @@
         <v>302</v>
       </c>
       <c r="Y17" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="Z17" t="s">
         <v>370</v>
       </c>
       <c r="AA17">
-        <v>0.99383936956194807</v>
+        <v>0.996629171401053</v>
       </c>
       <c r="AB17">
-        <v>112.94489136428538</v>
+        <v>61.798524314027716</v>
       </c>
       <c r="AD17" t="s">
         <v>287</v>
@@ -7911,10 +7911,10 @@
         <v>463</v>
       </c>
       <c r="AO17">
-        <v>0.99296304108660982</v>
+        <v>0.99562035686170025</v>
       </c>
       <c r="AP17">
-        <v>129.01091341215286</v>
+        <v>80.293457535494625</v>
       </c>
       <c r="AR17" t="s">
         <v>287</v>
@@ -7947,10 +7947,10 @@
         <v>530</v>
       </c>
       <c r="BC17">
-        <v>0.9888409065104441</v>
+        <v>0.99755731205629283</v>
       </c>
       <c r="BD17">
-        <v>204.58338064185853</v>
+        <v>44.782612301298634</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8015,16 +8015,16 @@
         <v>304</v>
       </c>
       <c r="Y18" t="s">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="Z18" t="s">
         <v>371</v>
       </c>
       <c r="AA18">
-        <v>0.98416398409272543</v>
+        <v>0.9940266623681554</v>
       </c>
       <c r="AB18">
-        <v>290.32695830003399</v>
+        <v>109.51118991715018</v>
       </c>
       <c r="AD18" t="s">
         <v>287</v>
@@ -8057,10 +8057,10 @@
         <v>465</v>
       </c>
       <c r="AO18">
-        <v>0.99152317643653909</v>
+        <v>0.9933445384762607</v>
       </c>
       <c r="AP18">
-        <v>155.40843199678267</v>
+        <v>122.01679460188713</v>
       </c>
       <c r="AR18" t="s">
         <v>287</v>
@@ -8090,13 +8090,13 @@
         <v>531</v>
       </c>
       <c r="BB18" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="BC18">
-        <v>0.99132158137897763</v>
+        <v>0.99371472191320109</v>
       </c>
       <c r="BD18">
-        <v>159.10434138541075</v>
+        <v>115.23009825798009</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8161,16 +8161,16 @@
         <v>306</v>
       </c>
       <c r="Y19" t="s">
-        <v>256</v>
+        <v>270</v>
       </c>
       <c r="Z19" t="s">
         <v>372</v>
       </c>
       <c r="AA19">
-        <v>0.99605704806429607</v>
+        <v>0.99629635001073991</v>
       </c>
       <c r="AB19">
-        <v>72.28745215457208</v>
+        <v>67.900249803101318</v>
       </c>
       <c r="AD19" t="s">
         <v>287</v>
@@ -8203,10 +8203,10 @@
         <v>467</v>
       </c>
       <c r="AO19">
-        <v>0.99475386493829931</v>
+        <v>0.9938298282896767</v>
       </c>
       <c r="AP19">
-        <v>96.179142797845941</v>
+        <v>113.11981468926018</v>
       </c>
       <c r="AR19" t="s">
         <v>287</v>
@@ -8233,16 +8233,16 @@
         <v>514</v>
       </c>
       <c r="BA19" t="s">
+        <v>533</v>
+      </c>
+      <c r="BB19" t="s">
         <v>532</v>
       </c>
-      <c r="BB19" t="s">
-        <v>530</v>
-      </c>
       <c r="BC19">
-        <v>0.99371472191320109</v>
+        <v>0.9888409065104441</v>
       </c>
       <c r="BD19">
-        <v>115.23009825798009</v>
+        <v>204.58338064185853</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8307,16 +8307,16 @@
         <v>308</v>
       </c>
       <c r="Y20" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="Z20" t="s">
         <v>373</v>
       </c>
       <c r="AA20">
-        <v>0.99167914755584141</v>
+        <v>0.99383936956194807</v>
       </c>
       <c r="AB20">
-        <v>152.54896147624135</v>
+        <v>112.94489136428538</v>
       </c>
       <c r="AD20" t="s">
         <v>287</v>
@@ -8346,13 +8346,13 @@
         <v>468</v>
       </c>
       <c r="AN20" t="s">
-        <v>469</v>
+        <v>381</v>
       </c>
       <c r="AO20">
-        <v>0.99795762496221851</v>
+        <v>0.99008544123370779</v>
       </c>
       <c r="AP20">
-        <v>37.443542359327118</v>
+        <v>181.76691071535706</v>
       </c>
       <c r="AR20" t="s">
         <v>287</v>
@@ -8379,16 +8379,16 @@
         <v>516</v>
       </c>
       <c r="BA20" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="BB20" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="BC20">
-        <v>0.99174031680019514</v>
+        <v>0.99132158137897763</v>
       </c>
       <c r="BD20">
-        <v>151.42752532975524</v>
+        <v>159.10434138541075</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -8453,16 +8453,16 @@
         <v>310</v>
       </c>
       <c r="Y21" t="s">
-        <v>279</v>
+        <v>264</v>
       </c>
       <c r="Z21" t="s">
         <v>374</v>
       </c>
       <c r="AA21">
-        <v>0.99133276722560904</v>
+        <v>0.98416398409272543</v>
       </c>
       <c r="AB21">
-        <v>158.89926753050145</v>
+        <v>290.32695830003399</v>
       </c>
       <c r="AD21" t="s">
         <v>287</v>
@@ -8489,16 +8489,16 @@
         <v>418</v>
       </c>
       <c r="AM21" t="s">
+        <v>469</v>
+      </c>
+      <c r="AN21" t="s">
         <v>470</v>
       </c>
-      <c r="AN21" t="s">
-        <v>471</v>
-      </c>
       <c r="AO21">
-        <v>0.99582871194680656</v>
+        <v>0.99795762496221851</v>
       </c>
       <c r="AP21">
-        <v>76.473614308545862</v>
+        <v>37.443542359327118</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8563,16 +8563,16 @@
         <v>312</v>
       </c>
       <c r="Y22" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="Z22" t="s">
         <v>375</v>
       </c>
       <c r="AA22">
-        <v>0.99728758220200375</v>
+        <v>0.99832768028365393</v>
       </c>
       <c r="AB22">
-        <v>49.727659629930621</v>
+        <v>30.659194799678048</v>
       </c>
       <c r="AD22" t="s">
         <v>287</v>
@@ -8599,16 +8599,16 @@
         <v>420</v>
       </c>
       <c r="AM22" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="AN22" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="AO22">
-        <v>0.99555964959117016</v>
+        <v>0.99582871194680656</v>
       </c>
       <c r="AP22">
-        <v>81.406424161880452</v>
+        <v>76.473614308545862</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -8673,16 +8673,16 @@
         <v>314</v>
       </c>
       <c r="Y23" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="Z23" t="s">
         <v>376</v>
       </c>
       <c r="AA23">
-        <v>0.993124380119488</v>
+        <v>0.99057172008573791</v>
       </c>
       <c r="AB23">
-        <v>126.05303114271953</v>
+        <v>172.85179842813815</v>
       </c>
       <c r="AD23" t="s">
         <v>287</v>
@@ -8709,16 +8709,16 @@
         <v>422</v>
       </c>
       <c r="AM23" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="AN23" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="AO23">
-        <v>0.98839759805196303</v>
+        <v>0.99555964959117016</v>
       </c>
       <c r="AP23">
-        <v>212.71070238067816</v>
+        <v>81.406424161880452</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -8783,16 +8783,16 @@
         <v>316</v>
       </c>
       <c r="Y24" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="Z24" t="s">
         <v>377</v>
       </c>
       <c r="AA24">
-        <v>0.99769438809486533</v>
+        <v>0.99095032933880767</v>
       </c>
       <c r="AB24">
-        <v>42.269551594135834</v>
+        <v>165.91062878852651</v>
       </c>
       <c r="AD24" t="s">
         <v>287</v>
@@ -8819,16 +8819,16 @@
         <v>424</v>
       </c>
       <c r="AM24" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="AN24" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="AO24">
-        <v>0.9933445384762607</v>
+        <v>0.99207403494667001</v>
       </c>
       <c r="AP24">
-        <v>122.01679460188713</v>
+        <v>145.30935931104892</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -8893,16 +8893,16 @@
         <v>318</v>
       </c>
       <c r="Y25" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="Z25" t="s">
         <v>378</v>
       </c>
       <c r="AA25">
-        <v>0.99489048613238573</v>
+        <v>0.9963457067026108</v>
       </c>
       <c r="AB25">
-        <v>93.674420906261602</v>
+        <v>66.99537711880258</v>
       </c>
       <c r="AD25" t="s">
         <v>287</v>
@@ -8929,16 +8929,16 @@
         <v>426</v>
       </c>
       <c r="AM25" t="s">
+        <v>476</v>
+      </c>
+      <c r="AN25" t="s">
         <v>477</v>
       </c>
-      <c r="AN25" t="s">
-        <v>478</v>
-      </c>
       <c r="AO25">
-        <v>0.9938298282896767</v>
+        <v>0.99637613831578808</v>
       </c>
       <c r="AP25">
-        <v>113.11981468926018</v>
+        <v>66.437464210551497</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -9003,16 +9003,16 @@
         <v>320</v>
       </c>
       <c r="Y26" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="Z26" t="s">
         <v>379</v>
       </c>
       <c r="AA26">
-        <v>0.99642867204968677</v>
+        <v>0.99644641159652714</v>
       </c>
       <c r="AB26">
-        <v>65.474345755743457</v>
+        <v>65.149120730335611</v>
       </c>
       <c r="AD26" t="s">
         <v>287</v>
@@ -9039,16 +9039,16 @@
         <v>428</v>
       </c>
       <c r="AM26" t="s">
+        <v>478</v>
+      </c>
+      <c r="AN26" t="s">
         <v>479</v>
       </c>
-      <c r="AN26" t="s">
-        <v>396</v>
-      </c>
       <c r="AO26">
-        <v>0.99008544123370779</v>
+        <v>0.99501745221162918</v>
       </c>
       <c r="AP26">
-        <v>181.76691071535706</v>
+        <v>91.346709453464783</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -9113,16 +9113,16 @@
         <v>322</v>
       </c>
       <c r="Y27" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="Z27" t="s">
         <v>380</v>
       </c>
       <c r="AA27">
-        <v>0.99832768028365393</v>
+        <v>0.99436579068013853</v>
       </c>
       <c r="AB27">
-        <v>30.659194799678048</v>
+        <v>103.29383753079337</v>
       </c>
       <c r="AD27" t="s">
         <v>287</v>
@@ -9152,13 +9152,13 @@
         <v>480</v>
       </c>
       <c r="AN27" t="s">
-        <v>481</v>
+        <v>381</v>
       </c>
       <c r="AO27">
-        <v>0.99740664776461363</v>
+        <v>0.99698529931119073</v>
       </c>
       <c r="AP27">
-        <v>47.544790982083583</v>
+        <v>55.269512628170503</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -9223,16 +9223,16 @@
         <v>324</v>
       </c>
       <c r="Y28" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="Z28" t="s">
         <v>381</v>
       </c>
       <c r="AA28">
-        <v>0.99057172008573791</v>
+        <v>0.99262439568706373</v>
       </c>
       <c r="AB28">
-        <v>172.85179842813815</v>
+        <v>135.21941240383219</v>
       </c>
       <c r="AD28" t="s">
         <v>287</v>
@@ -9259,16 +9259,16 @@
         <v>432</v>
       </c>
       <c r="AM28" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="AN28" t="s">
-        <v>483</v>
+        <v>372</v>
       </c>
       <c r="AO28">
-        <v>0.9913636988912532</v>
+        <v>0.99354454384798807</v>
       </c>
       <c r="AP28">
-        <v>158.33218699369189</v>
+        <v>118.35002945355123</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9333,16 +9333,16 @@
         <v>326</v>
       </c>
       <c r="Y29" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="Z29" t="s">
         <v>382</v>
       </c>
       <c r="AA29">
-        <v>0.99095032933880767</v>
+        <v>0.993124380119488</v>
       </c>
       <c r="AB29">
-        <v>165.91062878852651</v>
+        <v>126.05303114271953</v>
       </c>
       <c r="AD29" t="s">
         <v>287</v>
@@ -9369,16 +9369,16 @@
         <v>434</v>
       </c>
       <c r="AM29" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="AN29" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="AO29">
-        <v>0.99354454384798807</v>
+        <v>0.99069345154297106</v>
       </c>
       <c r="AP29">
-        <v>118.35002945355123</v>
+        <v>170.62005504553079</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9443,16 +9443,16 @@
         <v>328</v>
       </c>
       <c r="Y30" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="Z30" t="s">
         <v>383</v>
       </c>
       <c r="AA30">
-        <v>0.99339354842512728</v>
+        <v>0.99769438809486533</v>
       </c>
       <c r="AB30">
-        <v>121.1182788726671</v>
+        <v>42.269551594135834</v>
       </c>
       <c r="AD30" t="s">
         <v>287</v>
@@ -9479,16 +9479,16 @@
         <v>436</v>
       </c>
       <c r="AM30" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="AN30" t="s">
-        <v>382</v>
+        <v>484</v>
       </c>
       <c r="AO30">
-        <v>0.99069345154297106</v>
+        <v>0.9964390810242717</v>
       </c>
       <c r="AP30">
-        <v>170.62005504553079</v>
+        <v>65.283514555019096</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -9553,16 +9553,16 @@
         <v>330</v>
       </c>
       <c r="Y31" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="Z31" t="s">
         <v>384</v>
       </c>
       <c r="AA31">
-        <v>0.99805028151894915</v>
+        <v>0.99489048613238573</v>
       </c>
       <c r="AB31">
-        <v>35.744838819266263</v>
+        <v>93.674420906261602</v>
       </c>
       <c r="AD31" t="s">
         <v>287</v>
@@ -9589,16 +9589,16 @@
         <v>438</v>
       </c>
       <c r="AM31" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AN31" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="AO31">
-        <v>0.99671794291781168</v>
+        <v>0.99592873360628342</v>
       </c>
       <c r="AP31">
-        <v>60.171046506785672</v>
+        <v>74.639883884803922</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -9663,16 +9663,16 @@
         <v>332</v>
       </c>
       <c r="Y32" t="s">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="Z32" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="AA32">
-        <v>0.98395338050941106</v>
+        <v>0.99642867204968677</v>
       </c>
       <c r="AB32">
-        <v>294.18802399413073</v>
+        <v>65.474345755743457</v>
       </c>
       <c r="AD32" t="s">
         <v>287</v>
@@ -9699,16 +9699,16 @@
         <v>440</v>
       </c>
       <c r="AM32" t="s">
+        <v>486</v>
+      </c>
+      <c r="AN32" t="s">
         <v>487</v>
       </c>
-      <c r="AN32" t="s">
-        <v>488</v>
-      </c>
       <c r="AO32">
-        <v>0.9964390810242717</v>
+        <v>0.99534990870245532</v>
       </c>
       <c r="AP32">
-        <v>65.283514555019096</v>
+        <v>85.251673788320105</v>
       </c>
     </row>
     <row r="33" spans="2:42">
@@ -9773,16 +9773,16 @@
         <v>334</v>
       </c>
       <c r="Y33" t="s">
-        <v>251</v>
+        <v>284</v>
       </c>
       <c r="Z33" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AA33">
-        <v>0.99723470592138874</v>
+        <v>0.99514004796050048</v>
       </c>
       <c r="AB33">
-        <v>50.697058107873339</v>
+        <v>89.099120724157018</v>
       </c>
       <c r="AD33" t="s">
         <v>287</v>
@@ -9809,16 +9809,16 @@
         <v>442</v>
       </c>
       <c r="AM33" t="s">
+        <v>488</v>
+      </c>
+      <c r="AN33" t="s">
         <v>489</v>
       </c>
-      <c r="AN33" t="s">
-        <v>394</v>
-      </c>
       <c r="AO33">
-        <v>0.99592873360628342</v>
+        <v>0.99283555585293171</v>
       </c>
       <c r="AP33">
-        <v>74.639883884803922</v>
+        <v>131.34814269625272</v>
       </c>
     </row>
     <row r="34" spans="2:42">
@@ -9883,16 +9883,16 @@
         <v>336</v>
       </c>
       <c r="Y34" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="Z34" t="s">
-        <v>386</v>
+        <v>374</v>
       </c>
       <c r="AA34">
-        <v>0.99750455285561002</v>
+        <v>0.99589467345586935</v>
       </c>
       <c r="AB34">
-        <v>45.749864313816033</v>
+        <v>75.264319975727958</v>
       </c>
       <c r="AD34" t="s">
         <v>287</v>
@@ -9925,10 +9925,10 @@
         <v>491</v>
       </c>
       <c r="AO34">
-        <v>0.99534990870245532</v>
+        <v>0.99178855761800622</v>
       </c>
       <c r="AP34">
-        <v>85.251673788320105</v>
+        <v>150.54311033655213</v>
       </c>
     </row>
     <row r="35" spans="2:42">
@@ -9993,16 +9993,16 @@
         <v>338</v>
       </c>
       <c r="Y35" t="s">
-        <v>255</v>
+        <v>281</v>
       </c>
       <c r="Z35" t="s">
         <v>387</v>
       </c>
       <c r="AA35">
-        <v>0.99744993905722468</v>
+        <v>0.99339354842512728</v>
       </c>
       <c r="AB35">
-        <v>46.751117284213812</v>
+        <v>121.1182788726671</v>
       </c>
       <c r="AD35" t="s">
         <v>287</v>
@@ -10035,10 +10035,10 @@
         <v>493</v>
       </c>
       <c r="AO35">
-        <v>0.99283555585293171</v>
+        <v>0.99296304108660982</v>
       </c>
       <c r="AP35">
-        <v>131.34814269625272</v>
+        <v>129.01091341215286</v>
       </c>
     </row>
     <row r="36" spans="2:42">
@@ -10103,16 +10103,16 @@
         <v>340</v>
       </c>
       <c r="Y36" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Z36" t="s">
         <v>388</v>
       </c>
       <c r="AA36">
-        <v>0.99884992726149324</v>
+        <v>0.99805028151894915</v>
       </c>
       <c r="AB36">
-        <v>21.084666872623977</v>
+        <v>35.744838819266263</v>
       </c>
       <c r="AD36" t="s">
         <v>287</v>
@@ -10145,10 +10145,10 @@
         <v>495</v>
       </c>
       <c r="AO36">
-        <v>0.99429686126958916</v>
+        <v>0.99152317643653909</v>
       </c>
       <c r="AP36">
-        <v>104.55754339086491</v>
+        <v>155.40843199678267</v>
       </c>
     </row>
     <row r="37" spans="2:42">
@@ -10213,16 +10213,16 @@
         <v>342</v>
       </c>
       <c r="Y37" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="Z37" t="s">
-        <v>389</v>
+        <v>376</v>
       </c>
       <c r="AA37">
-        <v>0.99882431199806432</v>
+        <v>0.98395338050941106</v>
       </c>
       <c r="AB37">
-        <v>21.554280035486567</v>
+        <v>294.18802399413073</v>
       </c>
       <c r="AD37" t="s">
         <v>287</v>
@@ -10255,10 +10255,10 @@
         <v>497</v>
       </c>
       <c r="AO37">
-        <v>0.99562035686170025</v>
+        <v>0.99475386493829931</v>
       </c>
       <c r="AP37">
-        <v>80.293457535494625</v>
+        <v>96.179142797845941</v>
       </c>
     </row>
     <row r="38" spans="2:42">
@@ -10323,16 +10323,16 @@
         <v>344</v>
       </c>
       <c r="Y38" t="s">
-        <v>250</v>
+        <v>272</v>
       </c>
       <c r="Z38" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AA38">
-        <v>0.99732710525923551</v>
+        <v>0.99655017109874156</v>
       </c>
       <c r="AB38">
-        <v>49.003070247349498</v>
+        <v>63.246863189739024</v>
       </c>
     </row>
     <row r="39" spans="2:42">
@@ -10397,16 +10397,16 @@
         <v>346</v>
       </c>
       <c r="Y39" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="Z39" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AA39">
-        <v>0.99601914721828588</v>
+        <v>0.99802162515875081</v>
       </c>
       <c r="AB39">
-        <v>72.982300998092228</v>
+        <v>36.270205422902137</v>
       </c>
     </row>
     <row r="40" spans="2:42">
@@ -10471,16 +10471,16 @@
         <v>348</v>
       </c>
       <c r="Y40" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="Z40" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AA40">
-        <v>0.99403967905190227</v>
+        <v>0.99631349511992195</v>
       </c>
       <c r="AB40">
-        <v>109.27255071512499</v>
+        <v>67.585922801431252</v>
       </c>
     </row>
     <row r="41" spans="2:42">
@@ -10545,16 +10545,16 @@
         <v>350</v>
       </c>
       <c r="Y41" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="Z41" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AA41">
-        <v>0.9963457067026108</v>
+        <v>0.99133276722560904</v>
       </c>
       <c r="AB41">
-        <v>66.99537711880258</v>
+        <v>158.89926753050145</v>
       </c>
     </row>
     <row r="42" spans="2:42">
@@ -10619,16 +10619,16 @@
         <v>352</v>
       </c>
       <c r="Y42" t="s">
-        <v>277</v>
+        <v>260</v>
       </c>
       <c r="Z42" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AA42">
-        <v>0.99644641159652714</v>
+        <v>0.99728758220200375</v>
       </c>
       <c r="AB42">
-        <v>65.149120730335611</v>
+        <v>49.727659629930621</v>
       </c>
     </row>
     <row r="43" spans="2:42">
@@ -10693,16 +10693,16 @@
         <v>354</v>
       </c>
       <c r="Y43" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="Z43" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AA43">
-        <v>0.99436579068013853</v>
+        <v>0.99744993905722468</v>
       </c>
       <c r="AB43">
-        <v>103.29383753079337</v>
+        <v>46.751117284213812</v>
       </c>
     </row>
     <row r="44" spans="2:42">
@@ -10767,16 +10767,16 @@
         <v>356</v>
       </c>
       <c r="Y44" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
       <c r="Z44" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AA44">
-        <v>0.99262439568706373</v>
+        <v>0.99732710525923551</v>
       </c>
       <c r="AB44">
-        <v>135.21941240383219</v>
+        <v>49.003070247349498</v>
       </c>
     </row>
     <row r="45" spans="2:42">
@@ -10841,16 +10841,16 @@
         <v>358</v>
       </c>
       <c r="Y45" t="s">
-        <v>284</v>
+        <v>262</v>
       </c>
       <c r="Z45" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AA45">
-        <v>0.99514004796050048</v>
+        <v>0.99601914721828588</v>
       </c>
       <c r="AB45">
-        <v>89.099120724157018</v>
+        <v>72.982300998092228</v>
       </c>
     </row>
     <row r="46" spans="2:42">
@@ -10915,16 +10915,16 @@
         <v>360</v>
       </c>
       <c r="Y46" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="Z46" t="s">
-        <v>371</v>
+        <v>397</v>
       </c>
       <c r="AA46">
-        <v>0.99589467345586935</v>
+        <v>0.99403967905190227</v>
       </c>
       <c r="AB46">
-        <v>75.264319975727958</v>
+        <v>109.27255071512499</v>
       </c>
     </row>
   </sheetData>
@@ -10933,7 +10933,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AD1168F-B731-4C82-9C45-628781E4B84E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBDD3EB3-3D7B-459D-BF0E-CCBCB6742328}">
   <dimension ref="B9:Z37"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -11045,7 +11045,7 @@
         <v>535</v>
       </c>
       <c r="K11" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="L11">
         <v>10.088237612202811</v>
@@ -11078,7 +11078,7 @@
         <v>589</v>
       </c>
       <c r="X11" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="Y11">
         <v>0.16350000000000001</v>
@@ -11113,7 +11113,7 @@
         <v>537</v>
       </c>
       <c r="K12" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="L12">
         <v>4.7527038630847755</v>
@@ -11146,7 +11146,7 @@
         <v>591</v>
       </c>
       <c r="X12" t="s">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="Y12">
         <v>13.40025</v>
@@ -11181,7 +11181,7 @@
         <v>539</v>
       </c>
       <c r="K13" t="s">
-        <v>486</v>
+        <v>461</v>
       </c>
       <c r="L13">
         <v>1.4400913107240583</v>
@@ -11214,7 +11214,7 @@
         <v>593</v>
       </c>
       <c r="X13" t="s">
-        <v>533</v>
+        <v>522</v>
       </c>
       <c r="Y13">
         <v>8.4097500000000007</v>
@@ -11249,7 +11249,7 @@
         <v>541</v>
       </c>
       <c r="K14" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="L14">
         <v>1.437273477445641</v>
@@ -11282,7 +11282,7 @@
         <v>595</v>
       </c>
       <c r="X14" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="Y14">
         <v>14.358750000000001</v>
@@ -11317,7 +11317,7 @@
         <v>543</v>
       </c>
       <c r="K15" t="s">
-        <v>496</v>
+        <v>462</v>
       </c>
       <c r="L15">
         <v>2.1922713563210485</v>
@@ -11350,7 +11350,7 @@
         <v>597</v>
       </c>
       <c r="X15" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="Y15">
         <v>12.78825</v>
@@ -11385,7 +11385,7 @@
         <v>545</v>
       </c>
       <c r="K16" t="s">
-        <v>494</v>
+        <v>456</v>
       </c>
       <c r="L16">
         <v>0.73811583011208182</v>
@@ -11418,7 +11418,7 @@
         <v>599</v>
       </c>
       <c r="X16" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="Y16">
         <v>24.802499999999998</v>
@@ -11453,7 +11453,7 @@
         <v>547</v>
       </c>
       <c r="K17" t="s">
-        <v>480</v>
+        <v>452</v>
       </c>
       <c r="L17">
         <v>5.5236145427785717</v>
@@ -11486,7 +11486,7 @@
         <v>601</v>
       </c>
       <c r="X17" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="Y17">
         <v>8.6609999999999996</v>
@@ -11521,7 +11521,7 @@
         <v>549</v>
       </c>
       <c r="K18" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="L18">
         <v>5.5488357050452785E-3</v>
@@ -11554,7 +11554,7 @@
         <v>603</v>
       </c>
       <c r="X18" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="Y18">
         <v>3.4147500000000002</v>
@@ -11589,7 +11589,7 @@
         <v>551</v>
       </c>
       <c r="K19" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="L19">
         <v>6.6811161360847313</v>
@@ -11622,7 +11622,7 @@
         <v>605</v>
       </c>
       <c r="X19" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="Y19">
         <v>1.7250000000000001E-2</v>
@@ -11657,7 +11657,7 @@
         <v>553</v>
       </c>
       <c r="K20" t="s">
-        <v>477</v>
+        <v>466</v>
       </c>
       <c r="L20">
         <v>18.094012332227912</v>
@@ -11690,7 +11690,7 @@
         <v>607</v>
       </c>
       <c r="X20" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="Y20">
         <v>6.8624999999999998</v>
@@ -11725,7 +11725,7 @@
         <v>555</v>
       </c>
       <c r="K21" t="s">
-        <v>460</v>
+        <v>490</v>
       </c>
       <c r="L21">
         <v>1.3529085560597105</v>
@@ -11760,7 +11760,7 @@
         <v>557</v>
       </c>
       <c r="K22" t="s">
-        <v>482</v>
+        <v>454</v>
       </c>
       <c r="L22">
         <v>3.7088360788644938</v>
@@ -11795,7 +11795,7 @@
         <v>559</v>
       </c>
       <c r="K23" t="s">
-        <v>453</v>
+        <v>474</v>
       </c>
       <c r="L23">
         <v>13.683903390107789</v>
@@ -11830,7 +11830,7 @@
         <v>561</v>
       </c>
       <c r="K24" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="L24">
         <v>5.4676081362262012</v>
@@ -11865,7 +11865,7 @@
         <v>563</v>
       </c>
       <c r="K25" t="s">
-        <v>476</v>
+        <v>464</v>
       </c>
       <c r="L25">
         <v>8.9064794695455216</v>
@@ -11900,7 +11900,7 @@
         <v>565</v>
       </c>
       <c r="K26" t="s">
-        <v>459</v>
+        <v>480</v>
       </c>
       <c r="L26">
         <v>14.189229081738485</v>
@@ -11935,7 +11935,7 @@
         <v>567</v>
       </c>
       <c r="K27" t="s">
-        <v>466</v>
+        <v>496</v>
       </c>
       <c r="L27">
         <v>10.717982842540293</v>
@@ -11970,7 +11970,7 @@
         <v>569</v>
       </c>
       <c r="K28" t="s">
-        <v>474</v>
+        <v>459</v>
       </c>
       <c r="L28">
         <v>9.6743476082482847</v>
@@ -12005,7 +12005,7 @@
         <v>571</v>
       </c>
       <c r="K29" t="s">
-        <v>479</v>
+        <v>468</v>
       </c>
       <c r="L29">
         <v>23.206762484053751</v>
@@ -12040,7 +12040,7 @@
         <v>573</v>
       </c>
       <c r="K30" t="s">
-        <v>464</v>
+        <v>494</v>
       </c>
       <c r="L30">
         <v>5.8372174437039801</v>
@@ -12110,7 +12110,7 @@
         <v>577</v>
       </c>
       <c r="K32" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="L32">
         <v>7.179650801796102</v>
@@ -12145,7 +12145,7 @@
         <v>579</v>
       </c>
       <c r="K33" t="s">
-        <v>462</v>
+        <v>492</v>
       </c>
       <c r="L33">
         <v>14.559476964149322</v>
@@ -12180,7 +12180,7 @@
         <v>581</v>
       </c>
       <c r="K34" t="s">
-        <v>457</v>
+        <v>478</v>
       </c>
       <c r="L34">
         <v>1.3536151515148049</v>
@@ -12215,7 +12215,7 @@
         <v>583</v>
       </c>
       <c r="K35" t="s">
-        <v>455</v>
+        <v>476</v>
       </c>
       <c r="L35">
         <v>4.820514286595051</v>
@@ -12250,7 +12250,7 @@
         <v>585</v>
       </c>
       <c r="K36" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="L36">
         <v>8.1474073379531564</v>
@@ -12285,7 +12285,7 @@
         <v>587</v>
       </c>
       <c r="K37" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="L37">
         <v>9.9689850956014183</v>
@@ -12300,7 +12300,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C2A6245-EF42-4E34-A532-A037DDAD3F24}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD246E14-4019-4DCA-9F4C-D2D337415B55}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_NGA_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_NGA_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NGA_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{396EF01A-5D55-4676-94A9-B6AFF19FB766}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E37C2900-EAF7-4A14-BCCB-69275C6F413B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -993,34 +993,76 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_009</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 9</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_012</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 12</t>
   </si>
   <si>
-    <t>distr_solelc_spv_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
+    <t>distr_solelc_spv_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_033</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_035</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
   </si>
   <si>
     <t>distr_solelc_spv_007</t>
@@ -1035,6 +1077,114 @@
     <t>connecting solar to buses in cluster 29</t>
   </si>
   <si>
+    <t>distr_solelc_spv_034</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_032</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_036</t>
   </si>
   <si>
@@ -1065,172 +1215,43 @@
     <t>connecting solar to buses in cluster 15</t>
   </si>
   <si>
-    <t>distr_solelc_spv_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_034</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_033</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_035</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_032</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w1328602766-330,e_NG6-330</t>
+  </si>
+  <si>
+    <t>e_w746582404-330,e_w563732518-330,e_NG20-330,e_NG21-330,e_w334825256-330,e_w564429999-330</t>
+  </si>
+  <si>
     <t>e_NG18-330,e_w746582404-330,e_NG17-330</t>
   </si>
   <si>
     <t>e_w564430566-330,e_w564429999-330</t>
   </si>
   <si>
-    <t>e_w1328602766-330,e_NG6-330</t>
-  </si>
-  <si>
-    <t>e_w746582404-330,e_w563732518-330,e_NG20-330,e_NG21-330,e_w334825256-330,e_w564429999-330</t>
+    <t>e_w564410486-330,e_w695826179-330,e_w39469643-330,e_w1226249784-330</t>
+  </si>
+  <si>
+    <t>e_w565486405-330,e_NG3-330,e_NG4-330,e_NG5-330,e_w565847437-330</t>
+  </si>
+  <si>
+    <t>e_w563715917-330,e_NG5-330,e_w565081403-330</t>
+  </si>
+  <si>
+    <t>e_w556550171-330,e_w39469643-330,e_w266617120-330</t>
+  </si>
+  <si>
+    <t>e_w695826179-330</t>
+  </si>
+  <si>
+    <t>e_w267122040-330</t>
+  </si>
+  <si>
+    <t>e_w546666333-330,e_w565866986-330,e_NG18-330</t>
   </si>
   <si>
     <t>e_w564430566-330</t>
@@ -1239,6 +1260,57 @@
     <t>e_NG2-330,e_NG1-330,e_w395182311-330,e_w563723584-330</t>
   </si>
   <si>
+    <t>e_NG6-330,e_NG7-330,e_NG3-330,e_w565486405-330</t>
+  </si>
+  <si>
+    <t>e_w1226249784-330,e_NG1-330,e_NG2-330,e_w395182311-330</t>
+  </si>
+  <si>
+    <t>e_w266712817-330,e_w563723584-330,e_w267122040-330,e_w655273140-330</t>
+  </si>
+  <si>
+    <t>e_w563723584-330,e_w655273140-330</t>
+  </si>
+  <si>
+    <t>e_w108020974-330,e_w836122563-330,e_w559542338-330,e_NG9-330,e_w669957212-330,e_w1324578567-330,e_w565866986-330</t>
+  </si>
+  <si>
+    <t>e_NG8-330,e_w564445207-330,e_w1328602766-330</t>
+  </si>
+  <si>
+    <t>e_w565866986-330,e_NG11-330,e_w574152484-330</t>
+  </si>
+  <si>
+    <t>e_w565081403-330,e_w267122040-330</t>
+  </si>
+  <si>
+    <t>e_w565081403-330,e_w266617120-330,e_w266712817-330,e_w267122040-330</t>
+  </si>
+  <si>
+    <t>e_w215459565-330,e_w563715917-330,e_w548724506-330,e_w565081403-330</t>
+  </si>
+  <si>
+    <t>e_w564410486-330,e_w1226249784-330</t>
+  </si>
+  <si>
+    <t>e_NG13-330,e_NG15-330,e_w1057700475-330,e_w215459565-330,e_w671893504-330,e_w548724506-330,e_NG12-330</t>
+  </si>
+  <si>
+    <t>e_w564445207-330,e_w477596994-330,e_w565866986-330,e_NG11-330,e_w574152484-330,e_w215459565-330</t>
+  </si>
+  <si>
+    <t>e_w564429999-330,e_NG12-330</t>
+  </si>
+  <si>
+    <t>e_NG12-330,e_w565081403-330,e_w564429999-330</t>
+  </si>
+  <si>
+    <t>e_w695826179-330,e_w564410486-330,e_NG3-330,e_w556550171-330,e_w39469643-330</t>
+  </si>
+  <si>
+    <t>e_w546666333-330,e_NG17-330,e_w575706869-330</t>
+  </si>
+  <si>
     <t>e_w1328602766-330,e_w695826179-330,e_w540463591-330,e_w481286430-330</t>
   </si>
   <si>
@@ -1251,78 +1323,6 @@
     <t>e_w266617120-330,e_w395182311-330,e_w266712817-330,e_w563723584-330</t>
   </si>
   <si>
-    <t>e_w267122040-330</t>
-  </si>
-  <si>
-    <t>e_w565866986-330,e_NG11-330,e_w574152484-330</t>
-  </si>
-  <si>
-    <t>e_w565081403-330,e_w267122040-330</t>
-  </si>
-  <si>
-    <t>e_w565081403-330,e_w266617120-330,e_w266712817-330,e_w267122040-330</t>
-  </si>
-  <si>
-    <t>e_NG6-330,e_NG7-330,e_NG3-330,e_w565486405-330</t>
-  </si>
-  <si>
-    <t>e_w1226249784-330,e_NG1-330,e_NG2-330,e_w395182311-330</t>
-  </si>
-  <si>
-    <t>e_w266712817-330,e_w563723584-330,e_w267122040-330,e_w655273140-330</t>
-  </si>
-  <si>
-    <t>e_w563723584-330,e_w655273140-330</t>
-  </si>
-  <si>
-    <t>e_w564410486-330,e_w695826179-330,e_w39469643-330,e_w1226249784-330</t>
-  </si>
-  <si>
-    <t>e_w565486405-330,e_NG3-330,e_NG4-330,e_NG5-330,e_w565847437-330</t>
-  </si>
-  <si>
-    <t>e_w563715917-330,e_NG5-330,e_w565081403-330</t>
-  </si>
-  <si>
-    <t>e_w556550171-330,e_w39469643-330,e_w266617120-330</t>
-  </si>
-  <si>
-    <t>e_w695826179-330</t>
-  </si>
-  <si>
-    <t>e_w695826179-330,e_w564410486-330,e_NG3-330,e_w556550171-330,e_w39469643-330</t>
-  </si>
-  <si>
-    <t>e_w546666333-330,e_NG17-330,e_w575706869-330</t>
-  </si>
-  <si>
-    <t>e_w215459565-330,e_w563715917-330,e_w548724506-330,e_w565081403-330</t>
-  </si>
-  <si>
-    <t>e_w108020974-330,e_w836122563-330,e_w559542338-330,e_NG9-330,e_w669957212-330,e_w1324578567-330,e_w565866986-330</t>
-  </si>
-  <si>
-    <t>e_NG8-330,e_w564445207-330,e_w1328602766-330</t>
-  </si>
-  <si>
-    <t>e_w564410486-330,e_w1226249784-330</t>
-  </si>
-  <si>
-    <t>e_NG13-330,e_NG15-330,e_w1057700475-330,e_w215459565-330,e_w671893504-330,e_w548724506-330,e_NG12-330</t>
-  </si>
-  <si>
-    <t>e_w546666333-330,e_w565866986-330,e_NG18-330</t>
-  </si>
-  <si>
-    <t>e_w564445207-330,e_w477596994-330,e_w565866986-330,e_NG11-330,e_w574152484-330,e_w215459565-330</t>
-  </si>
-  <si>
-    <t>e_w564429999-330,e_NG12-330</t>
-  </si>
-  <si>
-    <t>e_NG12-330,e_w565081403-330,e_w564429999-330</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_007</t>
   </si>
   <si>
@@ -1335,156 +1335,156 @@
     <t>connecting wind onshore to buses in cluster 12</t>
   </si>
   <si>
+    <t>distr_wonelc_won_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_006</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 6</t>
   </si>
   <si>
+    <t>distr_wonelc_won_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_002</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 2</t>
   </si>
   <si>
-    <t>distr_wonelc_won_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
     <t>elc_won_007</t>
   </si>
   <si>
@@ -1497,130 +1497,160 @@
     <t>e_w564410486-330,e_w695826179-330</t>
   </si>
   <si>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>e_w108020974-330</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>e_w564410486-330</t>
+  </si>
+  <si>
+    <t>elc_won_021</t>
+  </si>
+  <si>
+    <t>e_w266617120-330,e_w266712817-330</t>
+  </si>
+  <si>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>e_NG3-330,e_w556550171-330,e_w39469643-330</t>
+  </si>
+  <si>
+    <t>elc_won_022</t>
+  </si>
+  <si>
+    <t>elc_won_027</t>
+  </si>
+  <si>
+    <t>e_w266617120-330,e_w266712817-330,e_w267122040-330</t>
+  </si>
+  <si>
+    <t>elc_won_026</t>
+  </si>
+  <si>
+    <t>e_w266712817-330,e_w267122040-330,e_w655273140-330</t>
+  </si>
+  <si>
     <t>elc_won_006</t>
   </si>
   <si>
     <t>e_w695826179-330,e_w1328602766-330,e_w540463591-330</t>
   </si>
   <si>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>e_NG3-330,e_w556550171-330,e_w39469643-330,e_w266617120-330</t>
+  </si>
+  <si>
+    <t>elc_won_019</t>
+  </si>
+  <si>
+    <t>elc_won_011</t>
+  </si>
+  <si>
+    <t>e_w695826179-330,e_w564410486-330</t>
+  </si>
+  <si>
+    <t>elc_won_023</t>
+  </si>
+  <si>
+    <t>e_w564410486-330,e_w1226249784-330,e_NG1-330</t>
+  </si>
+  <si>
+    <t>elc_won_020</t>
+  </si>
+  <si>
+    <t>e_w395182311-330,e_w266712817-330,e_w563723584-330</t>
+  </si>
+  <si>
+    <t>elc_won_017</t>
+  </si>
+  <si>
+    <t>e_w266712817-330,e_w563723584-330,e_w655273140-330</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>e_w548724506-330,e_w563715917-330,e_w565081403-330</t>
+  </si>
+  <si>
+    <t>elc_won_018</t>
+  </si>
+  <si>
+    <t>e_w395182311-330,e_w563723584-330</t>
+  </si>
+  <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>elc_won_013</t>
+  </si>
+  <si>
+    <t>e_w564410486-330,e_w39469643-330,e_w1226249784-330,e_NG1-330,e_NG2-330</t>
+  </si>
+  <si>
+    <t>elc_won_025</t>
+  </si>
+  <si>
+    <t>e_w395182311-330,e_NG2-330,e_w266617120-330</t>
+  </si>
+  <si>
+    <t>elc_won_024</t>
+  </si>
+  <si>
+    <t>e_w266617120-330,e_w395182311-330</t>
+  </si>
+  <si>
+    <t>elc_won_016</t>
+  </si>
+  <si>
     <t>elc_won_002</t>
   </si>
   <si>
-    <t>elc_won_018</t>
-  </si>
-  <si>
-    <t>e_w395182311-330,e_w563723584-330</t>
-  </si>
-  <si>
-    <t>elc_won_003</t>
-  </si>
-  <si>
-    <t>elc_won_005</t>
-  </si>
-  <si>
-    <t>e_w548724506-330,e_w563715917-330,e_w565081403-330</t>
-  </si>
-  <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>e_w564410486-330</t>
-  </si>
-  <si>
-    <t>elc_won_010</t>
-  </si>
-  <si>
-    <t>e_NG3-330,e_w556550171-330,e_w39469643-330,e_w266617120-330</t>
-  </si>
-  <si>
-    <t>elc_won_019</t>
-  </si>
-  <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>e_w108020974-330</t>
-  </si>
-  <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>elc_won_021</t>
-  </si>
-  <si>
-    <t>e_w266617120-330,e_w266712817-330</t>
-  </si>
-  <si>
-    <t>elc_won_013</t>
-  </si>
-  <si>
-    <t>e_w564410486-330,e_w39469643-330,e_w1226249784-330,e_NG1-330,e_NG2-330</t>
-  </si>
-  <si>
-    <t>elc_won_025</t>
-  </si>
-  <si>
-    <t>e_w395182311-330,e_NG2-330,e_w266617120-330</t>
-  </si>
-  <si>
-    <t>elc_won_024</t>
-  </si>
-  <si>
-    <t>e_w266617120-330,e_w395182311-330</t>
-  </si>
-  <si>
-    <t>elc_won_016</t>
-  </si>
-  <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>e_NG3-330,e_w556550171-330,e_w39469643-330</t>
-  </si>
-  <si>
-    <t>elc_won_022</t>
-  </si>
-  <si>
-    <t>elc_won_027</t>
-  </si>
-  <si>
-    <t>e_w266617120-330,e_w266712817-330,e_w267122040-330</t>
-  </si>
-  <si>
-    <t>elc_won_026</t>
-  </si>
-  <si>
-    <t>e_w266712817-330,e_w267122040-330,e_w655273140-330</t>
-  </si>
-  <si>
-    <t>elc_won_011</t>
-  </si>
-  <si>
-    <t>e_w695826179-330,e_w564410486-330</t>
-  </si>
-  <si>
-    <t>elc_won_023</t>
-  </si>
-  <si>
-    <t>e_w564410486-330,e_w1226249784-330,e_NG1-330</t>
-  </si>
-  <si>
-    <t>elc_won_020</t>
-  </si>
-  <si>
-    <t>e_w395182311-330,e_w266712817-330,e_w563723584-330</t>
-  </si>
-  <si>
-    <t>elc_won_017</t>
-  </si>
-  <si>
-    <t>e_w266712817-330,e_w563723584-330,e_w655273140-330</t>
+    <t>distr_wofelc_wof_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
   </si>
   <si>
     <t>distr_wofelc_wof_004</t>
@@ -1635,42 +1665,12 @@
     <t>connecting wind offshore to buses in cluster 7</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_009</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 9</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_005</t>
   </si>
   <si>
@@ -1683,6 +1683,33 @@
     <t>connecting wind offshore to buses in cluster 6</t>
   </si>
   <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>elc_wof_010</t>
+  </si>
+  <si>
+    <t>e_NG18-330,e_w746582404-330</t>
+  </si>
+  <si>
+    <t>elc_wof_001</t>
+  </si>
+  <si>
+    <t>e_NG9-330,e_w1324578567-330,e_w565866986-330</t>
+  </si>
+  <si>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>e_w706082453-330,e_w108020974-330,e_w559542338-330,e_w565866986-330,e_w546666333-330</t>
+  </si>
+  <si>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
+    <t>e_NG18-330</t>
+  </si>
+  <si>
     <t>elc_wof_004</t>
   </si>
   <si>
@@ -1695,37 +1722,10 @@
     <t>e_w746582404-330,e_w564430566-330</t>
   </si>
   <si>
-    <t>elc_wof_003</t>
-  </si>
-  <si>
-    <t>e_NG18-330</t>
-  </si>
-  <si>
-    <t>elc_wof_001</t>
-  </si>
-  <si>
-    <t>e_NG9-330,e_w1324578567-330,e_w565866986-330</t>
-  </si>
-  <si>
-    <t>elc_wof_002</t>
-  </si>
-  <si>
-    <t>e_w706082453-330,e_w108020974-330,e_w559542338-330,e_w565866986-330,e_w546666333-330</t>
-  </si>
-  <si>
-    <t>elc_wof_008</t>
-  </si>
-  <si>
     <t>elc_wof_009</t>
   </si>
   <si>
     <t>e_w746582404-330</t>
-  </si>
-  <si>
-    <t>elc_wof_010</t>
-  </si>
-  <si>
-    <t>e_NG18-330,e_w746582404-330</t>
   </si>
   <si>
     <t>elc_wof_005</t>
@@ -6755,7 +6755,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EB6375C-E804-4453-90D9-50E27C892516}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EA44A11-E72C-437B-BF30-04DE123DD0B9}">
   <dimension ref="B9:BD46"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6993,16 +6993,16 @@
         <v>288</v>
       </c>
       <c r="Y11" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="Z11" t="s">
         <v>364</v>
       </c>
       <c r="AA11">
-        <v>0.99884992726149324</v>
+        <v>0.99723470592138874</v>
       </c>
       <c r="AB11">
-        <v>21.084666872623977</v>
+        <v>50.697058107873339</v>
       </c>
       <c r="AD11" t="s">
         <v>287</v>
@@ -7068,13 +7068,13 @@
         <v>518</v>
       </c>
       <c r="BB11" t="s">
-        <v>519</v>
+        <v>375</v>
       </c>
       <c r="BC11">
-        <v>0.99246115999793105</v>
+        <v>0.99337755486839363</v>
       </c>
       <c r="BD11">
-        <v>138.21206670459694</v>
+        <v>121.41149407945062</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7139,16 +7139,16 @@
         <v>292</v>
       </c>
       <c r="Y12" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="Z12" t="s">
         <v>365</v>
       </c>
       <c r="AA12">
-        <v>0.99882431199806432</v>
+        <v>0.99750455285561002</v>
       </c>
       <c r="AB12">
-        <v>21.554280035486567</v>
+        <v>45.749864313816033</v>
       </c>
       <c r="AD12" t="s">
         <v>287</v>
@@ -7211,16 +7211,16 @@
         <v>500</v>
       </c>
       <c r="BA12" t="s">
+        <v>519</v>
+      </c>
+      <c r="BB12" t="s">
         <v>520</v>
       </c>
-      <c r="BB12" t="s">
-        <v>521</v>
-      </c>
       <c r="BC12">
-        <v>0.99268778174342398</v>
+        <v>0.99371472191320109</v>
       </c>
       <c r="BD12">
-        <v>134.05733470389279</v>
+        <v>115.23009825798009</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -7285,16 +7285,16 @@
         <v>294</v>
       </c>
       <c r="Y13" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="Z13" t="s">
         <v>366</v>
       </c>
       <c r="AA13">
-        <v>0.99723470592138874</v>
+        <v>0.99884992726149324</v>
       </c>
       <c r="AB13">
-        <v>50.697058107873339</v>
+        <v>21.084666872623977</v>
       </c>
       <c r="AD13" t="s">
         <v>287</v>
@@ -7327,10 +7327,10 @@
         <v>457</v>
       </c>
       <c r="AO13">
-        <v>0.99429686126958916</v>
+        <v>0.99795762496221851</v>
       </c>
       <c r="AP13">
-        <v>104.55754339086491</v>
+        <v>37.443542359327118</v>
       </c>
       <c r="AR13" t="s">
         <v>287</v>
@@ -7357,16 +7357,16 @@
         <v>502</v>
       </c>
       <c r="BA13" t="s">
+        <v>521</v>
+      </c>
+      <c r="BB13" t="s">
         <v>522</v>
       </c>
-      <c r="BB13" t="s">
-        <v>523</v>
-      </c>
       <c r="BC13">
-        <v>0.99174031680019514</v>
+        <v>0.99794494286432878</v>
       </c>
       <c r="BD13">
-        <v>151.42752532975524</v>
+        <v>37.67604748730637</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -7431,16 +7431,16 @@
         <v>296</v>
       </c>
       <c r="Y14" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="Z14" t="s">
         <v>367</v>
       </c>
       <c r="AA14">
-        <v>0.99750455285561002</v>
+        <v>0.99882431199806432</v>
       </c>
       <c r="AB14">
-        <v>45.749864313816033</v>
+        <v>21.554280035486567</v>
       </c>
       <c r="AD14" t="s">
         <v>287</v>
@@ -7470,13 +7470,13 @@
         <v>458</v>
       </c>
       <c r="AN14" t="s">
-        <v>374</v>
+        <v>459</v>
       </c>
       <c r="AO14">
-        <v>0.99537626424805781</v>
+        <v>0.99582871194680656</v>
       </c>
       <c r="AP14">
-        <v>84.768488785605911</v>
+        <v>76.473614308545862</v>
       </c>
       <c r="AR14" t="s">
         <v>287</v>
@@ -7503,16 +7503,16 @@
         <v>504</v>
       </c>
       <c r="BA14" t="s">
+        <v>523</v>
+      </c>
+      <c r="BB14" t="s">
         <v>524</v>
       </c>
-      <c r="BB14" t="s">
-        <v>525</v>
-      </c>
       <c r="BC14">
-        <v>0.99794494286432878</v>
+        <v>0.9962053430710629</v>
       </c>
       <c r="BD14">
-        <v>37.67604748730637</v>
+        <v>69.568710363846861</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7577,16 +7577,16 @@
         <v>298</v>
       </c>
       <c r="Y15" t="s">
-        <v>256</v>
+        <v>280</v>
       </c>
       <c r="Z15" t="s">
         <v>368</v>
       </c>
       <c r="AA15">
-        <v>0.99605704806429607</v>
+        <v>0.993124380119488</v>
       </c>
       <c r="AB15">
-        <v>72.28745215457208</v>
+        <v>126.05303114271953</v>
       </c>
       <c r="AD15" t="s">
         <v>287</v>
@@ -7613,16 +7613,16 @@
         <v>406</v>
       </c>
       <c r="AM15" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AN15" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AO15">
-        <v>0.98839759805196303</v>
+        <v>0.99555964959117016</v>
       </c>
       <c r="AP15">
-        <v>212.71070238067816</v>
+        <v>81.406424161880452</v>
       </c>
       <c r="AR15" t="s">
         <v>287</v>
@@ -7649,16 +7649,16 @@
         <v>506</v>
       </c>
       <c r="BA15" t="s">
+        <v>525</v>
+      </c>
+      <c r="BB15" t="s">
         <v>526</v>
       </c>
-      <c r="BB15" t="s">
-        <v>527</v>
-      </c>
       <c r="BC15">
-        <v>0.9962053430710629</v>
+        <v>0.99174031680019514</v>
       </c>
       <c r="BD15">
-        <v>69.568710363846861</v>
+        <v>151.42752532975524</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -7723,16 +7723,16 @@
         <v>300</v>
       </c>
       <c r="Y16" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="Z16" t="s">
         <v>369</v>
       </c>
       <c r="AA16">
-        <v>0.99167914755584141</v>
+        <v>0.99769438809486533</v>
       </c>
       <c r="AB16">
-        <v>152.54896147624135</v>
+        <v>42.269551594135834</v>
       </c>
       <c r="AD16" t="s">
         <v>287</v>
@@ -7759,16 +7759,16 @@
         <v>408</v>
       </c>
       <c r="AM16" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AN16" t="s">
-        <v>374</v>
+        <v>463</v>
       </c>
       <c r="AO16">
-        <v>0.99671794291781168</v>
+        <v>0.9964390810242717</v>
       </c>
       <c r="AP16">
-        <v>60.171046506785672</v>
+        <v>65.283514555019096</v>
       </c>
       <c r="AR16" t="s">
         <v>287</v>
@@ -7795,16 +7795,16 @@
         <v>508</v>
       </c>
       <c r="BA16" t="s">
+        <v>527</v>
+      </c>
+      <c r="BB16" t="s">
         <v>528</v>
       </c>
-      <c r="BB16" t="s">
-        <v>368</v>
-      </c>
       <c r="BC16">
-        <v>0.99337755486839363</v>
+        <v>0.99246115999793105</v>
       </c>
       <c r="BD16">
-        <v>121.41149407945062</v>
+        <v>138.21206670459694</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -7869,16 +7869,16 @@
         <v>302</v>
       </c>
       <c r="Y17" t="s">
-        <v>285</v>
+        <v>271</v>
       </c>
       <c r="Z17" t="s">
         <v>370</v>
       </c>
       <c r="AA17">
-        <v>0.996629171401053</v>
+        <v>0.99489048613238573</v>
       </c>
       <c r="AB17">
-        <v>61.798524314027716</v>
+        <v>93.674420906261602</v>
       </c>
       <c r="AD17" t="s">
         <v>287</v>
@@ -7905,16 +7905,16 @@
         <v>410</v>
       </c>
       <c r="AM17" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AN17" t="s">
-        <v>463</v>
+        <v>378</v>
       </c>
       <c r="AO17">
-        <v>0.99562035686170025</v>
+        <v>0.99592873360628342</v>
       </c>
       <c r="AP17">
-        <v>80.293457535494625</v>
+        <v>74.639883884803922</v>
       </c>
       <c r="AR17" t="s">
         <v>287</v>
@@ -7947,10 +7947,10 @@
         <v>530</v>
       </c>
       <c r="BC17">
-        <v>0.99755731205629283</v>
+        <v>0.99268778174342398</v>
       </c>
       <c r="BD17">
-        <v>44.782612301298634</v>
+        <v>134.05733470389279</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8015,16 +8015,16 @@
         <v>304</v>
       </c>
       <c r="Y18" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="Z18" t="s">
         <v>371</v>
       </c>
       <c r="AA18">
-        <v>0.9940266623681554</v>
+        <v>0.99642867204968677</v>
       </c>
       <c r="AB18">
-        <v>109.51118991715018</v>
+        <v>65.474345755743457</v>
       </c>
       <c r="AD18" t="s">
         <v>287</v>
@@ -8051,16 +8051,16 @@
         <v>412</v>
       </c>
       <c r="AM18" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AN18" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AO18">
-        <v>0.9933445384762607</v>
+        <v>0.99534990870245532</v>
       </c>
       <c r="AP18">
-        <v>122.01679460188713</v>
+        <v>85.251673788320105</v>
       </c>
       <c r="AR18" t="s">
         <v>287</v>
@@ -8093,10 +8093,10 @@
         <v>532</v>
       </c>
       <c r="BC18">
-        <v>0.99371472191320109</v>
+        <v>0.99755731205629283</v>
       </c>
       <c r="BD18">
-        <v>115.23009825798009</v>
+        <v>44.782612301298634</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8161,16 +8161,16 @@
         <v>306</v>
       </c>
       <c r="Y19" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="Z19" t="s">
         <v>372</v>
       </c>
       <c r="AA19">
-        <v>0.99629635001073991</v>
+        <v>0.99514004796050048</v>
       </c>
       <c r="AB19">
-        <v>67.900249803101318</v>
+        <v>89.099120724157018</v>
       </c>
       <c r="AD19" t="s">
         <v>287</v>
@@ -8197,16 +8197,16 @@
         <v>414</v>
       </c>
       <c r="AM19" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AN19" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AO19">
-        <v>0.9938298282896767</v>
+        <v>0.99283555585293171</v>
       </c>
       <c r="AP19">
-        <v>113.11981468926018</v>
+        <v>131.34814269625272</v>
       </c>
       <c r="AR19" t="s">
         <v>287</v>
@@ -8236,7 +8236,7 @@
         <v>533</v>
       </c>
       <c r="BB19" t="s">
-        <v>532</v>
+        <v>520</v>
       </c>
       <c r="BC19">
         <v>0.9888409065104441</v>
@@ -8307,16 +8307,16 @@
         <v>308</v>
       </c>
       <c r="Y20" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="Z20" t="s">
         <v>373</v>
       </c>
       <c r="AA20">
-        <v>0.99383936956194807</v>
+        <v>0.99589467345586935</v>
       </c>
       <c r="AB20">
-        <v>112.94489136428538</v>
+        <v>75.264319975727958</v>
       </c>
       <c r="AD20" t="s">
         <v>287</v>
@@ -8343,16 +8343,16 @@
         <v>416</v>
       </c>
       <c r="AM20" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AN20" t="s">
-        <v>381</v>
+        <v>470</v>
       </c>
       <c r="AO20">
-        <v>0.99008544123370779</v>
+        <v>0.99429686126958916</v>
       </c>
       <c r="AP20">
-        <v>181.76691071535706</v>
+        <v>104.55754339086491</v>
       </c>
       <c r="AR20" t="s">
         <v>287</v>
@@ -8382,7 +8382,7 @@
         <v>534</v>
       </c>
       <c r="BB20" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="BC20">
         <v>0.99132158137897763</v>
@@ -8453,16 +8453,16 @@
         <v>310</v>
       </c>
       <c r="Y21" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="Z21" t="s">
         <v>374</v>
       </c>
       <c r="AA21">
-        <v>0.98416398409272543</v>
+        <v>0.99744993905722468</v>
       </c>
       <c r="AB21">
-        <v>290.32695830003399</v>
+        <v>46.751117284213812</v>
       </c>
       <c r="AD21" t="s">
         <v>287</v>
@@ -8489,16 +8489,16 @@
         <v>418</v>
       </c>
       <c r="AM21" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AN21" t="s">
-        <v>470</v>
+        <v>459</v>
       </c>
       <c r="AO21">
-        <v>0.99795762496221851</v>
+        <v>0.9933445384762607</v>
       </c>
       <c r="AP21">
-        <v>37.443542359327118</v>
+        <v>122.01679460188713</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8563,16 +8563,16 @@
         <v>312</v>
       </c>
       <c r="Y22" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Z22" t="s">
         <v>375</v>
       </c>
       <c r="AA22">
-        <v>0.99832768028365393</v>
+        <v>0.99605704806429607</v>
       </c>
       <c r="AB22">
-        <v>30.659194799678048</v>
+        <v>72.28745215457208</v>
       </c>
       <c r="AD22" t="s">
         <v>287</v>
@@ -8599,16 +8599,16 @@
         <v>420</v>
       </c>
       <c r="AM22" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AN22" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="AO22">
-        <v>0.99582871194680656</v>
+        <v>0.9938298282896767</v>
       </c>
       <c r="AP22">
-        <v>76.473614308545862</v>
+        <v>113.11981468926018</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -8673,16 +8673,16 @@
         <v>314</v>
       </c>
       <c r="Y23" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="Z23" t="s">
         <v>376</v>
       </c>
       <c r="AA23">
-        <v>0.99057172008573791</v>
+        <v>0.99167914755584141</v>
       </c>
       <c r="AB23">
-        <v>172.85179842813815</v>
+        <v>152.54896147624135</v>
       </c>
       <c r="AD23" t="s">
         <v>287</v>
@@ -8709,16 +8709,16 @@
         <v>422</v>
       </c>
       <c r="AM23" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AN23" t="s">
-        <v>473</v>
+        <v>380</v>
       </c>
       <c r="AO23">
-        <v>0.99555964959117016</v>
+        <v>0.99008544123370779</v>
       </c>
       <c r="AP23">
-        <v>81.406424161880452</v>
+        <v>181.76691071535706</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -8783,16 +8783,16 @@
         <v>316</v>
       </c>
       <c r="Y24" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="Z24" t="s">
         <v>377</v>
       </c>
       <c r="AA24">
-        <v>0.99095032933880767</v>
+        <v>0.9963457067026108</v>
       </c>
       <c r="AB24">
-        <v>165.91062878852651</v>
+        <v>66.99537711880258</v>
       </c>
       <c r="AD24" t="s">
         <v>287</v>
@@ -8819,16 +8819,16 @@
         <v>424</v>
       </c>
       <c r="AM24" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AN24" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AO24">
-        <v>0.99207403494667001</v>
+        <v>0.99178855761800622</v>
       </c>
       <c r="AP24">
-        <v>145.30935931104892</v>
+        <v>150.54311033655213</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -8893,16 +8893,16 @@
         <v>318</v>
       </c>
       <c r="Y25" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="Z25" t="s">
         <v>378</v>
       </c>
       <c r="AA25">
-        <v>0.9963457067026108</v>
+        <v>0.99644641159652714</v>
       </c>
       <c r="AB25">
-        <v>66.99537711880258</v>
+        <v>65.149120730335611</v>
       </c>
       <c r="AD25" t="s">
         <v>287</v>
@@ -8929,16 +8929,16 @@
         <v>426</v>
       </c>
       <c r="AM25" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AN25" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AO25">
-        <v>0.99637613831578808</v>
+        <v>0.99296304108660982</v>
       </c>
       <c r="AP25">
-        <v>66.437464210551497</v>
+        <v>129.01091341215286</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -9003,16 +9003,16 @@
         <v>320</v>
       </c>
       <c r="Y26" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="Z26" t="s">
         <v>379</v>
       </c>
       <c r="AA26">
-        <v>0.99644641159652714</v>
+        <v>0.99436579068013853</v>
       </c>
       <c r="AB26">
-        <v>65.149120730335611</v>
+        <v>103.29383753079337</v>
       </c>
       <c r="AD26" t="s">
         <v>287</v>
@@ -9039,16 +9039,16 @@
         <v>428</v>
       </c>
       <c r="AM26" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AN26" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AO26">
-        <v>0.99501745221162918</v>
+        <v>0.99152317643653909</v>
       </c>
       <c r="AP26">
-        <v>91.346709453464783</v>
+        <v>155.40843199678267</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -9113,16 +9113,16 @@
         <v>322</v>
       </c>
       <c r="Y27" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="Z27" t="s">
         <v>380</v>
       </c>
       <c r="AA27">
-        <v>0.99436579068013853</v>
+        <v>0.99262439568706373</v>
       </c>
       <c r="AB27">
-        <v>103.29383753079337</v>
+        <v>135.21941240383219</v>
       </c>
       <c r="AD27" t="s">
         <v>287</v>
@@ -9149,16 +9149,16 @@
         <v>430</v>
       </c>
       <c r="AM27" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AN27" t="s">
-        <v>381</v>
+        <v>482</v>
       </c>
       <c r="AO27">
-        <v>0.99698529931119073</v>
+        <v>0.99475386493829931</v>
       </c>
       <c r="AP27">
-        <v>55.269512628170503</v>
+        <v>96.179142797845941</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -9223,16 +9223,16 @@
         <v>324</v>
       </c>
       <c r="Y28" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="Z28" t="s">
         <v>381</v>
       </c>
       <c r="AA28">
-        <v>0.99262439568706373</v>
+        <v>0.99802162515875081</v>
       </c>
       <c r="AB28">
-        <v>135.21941240383219</v>
+        <v>36.270205422902137</v>
       </c>
       <c r="AD28" t="s">
         <v>287</v>
@@ -9259,16 +9259,16 @@
         <v>432</v>
       </c>
       <c r="AM28" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AN28" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AO28">
-        <v>0.99354454384798807</v>
+        <v>0.99671794291781168</v>
       </c>
       <c r="AP28">
-        <v>118.35002945355123</v>
+        <v>60.171046506785672</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9333,16 +9333,16 @@
         <v>326</v>
       </c>
       <c r="Y29" t="s">
-        <v>280</v>
+        <v>252</v>
       </c>
       <c r="Z29" t="s">
         <v>382</v>
       </c>
       <c r="AA29">
-        <v>0.993124380119488</v>
+        <v>0.99631349511992195</v>
       </c>
       <c r="AB29">
-        <v>126.05303114271953</v>
+        <v>67.585922801431252</v>
       </c>
       <c r="AD29" t="s">
         <v>287</v>
@@ -9369,16 +9369,16 @@
         <v>434</v>
       </c>
       <c r="AM29" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="AN29" t="s">
-        <v>377</v>
+        <v>485</v>
       </c>
       <c r="AO29">
-        <v>0.99069345154297106</v>
+        <v>0.99562035686170025</v>
       </c>
       <c r="AP29">
-        <v>170.62005504553079</v>
+        <v>80.293457535494625</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9443,16 +9443,16 @@
         <v>328</v>
       </c>
       <c r="Y30" t="s">
-        <v>274</v>
+        <v>254</v>
       </c>
       <c r="Z30" t="s">
         <v>383</v>
       </c>
       <c r="AA30">
-        <v>0.99769438809486533</v>
+        <v>0.99832768028365393</v>
       </c>
       <c r="AB30">
-        <v>42.269551594135834</v>
+        <v>30.659194799678048</v>
       </c>
       <c r="AD30" t="s">
         <v>287</v>
@@ -9479,16 +9479,16 @@
         <v>436</v>
       </c>
       <c r="AM30" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="AN30" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="AO30">
-        <v>0.9964390810242717</v>
+        <v>0.98839759805196303</v>
       </c>
       <c r="AP30">
-        <v>65.283514555019096</v>
+        <v>212.71070238067816</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -9553,16 +9553,16 @@
         <v>330</v>
       </c>
       <c r="Y31" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="Z31" t="s">
         <v>384</v>
       </c>
       <c r="AA31">
-        <v>0.99489048613238573</v>
+        <v>0.99057172008573791</v>
       </c>
       <c r="AB31">
-        <v>93.674420906261602</v>
+        <v>172.85179842813815</v>
       </c>
       <c r="AD31" t="s">
         <v>287</v>
@@ -9589,16 +9589,16 @@
         <v>438</v>
       </c>
       <c r="AM31" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="AN31" t="s">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="AO31">
-        <v>0.99592873360628342</v>
+        <v>0.99354454384798807</v>
       </c>
       <c r="AP31">
-        <v>74.639883884803922</v>
+        <v>118.35002945355123</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -9663,16 +9663,16 @@
         <v>332</v>
       </c>
       <c r="Y32" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="Z32" t="s">
         <v>385</v>
       </c>
       <c r="AA32">
-        <v>0.99642867204968677</v>
+        <v>0.99095032933880767</v>
       </c>
       <c r="AB32">
-        <v>65.474345755743457</v>
+        <v>165.91062878852651</v>
       </c>
       <c r="AD32" t="s">
         <v>287</v>
@@ -9699,16 +9699,16 @@
         <v>440</v>
       </c>
       <c r="AM32" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="AN32" t="s">
-        <v>487</v>
+        <v>385</v>
       </c>
       <c r="AO32">
-        <v>0.99534990870245532</v>
+        <v>0.99069345154297106</v>
       </c>
       <c r="AP32">
-        <v>85.251673788320105</v>
+        <v>170.62005504553079</v>
       </c>
     </row>
     <row r="33" spans="2:42">
@@ -9773,16 +9773,16 @@
         <v>334</v>
       </c>
       <c r="Y33" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="Z33" t="s">
         <v>386</v>
       </c>
       <c r="AA33">
-        <v>0.99514004796050048</v>
+        <v>0.99655017109874156</v>
       </c>
       <c r="AB33">
-        <v>89.099120724157018</v>
+        <v>63.246863189739024</v>
       </c>
       <c r="AD33" t="s">
         <v>287</v>
@@ -9809,16 +9809,16 @@
         <v>442</v>
       </c>
       <c r="AM33" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="AN33" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="AO33">
-        <v>0.99283555585293171</v>
+        <v>0.99207403494667001</v>
       </c>
       <c r="AP33">
-        <v>131.34814269625272</v>
+        <v>145.30935931104892</v>
       </c>
     </row>
     <row r="34" spans="2:42">
@@ -9883,16 +9883,16 @@
         <v>336</v>
       </c>
       <c r="Y34" t="s">
-        <v>265</v>
+        <v>279</v>
       </c>
       <c r="Z34" t="s">
-        <v>374</v>
+        <v>387</v>
       </c>
       <c r="AA34">
-        <v>0.99589467345586935</v>
+        <v>0.99133276722560904</v>
       </c>
       <c r="AB34">
-        <v>75.264319975727958</v>
+        <v>158.89926753050145</v>
       </c>
       <c r="AD34" t="s">
         <v>287</v>
@@ -9919,16 +9919,16 @@
         <v>444</v>
       </c>
       <c r="AM34" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AN34" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AO34">
-        <v>0.99178855761800622</v>
+        <v>0.99637613831578808</v>
       </c>
       <c r="AP34">
-        <v>150.54311033655213</v>
+        <v>66.437464210551497</v>
       </c>
     </row>
     <row r="35" spans="2:42">
@@ -9993,16 +9993,16 @@
         <v>338</v>
       </c>
       <c r="Y35" t="s">
-        <v>281</v>
+        <v>260</v>
       </c>
       <c r="Z35" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AA35">
-        <v>0.99339354842512728</v>
+        <v>0.99728758220200375</v>
       </c>
       <c r="AB35">
-        <v>121.1182788726671</v>
+        <v>49.727659629930621</v>
       </c>
       <c r="AD35" t="s">
         <v>287</v>
@@ -10029,16 +10029,16 @@
         <v>446</v>
       </c>
       <c r="AM35" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="AN35" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="AO35">
-        <v>0.99296304108660982</v>
+        <v>0.99501745221162918</v>
       </c>
       <c r="AP35">
-        <v>129.01091341215286</v>
+        <v>91.346709453464783</v>
       </c>
     </row>
     <row r="36" spans="2:42">
@@ -10103,16 +10103,16 @@
         <v>340</v>
       </c>
       <c r="Y36" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="Z36" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AA36">
-        <v>0.99805028151894915</v>
+        <v>0.99732710525923551</v>
       </c>
       <c r="AB36">
-        <v>35.744838819266263</v>
+        <v>49.003070247349498</v>
       </c>
       <c r="AD36" t="s">
         <v>287</v>
@@ -10139,16 +10139,16 @@
         <v>448</v>
       </c>
       <c r="AM36" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="AN36" t="s">
-        <v>495</v>
+        <v>380</v>
       </c>
       <c r="AO36">
-        <v>0.99152317643653909</v>
+        <v>0.99698529931119073</v>
       </c>
       <c r="AP36">
-        <v>155.40843199678267</v>
+        <v>55.269512628170503</v>
       </c>
     </row>
     <row r="37" spans="2:42">
@@ -10213,16 +10213,16 @@
         <v>342</v>
       </c>
       <c r="Y37" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="Z37" t="s">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c r="AA37">
-        <v>0.98395338050941106</v>
+        <v>0.99601914721828588</v>
       </c>
       <c r="AB37">
-        <v>294.18802399413073</v>
+        <v>72.982300998092228</v>
       </c>
       <c r="AD37" t="s">
         <v>287</v>
@@ -10249,16 +10249,16 @@
         <v>450</v>
       </c>
       <c r="AM37" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AN37" t="s">
-        <v>497</v>
+        <v>373</v>
       </c>
       <c r="AO37">
-        <v>0.99475386493829931</v>
+        <v>0.99537626424805781</v>
       </c>
       <c r="AP37">
-        <v>96.179142797845941</v>
+        <v>84.768488785605911</v>
       </c>
     </row>
     <row r="38" spans="2:42">
@@ -10323,16 +10323,16 @@
         <v>344</v>
       </c>
       <c r="Y38" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="Z38" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AA38">
-        <v>0.99655017109874156</v>
+        <v>0.99403967905190227</v>
       </c>
       <c r="AB38">
-        <v>63.246863189739024</v>
+        <v>109.27255071512499</v>
       </c>
     </row>
     <row r="39" spans="2:42">
@@ -10397,16 +10397,16 @@
         <v>346</v>
       </c>
       <c r="Y39" t="s">
-        <v>253</v>
+        <v>281</v>
       </c>
       <c r="Z39" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AA39">
-        <v>0.99802162515875081</v>
+        <v>0.99339354842512728</v>
       </c>
       <c r="AB39">
-        <v>36.270205422902137</v>
+        <v>121.1182788726671</v>
       </c>
     </row>
     <row r="40" spans="2:42">
@@ -10471,16 +10471,16 @@
         <v>348</v>
       </c>
       <c r="Y40" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="Z40" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AA40">
-        <v>0.99631349511992195</v>
+        <v>0.99805028151894915</v>
       </c>
       <c r="AB40">
-        <v>67.585922801431252</v>
+        <v>35.744838819266263</v>
       </c>
     </row>
     <row r="41" spans="2:42">
@@ -10545,16 +10545,16 @@
         <v>350</v>
       </c>
       <c r="Y41" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="Z41" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="AA41">
-        <v>0.99133276722560904</v>
+        <v>0.98395338050941106</v>
       </c>
       <c r="AB41">
-        <v>158.89926753050145</v>
+        <v>294.18802399413073</v>
       </c>
     </row>
     <row r="42" spans="2:42">
@@ -10619,16 +10619,16 @@
         <v>352</v>
       </c>
       <c r="Y42" t="s">
-        <v>260</v>
+        <v>285</v>
       </c>
       <c r="Z42" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AA42">
-        <v>0.99728758220200375</v>
+        <v>0.996629171401053</v>
       </c>
       <c r="AB42">
-        <v>49.727659629930621</v>
+        <v>61.798524314027716</v>
       </c>
     </row>
     <row r="43" spans="2:42">
@@ -10693,16 +10693,16 @@
         <v>354</v>
       </c>
       <c r="Y43" t="s">
-        <v>255</v>
+        <v>275</v>
       </c>
       <c r="Z43" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AA43">
-        <v>0.99744993905722468</v>
+        <v>0.9940266623681554</v>
       </c>
       <c r="AB43">
-        <v>46.751117284213812</v>
+        <v>109.51118991715018</v>
       </c>
     </row>
     <row r="44" spans="2:42">
@@ -10767,16 +10767,16 @@
         <v>356</v>
       </c>
       <c r="Y44" t="s">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="Z44" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AA44">
-        <v>0.99732710525923551</v>
+        <v>0.99629635001073991</v>
       </c>
       <c r="AB44">
-        <v>49.003070247349498</v>
+        <v>67.900249803101318</v>
       </c>
     </row>
     <row r="45" spans="2:42">
@@ -10841,16 +10841,16 @@
         <v>358</v>
       </c>
       <c r="Y45" t="s">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="Z45" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AA45">
-        <v>0.99601914721828588</v>
+        <v>0.99383936956194807</v>
       </c>
       <c r="AB45">
-        <v>72.982300998092228</v>
+        <v>112.94489136428538</v>
       </c>
     </row>
     <row r="46" spans="2:42">
@@ -10915,16 +10915,16 @@
         <v>360</v>
       </c>
       <c r="Y46" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Z46" t="s">
-        <v>397</v>
+        <v>373</v>
       </c>
       <c r="AA46">
-        <v>0.99403967905190227</v>
+        <v>0.98416398409272543</v>
       </c>
       <c r="AB46">
-        <v>109.27255071512499</v>
+        <v>290.32695830003399</v>
       </c>
     </row>
   </sheetData>
@@ -10933,7 +10933,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBDD3EB3-3D7B-459D-BF0E-CCBCB6742328}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C649A00-0D04-454E-A807-475C15654135}">
   <dimension ref="B9:Z37"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -11045,7 +11045,7 @@
         <v>535</v>
       </c>
       <c r="K11" t="s">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="L11">
         <v>10.088237612202811</v>
@@ -11078,7 +11078,7 @@
         <v>589</v>
       </c>
       <c r="X11" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="Y11">
         <v>0.16350000000000001</v>
@@ -11113,7 +11113,7 @@
         <v>537</v>
       </c>
       <c r="K12" t="s">
-        <v>458</v>
+        <v>497</v>
       </c>
       <c r="L12">
         <v>4.7527038630847755</v>
@@ -11146,7 +11146,7 @@
         <v>591</v>
       </c>
       <c r="X12" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="Y12">
         <v>13.40025</v>
@@ -11181,7 +11181,7 @@
         <v>539</v>
       </c>
       <c r="K13" t="s">
-        <v>461</v>
+        <v>483</v>
       </c>
       <c r="L13">
         <v>1.4400913107240583</v>
@@ -11214,7 +11214,7 @@
         <v>593</v>
       </c>
       <c r="X13" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="Y13">
         <v>8.4097500000000007</v>
@@ -11249,7 +11249,7 @@
         <v>541</v>
       </c>
       <c r="K14" t="s">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="L14">
         <v>1.437273477445641</v>
@@ -11282,7 +11282,7 @@
         <v>595</v>
       </c>
       <c r="X14" t="s">
-        <v>518</v>
+        <v>527</v>
       </c>
       <c r="Y14">
         <v>14.358750000000001</v>
@@ -11317,7 +11317,7 @@
         <v>543</v>
       </c>
       <c r="K15" t="s">
-        <v>462</v>
+        <v>484</v>
       </c>
       <c r="L15">
         <v>2.1922713563210485</v>
@@ -11385,7 +11385,7 @@
         <v>545</v>
       </c>
       <c r="K16" t="s">
-        <v>456</v>
+        <v>469</v>
       </c>
       <c r="L16">
         <v>0.73811583011208182</v>
@@ -11486,7 +11486,7 @@
         <v>601</v>
       </c>
       <c r="X17" t="s">
-        <v>520</v>
+        <v>529</v>
       </c>
       <c r="Y17">
         <v>8.6609999999999996</v>
@@ -11521,7 +11521,7 @@
         <v>549</v>
       </c>
       <c r="K18" t="s">
-        <v>469</v>
+        <v>456</v>
       </c>
       <c r="L18">
         <v>5.5488357050452785E-3</v>
@@ -11554,7 +11554,7 @@
         <v>603</v>
       </c>
       <c r="X18" t="s">
-        <v>528</v>
+        <v>518</v>
       </c>
       <c r="Y18">
         <v>3.4147500000000002</v>
@@ -11589,7 +11589,7 @@
         <v>551</v>
       </c>
       <c r="K19" t="s">
-        <v>483</v>
+        <v>462</v>
       </c>
       <c r="L19">
         <v>6.6811161360847313</v>
@@ -11622,7 +11622,7 @@
         <v>605</v>
       </c>
       <c r="X19" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="Y19">
         <v>1.7250000000000001E-2</v>
@@ -11657,7 +11657,7 @@
         <v>553</v>
       </c>
       <c r="K20" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="L20">
         <v>18.094012332227912</v>
@@ -11690,7 +11690,7 @@
         <v>607</v>
       </c>
       <c r="X20" t="s">
-        <v>531</v>
+        <v>519</v>
       </c>
       <c r="Y20">
         <v>6.8624999999999998</v>
@@ -11725,7 +11725,7 @@
         <v>555</v>
       </c>
       <c r="K21" t="s">
-        <v>490</v>
+        <v>475</v>
       </c>
       <c r="L21">
         <v>1.3529085560597105</v>
@@ -11795,7 +11795,7 @@
         <v>559</v>
       </c>
       <c r="K23" t="s">
-        <v>474</v>
+        <v>490</v>
       </c>
       <c r="L23">
         <v>13.683903390107789</v>
@@ -11830,7 +11830,7 @@
         <v>561</v>
       </c>
       <c r="K24" t="s">
-        <v>471</v>
+        <v>458</v>
       </c>
       <c r="L24">
         <v>5.4676081362262012</v>
@@ -11865,7 +11865,7 @@
         <v>563</v>
       </c>
       <c r="K25" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="L25">
         <v>8.9064794695455216</v>
@@ -11900,7 +11900,7 @@
         <v>565</v>
       </c>
       <c r="K26" t="s">
-        <v>480</v>
+        <v>496</v>
       </c>
       <c r="L26">
         <v>14.189229081738485</v>
@@ -11935,7 +11935,7 @@
         <v>567</v>
       </c>
       <c r="K27" t="s">
-        <v>496</v>
+        <v>481</v>
       </c>
       <c r="L27">
         <v>10.717982842540293</v>
@@ -11970,7 +11970,7 @@
         <v>569</v>
       </c>
       <c r="K28" t="s">
-        <v>459</v>
+        <v>486</v>
       </c>
       <c r="L28">
         <v>9.6743476082482847</v>
@@ -12005,7 +12005,7 @@
         <v>571</v>
       </c>
       <c r="K29" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="L29">
         <v>23.206762484053751</v>
@@ -12040,7 +12040,7 @@
         <v>573</v>
       </c>
       <c r="K30" t="s">
-        <v>494</v>
+        <v>479</v>
       </c>
       <c r="L30">
         <v>5.8372174437039801</v>
@@ -12075,7 +12075,7 @@
         <v>575</v>
       </c>
       <c r="K31" t="s">
-        <v>472</v>
+        <v>460</v>
       </c>
       <c r="L31">
         <v>1.8845590125315521</v>
@@ -12110,7 +12110,7 @@
         <v>577</v>
       </c>
       <c r="K32" t="s">
-        <v>485</v>
+        <v>464</v>
       </c>
       <c r="L32">
         <v>7.179650801796102</v>
@@ -12145,7 +12145,7 @@
         <v>579</v>
       </c>
       <c r="K33" t="s">
-        <v>492</v>
+        <v>477</v>
       </c>
       <c r="L33">
         <v>14.559476964149322</v>
@@ -12180,7 +12180,7 @@
         <v>581</v>
       </c>
       <c r="K34" t="s">
-        <v>478</v>
+        <v>494</v>
       </c>
       <c r="L34">
         <v>1.3536151515148049</v>
@@ -12215,7 +12215,7 @@
         <v>583</v>
       </c>
       <c r="K35" t="s">
-        <v>476</v>
+        <v>492</v>
       </c>
       <c r="L35">
         <v>4.820514286595051</v>
@@ -12250,7 +12250,7 @@
         <v>585</v>
       </c>
       <c r="K36" t="s">
-        <v>488</v>
+        <v>467</v>
       </c>
       <c r="L36">
         <v>8.1474073379531564</v>
@@ -12285,7 +12285,7 @@
         <v>587</v>
       </c>
       <c r="K37" t="s">
-        <v>486</v>
+        <v>465</v>
       </c>
       <c r="L37">
         <v>9.9689850956014183</v>
@@ -12300,7 +12300,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD246E14-4019-4DCA-9F4C-D2D337415B55}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D638586-4FF1-4DAC-8B30-A3EAD68996BA}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_NGA_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_NGA_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NGA_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E37C2900-EAF7-4A14-BCCB-69275C6F413B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{763D2A22-E452-476E-BCD1-BDE8804280FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misc" sheetId="7" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2191" uniqueCount="632">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2191" uniqueCount="633">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -2024,6 +2024,9 @@
   <si>
     <t>yes</t>
   </si>
+  <si>
+    <t>e_NG10-330,e_w559542338-330,e_w669957212-330,e_w706082453-330,e_w746582404-330</t>
+  </si>
 </sst>
 </file>
 
@@ -2037,7 +2040,7 @@
     <numFmt numFmtId="168" formatCode="0.0"/>
     <numFmt numFmtId="169" formatCode="0.000"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2185,15 +2188,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="18">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2285,11 +2281,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFDBDBDB"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -2504,7 +2495,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
+  <cellStyleXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -2524,9 +2515,8 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="154">
+  <cellXfs count="153">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1"/>
@@ -2918,7 +2908,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="17"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" xfId="19"/>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2938,9 +2927,8 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="20">
+  <cellStyles count="19">
     <cellStyle name="20% - Accent3 3 2" xfId="4" xr:uid="{ABC4988B-8BA7-47D0-A9D6-448C999748B6}"/>
-    <cellStyle name="Bad" xfId="19" builtinId="27"/>
     <cellStyle name="Comma 2" xfId="9" xr:uid="{DF4BF3A2-D7A3-47EF-AC54-A7FAB7C9E75A}"/>
     <cellStyle name="Good" xfId="5" builtinId="26"/>
     <cellStyle name="Heading 2" xfId="16" builtinId="17"/>
@@ -3916,7 +3904,7 @@
       </c>
       <c r="L27" t="str">
         <f>$V$28</f>
-        <v>ELC</v>
+        <v>e_NG10-330,e_w559542338-330,e_w669957212-330,e_w706082453-330,e_w746582404-330</v>
       </c>
       <c r="P27">
         <v>0</v>
@@ -3938,7 +3926,7 @@
       </c>
       <c r="K28" t="str">
         <f>$V$28</f>
-        <v>ELC</v>
+        <v>e_NG10-330,e_w559542338-330,e_w669957212-330,e_w706082453-330,e_w746582404-330</v>
       </c>
       <c r="P28">
         <v>0</v>
@@ -3952,8 +3940,8 @@
       <c r="S28">
         <v>50</v>
       </c>
-      <c r="V28" s="147" t="s">
-        <v>19</v>
+      <c r="V28" t="s">
+        <v>632</v>
       </c>
     </row>
   </sheetData>
@@ -5499,25 +5487,25 @@
       <c r="A1" t="s">
         <v>108</v>
       </c>
-      <c r="C1" s="148" t="s">
+      <c r="C1" s="147" t="s">
         <v>109</v>
       </c>
-      <c r="D1" s="148"/>
-      <c r="E1" s="148"/>
-      <c r="F1" s="149" t="s">
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148" t="s">
         <v>110</v>
       </c>
-      <c r="G1" s="148"/>
-      <c r="H1" s="150"/>
-      <c r="I1" s="148" t="s">
+      <c r="G1" s="147"/>
+      <c r="H1" s="149"/>
+      <c r="I1" s="147" t="s">
         <v>111</v>
       </c>
-      <c r="J1" s="148"/>
-      <c r="K1" s="148"/>
-      <c r="L1" s="148"/>
-      <c r="M1" s="148"/>
-      <c r="N1" s="148"/>
-      <c r="O1" s="151" t="s">
+      <c r="J1" s="147"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="147"/>
+      <c r="M1" s="147"/>
+      <c r="N1" s="147"/>
+      <c r="O1" s="150" t="s">
         <v>112</v>
       </c>
       <c r="P1" s="27"/>
@@ -5563,7 +5551,7 @@
       <c r="N2" s="28" t="s">
         <v>146</v>
       </c>
-      <c r="O2" s="152"/>
+      <c r="O2" s="151"/>
       <c r="P2" s="27"/>
       <c r="Q2" s="27"/>
       <c r="R2" s="27"/>
@@ -5608,7 +5596,7 @@
       <c r="N3" s="28">
         <v>2050</v>
       </c>
-      <c r="O3" s="152"/>
+      <c r="O3" s="151"/>
       <c r="P3" s="27"/>
       <c r="Q3" s="27"/>
       <c r="R3" s="27"/>
@@ -5650,7 +5638,7 @@
       <c r="N4" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="O4" s="153"/>
+      <c r="O4" s="152"/>
       <c r="P4" s="27"/>
       <c r="Q4" s="27"/>
       <c r="R4" s="27"/>

--- a/VerveStacks_NGA_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_NGA_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NGA_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{763D2A22-E452-476E-BCD1-BDE8804280FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D7DD1836-AF72-48BB-9A0F-E3C61723F9CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misc" sheetId="7" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2191" uniqueCount="633">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2191" uniqueCount="632">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -1011,6 +1011,126 @@
     <t>connecting solar to buses in cluster 8</t>
   </si>
   <si>
+    <t>distr_solelc_spv_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_032</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_033</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_035</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_009</t>
   </si>
   <si>
@@ -1023,40 +1143,16 @@
     <t>connecting solar to buses in cluster 12</t>
   </si>
   <si>
-    <t>distr_solelc_spv_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_033</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_035</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
+    <t>distr_solelc_spv_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
   </si>
   <si>
     <t>distr_solelc_spv_006</t>
@@ -1065,18 +1161,6 @@
     <t>connecting solar to buses in cluster 6</t>
   </si>
   <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_034</t>
   </si>
   <si>
@@ -1101,90 +1185,6 @@
     <t>connecting solar to buses in cluster 17</t>
   </si>
   <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_032</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_036</t>
   </si>
   <si>
@@ -1227,39 +1227,78 @@
     <t>e_w746582404-330,e_w563732518-330,e_NG20-330,e_NG21-330,e_w334825256-330,e_w564429999-330</t>
   </si>
   <si>
+    <t>e_w564445207-330,e_w477596994-330,e_w565866986-330,e_NG11-330,e_w574152484-330,e_w215459565-330</t>
+  </si>
+  <si>
+    <t>e_w564429999-330,e_NG12-330</t>
+  </si>
+  <si>
+    <t>e_NG12-330,e_w565081403-330,e_w564429999-330</t>
+  </si>
+  <si>
+    <t>e_w695826179-330,e_w564410486-330,e_NG3-330,e_w556550171-330,e_w39469643-330</t>
+  </si>
+  <si>
+    <t>e_w546666333-330,e_NG17-330,e_w575706869-330</t>
+  </si>
+  <si>
+    <t>e_w565081403-330,e_w267122040-330</t>
+  </si>
+  <si>
+    <t>e_w564410486-330,e_w695826179-330,e_w39469643-330,e_w1226249784-330</t>
+  </si>
+  <si>
+    <t>e_w565486405-330,e_NG3-330,e_NG4-330,e_NG5-330,e_w565847437-330</t>
+  </si>
+  <si>
+    <t>e_w563715917-330,e_NG5-330,e_w565081403-330</t>
+  </si>
+  <si>
+    <t>e_w556550171-330,e_w39469643-330,e_w266617120-330</t>
+  </si>
+  <si>
+    <t>e_w215459565-330,e_w563715917-330,e_w548724506-330,e_w565081403-330</t>
+  </si>
+  <si>
+    <t>e_w108020974-330,e_w836122563-330,e_w559542338-330,e_NG9-330,e_w669957212-330,e_w1324578567-330,e_w565866986-330</t>
+  </si>
+  <si>
+    <t>e_NG8-330,e_w564445207-330,e_w1328602766-330</t>
+  </si>
+  <si>
+    <t>e_w565866986-330,e_NG11-330,e_w574152484-330</t>
+  </si>
+  <si>
+    <t>e_w565081403-330,e_w266617120-330,e_w266712817-330,e_w267122040-330</t>
+  </si>
+  <si>
+    <t>e_w564430566-330</t>
+  </si>
+  <si>
+    <t>e_NG2-330,e_NG1-330,e_w395182311-330,e_w563723584-330</t>
+  </si>
+  <si>
+    <t>e_w695826179-330</t>
+  </si>
+  <si>
+    <t>e_w267122040-330</t>
+  </si>
+  <si>
     <t>e_NG18-330,e_w746582404-330,e_NG17-330</t>
   </si>
   <si>
     <t>e_w564430566-330,e_w564429999-330</t>
   </si>
   <si>
-    <t>e_w564410486-330,e_w695826179-330,e_w39469643-330,e_w1226249784-330</t>
-  </si>
-  <si>
-    <t>e_w565486405-330,e_NG3-330,e_NG4-330,e_NG5-330,e_w565847437-330</t>
-  </si>
-  <si>
-    <t>e_w563715917-330,e_NG5-330,e_w565081403-330</t>
-  </si>
-  <si>
-    <t>e_w556550171-330,e_w39469643-330,e_w266617120-330</t>
-  </si>
-  <si>
-    <t>e_w695826179-330</t>
-  </si>
-  <si>
-    <t>e_w267122040-330</t>
+    <t>e_w564410486-330,e_w1226249784-330</t>
+  </si>
+  <si>
+    <t>e_NG13-330,e_NG15-330,e_w1057700475-330,e_w215459565-330,e_w671893504-330,e_w548724506-330,e_NG12-330</t>
   </si>
   <si>
     <t>e_w546666333-330,e_w565866986-330,e_NG18-330</t>
   </si>
   <si>
-    <t>e_w564430566-330</t>
-  </si>
-  <si>
-    <t>e_NG2-330,e_NG1-330,e_w395182311-330,e_w563723584-330</t>
-  </si>
-  <si>
     <t>e_NG6-330,e_NG7-330,e_NG3-330,e_w565486405-330</t>
   </si>
   <si>
@@ -1272,45 +1311,6 @@
     <t>e_w563723584-330,e_w655273140-330</t>
   </si>
   <si>
-    <t>e_w108020974-330,e_w836122563-330,e_w559542338-330,e_NG9-330,e_w669957212-330,e_w1324578567-330,e_w565866986-330</t>
-  </si>
-  <si>
-    <t>e_NG8-330,e_w564445207-330,e_w1328602766-330</t>
-  </si>
-  <si>
-    <t>e_w565866986-330,e_NG11-330,e_w574152484-330</t>
-  </si>
-  <si>
-    <t>e_w565081403-330,e_w267122040-330</t>
-  </si>
-  <si>
-    <t>e_w565081403-330,e_w266617120-330,e_w266712817-330,e_w267122040-330</t>
-  </si>
-  <si>
-    <t>e_w215459565-330,e_w563715917-330,e_w548724506-330,e_w565081403-330</t>
-  </si>
-  <si>
-    <t>e_w564410486-330,e_w1226249784-330</t>
-  </si>
-  <si>
-    <t>e_NG13-330,e_NG15-330,e_w1057700475-330,e_w215459565-330,e_w671893504-330,e_w548724506-330,e_NG12-330</t>
-  </si>
-  <si>
-    <t>e_w564445207-330,e_w477596994-330,e_w565866986-330,e_NG11-330,e_w574152484-330,e_w215459565-330</t>
-  </si>
-  <si>
-    <t>e_w564429999-330,e_NG12-330</t>
-  </si>
-  <si>
-    <t>e_NG12-330,e_w565081403-330,e_w564429999-330</t>
-  </si>
-  <si>
-    <t>e_w695826179-330,e_w564410486-330,e_NG3-330,e_w556550171-330,e_w39469643-330</t>
-  </si>
-  <si>
-    <t>e_w546666333-330,e_NG17-330,e_w575706869-330</t>
-  </si>
-  <si>
     <t>e_w1328602766-330,e_w695826179-330,e_w540463591-330,e_w481286430-330</t>
   </si>
   <si>
@@ -1323,6 +1323,36 @@
     <t>e_w266617120-330,e_w395182311-330,e_w266712817-330,e_w563723584-330</t>
   </si>
   <si>
+    <t>distr_wonelc_won_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_007</t>
   </si>
   <si>
@@ -1335,6 +1365,102 @@
     <t>connecting wind onshore to buses in cluster 12</t>
   </si>
   <si>
+    <t>distr_wonelc_won_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_008</t>
   </si>
   <si>
@@ -1353,136 +1479,34 @@
     <t>connecting wind onshore to buses in cluster 21</t>
   </si>
   <si>
-    <t>distr_wonelc_won_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_006</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 6</t>
   </si>
   <si>
-    <t>distr_wonelc_won_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
+    <t>elc_won_013</t>
+  </si>
+  <si>
+    <t>e_w564410486-330,e_w39469643-330,e_w1226249784-330,e_NG1-330,e_NG2-330</t>
+  </si>
+  <si>
+    <t>elc_won_025</t>
+  </si>
+  <si>
+    <t>e_w395182311-330,e_NG2-330,e_w266617120-330</t>
+  </si>
+  <si>
+    <t>elc_won_024</t>
+  </si>
+  <si>
+    <t>e_w266617120-330,e_w395182311-330</t>
+  </si>
+  <si>
+    <t>elc_won_016</t>
+  </si>
+  <si>
+    <t>elc_won_002</t>
   </si>
   <si>
     <t>elc_won_007</t>
@@ -1497,6 +1521,87 @@
     <t>e_w564410486-330,e_w695826179-330</t>
   </si>
   <si>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>e_w564410486-330</t>
+  </si>
+  <si>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>e_NG3-330,e_w556550171-330,e_w39469643-330,e_w266617120-330</t>
+  </si>
+  <si>
+    <t>elc_won_019</t>
+  </si>
+  <si>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>e_w548724506-330,e_w563715917-330,e_w565081403-330</t>
+  </si>
+  <si>
+    <t>elc_won_011</t>
+  </si>
+  <si>
+    <t>e_w695826179-330,e_w564410486-330</t>
+  </si>
+  <si>
+    <t>elc_won_023</t>
+  </si>
+  <si>
+    <t>e_w564410486-330,e_w1226249784-330,e_NG1-330</t>
+  </si>
+  <si>
+    <t>elc_won_020</t>
+  </si>
+  <si>
+    <t>e_w395182311-330,e_w266712817-330,e_w563723584-330</t>
+  </si>
+  <si>
+    <t>elc_won_017</t>
+  </si>
+  <si>
+    <t>e_w266712817-330,e_w563723584-330,e_w655273140-330</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>elc_won_018</t>
+  </si>
+  <si>
+    <t>e_w395182311-330,e_w563723584-330</t>
+  </si>
+  <si>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>e_NG3-330,e_w556550171-330,e_w39469643-330</t>
+  </si>
+  <si>
+    <t>elc_won_022</t>
+  </si>
+  <si>
+    <t>elc_won_027</t>
+  </si>
+  <si>
+    <t>e_w266617120-330,e_w266712817-330,e_w267122040-330</t>
+  </si>
+  <si>
+    <t>elc_won_026</t>
+  </si>
+  <si>
+    <t>e_w266712817-330,e_w267122040-330,e_w655273140-330</t>
+  </si>
+  <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>elc_won_001</t>
+  </si>
+  <si>
     <t>elc_won_008</t>
   </si>
   <si>
@@ -1506,171 +1611,66 @@
     <t>elc_won_014</t>
   </si>
   <si>
-    <t>e_w564410486-330</t>
-  </si>
-  <si>
     <t>elc_won_021</t>
   </si>
   <si>
     <t>e_w266617120-330,e_w266712817-330</t>
   </si>
   <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>e_NG3-330,e_w556550171-330,e_w39469643-330</t>
-  </si>
-  <si>
-    <t>elc_won_022</t>
-  </si>
-  <si>
-    <t>elc_won_027</t>
-  </si>
-  <si>
-    <t>e_w266617120-330,e_w266712817-330,e_w267122040-330</t>
-  </si>
-  <si>
-    <t>elc_won_026</t>
-  </si>
-  <si>
-    <t>e_w266712817-330,e_w267122040-330,e_w655273140-330</t>
-  </si>
-  <si>
     <t>elc_won_006</t>
   </si>
   <si>
     <t>e_w695826179-330,e_w1328602766-330,e_w540463591-330</t>
   </si>
   <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>elc_won_010</t>
-  </si>
-  <si>
-    <t>e_NG3-330,e_w556550171-330,e_w39469643-330,e_w266617120-330</t>
-  </si>
-  <si>
-    <t>elc_won_019</t>
-  </si>
-  <si>
-    <t>elc_won_011</t>
-  </si>
-  <si>
-    <t>e_w695826179-330,e_w564410486-330</t>
-  </si>
-  <si>
-    <t>elc_won_023</t>
-  </si>
-  <si>
-    <t>e_w564410486-330,e_w1226249784-330,e_NG1-330</t>
-  </si>
-  <si>
-    <t>elc_won_020</t>
-  </si>
-  <si>
-    <t>e_w395182311-330,e_w266712817-330,e_w563723584-330</t>
-  </si>
-  <si>
-    <t>elc_won_017</t>
-  </si>
-  <si>
-    <t>e_w266712817-330,e_w563723584-330,e_w655273140-330</t>
-  </si>
-  <si>
-    <t>elc_won_003</t>
-  </si>
-  <si>
-    <t>elc_won_005</t>
-  </si>
-  <si>
-    <t>e_w548724506-330,e_w563715917-330,e_w565081403-330</t>
-  </si>
-  <si>
-    <t>elc_won_018</t>
-  </si>
-  <si>
-    <t>e_w395182311-330,e_w563723584-330</t>
-  </si>
-  <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>elc_won_013</t>
-  </si>
-  <si>
-    <t>e_w564410486-330,e_w39469643-330,e_w1226249784-330,e_NG1-330,e_NG2-330</t>
-  </si>
-  <si>
-    <t>elc_won_025</t>
-  </si>
-  <si>
-    <t>e_w395182311-330,e_NG2-330,e_w266617120-330</t>
-  </si>
-  <si>
-    <t>elc_won_024</t>
-  </si>
-  <si>
-    <t>e_w266617120-330,e_w395182311-330</t>
-  </si>
-  <si>
-    <t>elc_won_016</t>
-  </si>
-  <si>
-    <t>elc_won_002</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_008</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 8</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_010</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 10</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_005</t>
   </si>
   <si>
@@ -1686,48 +1686,48 @@
     <t>elc_wof_008</t>
   </si>
   <si>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
+    <t>e_NG18-330</t>
+  </si>
+  <si>
+    <t>elc_wof_004</t>
+  </si>
+  <si>
+    <t>e_NG18-330,e_w559542338-330</t>
+  </si>
+  <si>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>e_w746582404-330,e_w564430566-330</t>
+  </si>
+  <si>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>e_w746582404-330</t>
+  </si>
+  <si>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>e_w706082453-330,e_w108020974-330,e_w559542338-330,e_w565866986-330,e_w546666333-330</t>
+  </si>
+  <si>
+    <t>elc_wof_001</t>
+  </si>
+  <si>
+    <t>e_NG9-330,e_w1324578567-330,e_w565866986-330</t>
+  </si>
+  <si>
     <t>elc_wof_010</t>
   </si>
   <si>
     <t>e_NG18-330,e_w746582404-330</t>
   </si>
   <si>
-    <t>elc_wof_001</t>
-  </si>
-  <si>
-    <t>e_NG9-330,e_w1324578567-330,e_w565866986-330</t>
-  </si>
-  <si>
-    <t>elc_wof_002</t>
-  </si>
-  <si>
-    <t>e_w706082453-330,e_w108020974-330,e_w559542338-330,e_w565866986-330,e_w546666333-330</t>
-  </si>
-  <si>
-    <t>elc_wof_003</t>
-  </si>
-  <si>
-    <t>e_NG18-330</t>
-  </si>
-  <si>
-    <t>elc_wof_004</t>
-  </si>
-  <si>
-    <t>e_NG18-330,e_w559542338-330</t>
-  </si>
-  <si>
-    <t>elc_wof_007</t>
-  </si>
-  <si>
-    <t>e_w746582404-330,e_w564430566-330</t>
-  </si>
-  <si>
-    <t>elc_wof_009</t>
-  </si>
-  <si>
-    <t>e_w746582404-330</t>
-  </si>
-  <si>
     <t>elc_wof_005</t>
   </si>
   <si>
@@ -2023,9 +2023,6 @@
   </si>
   <si>
     <t>yes</t>
-  </si>
-  <si>
-    <t>e_NG10-330,e_w559542338-330,e_w669957212-330,e_w706082453-330,e_w746582404-330</t>
   </si>
 </sst>
 </file>
@@ -2040,7 +2037,7 @@
     <numFmt numFmtId="168" formatCode="0.0"/>
     <numFmt numFmtId="169" formatCode="0.000"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2188,8 +2185,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="17">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2281,6 +2285,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFDBDBDB"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -2495,7 +2504,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="19">
+  <cellStyleXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -2515,8 +2524,9 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="153">
+  <cellXfs count="154">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1"/>
@@ -2908,6 +2918,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="17"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" xfId="19"/>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2927,8 +2938,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="19">
+  <cellStyles count="20">
     <cellStyle name="20% - Accent3 3 2" xfId="4" xr:uid="{ABC4988B-8BA7-47D0-A9D6-448C999748B6}"/>
+    <cellStyle name="Bad" xfId="19" builtinId="27"/>
     <cellStyle name="Comma 2" xfId="9" xr:uid="{DF4BF3A2-D7A3-47EF-AC54-A7FAB7C9E75A}"/>
     <cellStyle name="Good" xfId="5" builtinId="26"/>
     <cellStyle name="Heading 2" xfId="16" builtinId="17"/>
@@ -3904,7 +3916,7 @@
       </c>
       <c r="L27" t="str">
         <f>$V$28</f>
-        <v>e_NG10-330,e_w559542338-330,e_w669957212-330,e_w706082453-330,e_w746582404-330</v>
+        <v>ELC</v>
       </c>
       <c r="P27">
         <v>0</v>
@@ -3926,7 +3938,7 @@
       </c>
       <c r="K28" t="str">
         <f>$V$28</f>
-        <v>e_NG10-330,e_w559542338-330,e_w669957212-330,e_w706082453-330,e_w746582404-330</v>
+        <v>ELC</v>
       </c>
       <c r="P28">
         <v>0</v>
@@ -3940,8 +3952,8 @@
       <c r="S28">
         <v>50</v>
       </c>
-      <c r="V28" t="s">
-        <v>632</v>
+      <c r="V28" s="147" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -5487,25 +5499,25 @@
       <c r="A1" t="s">
         <v>108</v>
       </c>
-      <c r="C1" s="147" t="s">
+      <c r="C1" s="148" t="s">
         <v>109</v>
       </c>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148" t="s">
+      <c r="D1" s="148"/>
+      <c r="E1" s="148"/>
+      <c r="F1" s="149" t="s">
         <v>110</v>
       </c>
-      <c r="G1" s="147"/>
-      <c r="H1" s="149"/>
-      <c r="I1" s="147" t="s">
+      <c r="G1" s="148"/>
+      <c r="H1" s="150"/>
+      <c r="I1" s="148" t="s">
         <v>111</v>
       </c>
-      <c r="J1" s="147"/>
-      <c r="K1" s="147"/>
-      <c r="L1" s="147"/>
-      <c r="M1" s="147"/>
-      <c r="N1" s="147"/>
-      <c r="O1" s="150" t="s">
+      <c r="J1" s="148"/>
+      <c r="K1" s="148"/>
+      <c r="L1" s="148"/>
+      <c r="M1" s="148"/>
+      <c r="N1" s="148"/>
+      <c r="O1" s="151" t="s">
         <v>112</v>
       </c>
       <c r="P1" s="27"/>
@@ -5551,7 +5563,7 @@
       <c r="N2" s="28" t="s">
         <v>146</v>
       </c>
-      <c r="O2" s="151"/>
+      <c r="O2" s="152"/>
       <c r="P2" s="27"/>
       <c r="Q2" s="27"/>
       <c r="R2" s="27"/>
@@ -5596,7 +5608,7 @@
       <c r="N3" s="28">
         <v>2050</v>
       </c>
-      <c r="O3" s="151"/>
+      <c r="O3" s="152"/>
       <c r="P3" s="27"/>
       <c r="Q3" s="27"/>
       <c r="R3" s="27"/>
@@ -5638,7 +5650,7 @@
       <c r="N4" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="O4" s="152"/>
+      <c r="O4" s="153"/>
       <c r="P4" s="27"/>
       <c r="Q4" s="27"/>
       <c r="R4" s="27"/>
@@ -6743,7 +6755,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EA44A11-E72C-437B-BF30-04DE123DD0B9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6ABACE4-C695-4B11-9F5A-6500E6F1FF35}">
   <dimension ref="B9:BD46"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7023,10 +7035,10 @@
         <v>453</v>
       </c>
       <c r="AO11">
-        <v>0.99740664776461363</v>
+        <v>0.99207403494667001</v>
       </c>
       <c r="AP11">
-        <v>47.544790982083583</v>
+        <v>145.30935931104892</v>
       </c>
       <c r="AR11" t="s">
         <v>287</v>
@@ -7056,7 +7068,7 @@
         <v>518</v>
       </c>
       <c r="BB11" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="BC11">
         <v>0.99337755486839363</v>
@@ -7169,10 +7181,10 @@
         <v>455</v>
       </c>
       <c r="AO12">
-        <v>0.9913636988912532</v>
+        <v>0.99637613831578808</v>
       </c>
       <c r="AP12">
-        <v>158.33218699369189</v>
+        <v>66.437464210551497</v>
       </c>
       <c r="AR12" t="s">
         <v>287</v>
@@ -7205,10 +7217,10 @@
         <v>520</v>
       </c>
       <c r="BC12">
-        <v>0.99371472191320109</v>
+        <v>0.99174031680019514</v>
       </c>
       <c r="BD12">
-        <v>115.23009825798009</v>
+        <v>151.42752532975524</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -7273,16 +7285,16 @@
         <v>294</v>
       </c>
       <c r="Y13" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="Z13" t="s">
         <v>366</v>
       </c>
       <c r="AA13">
-        <v>0.99884992726149324</v>
+        <v>0.99732710525923551</v>
       </c>
       <c r="AB13">
-        <v>21.084666872623977</v>
+        <v>49.003070247349498</v>
       </c>
       <c r="AD13" t="s">
         <v>287</v>
@@ -7315,10 +7327,10 @@
         <v>457</v>
       </c>
       <c r="AO13">
-        <v>0.99795762496221851</v>
+        <v>0.99501745221162918</v>
       </c>
       <c r="AP13">
-        <v>37.443542359327118</v>
+        <v>91.346709453464783</v>
       </c>
       <c r="AR13" t="s">
         <v>287</v>
@@ -7351,10 +7363,10 @@
         <v>522</v>
       </c>
       <c r="BC13">
-        <v>0.99794494286432878</v>
+        <v>0.99246115999793105</v>
       </c>
       <c r="BD13">
-        <v>37.67604748730637</v>
+        <v>138.21206670459694</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -7419,16 +7431,16 @@
         <v>296</v>
       </c>
       <c r="Y14" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z14" t="s">
         <v>367</v>
       </c>
       <c r="AA14">
-        <v>0.99882431199806432</v>
+        <v>0.99601914721828588</v>
       </c>
       <c r="AB14">
-        <v>21.554280035486567</v>
+        <v>72.982300998092228</v>
       </c>
       <c r="AD14" t="s">
         <v>287</v>
@@ -7458,13 +7470,13 @@
         <v>458</v>
       </c>
       <c r="AN14" t="s">
-        <v>459</v>
+        <v>393</v>
       </c>
       <c r="AO14">
-        <v>0.99582871194680656</v>
+        <v>0.99698529931119073</v>
       </c>
       <c r="AP14">
-        <v>76.473614308545862</v>
+        <v>55.269512628170503</v>
       </c>
       <c r="AR14" t="s">
         <v>287</v>
@@ -7497,10 +7509,10 @@
         <v>524</v>
       </c>
       <c r="BC14">
-        <v>0.9962053430710629</v>
+        <v>0.99268778174342398</v>
       </c>
       <c r="BD14">
-        <v>69.568710363846861</v>
+        <v>134.05733470389279</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7565,16 +7577,16 @@
         <v>298</v>
       </c>
       <c r="Y15" t="s">
-        <v>280</v>
+        <v>263</v>
       </c>
       <c r="Z15" t="s">
         <v>368</v>
       </c>
       <c r="AA15">
-        <v>0.993124380119488</v>
+        <v>0.99403967905190227</v>
       </c>
       <c r="AB15">
-        <v>126.05303114271953</v>
+        <v>109.27255071512499</v>
       </c>
       <c r="AD15" t="s">
         <v>287</v>
@@ -7601,16 +7613,16 @@
         <v>406</v>
       </c>
       <c r="AM15" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AN15" t="s">
-        <v>461</v>
+        <v>384</v>
       </c>
       <c r="AO15">
-        <v>0.99555964959117016</v>
+        <v>0.99537626424805781</v>
       </c>
       <c r="AP15">
-        <v>81.406424161880452</v>
+        <v>84.768488785605911</v>
       </c>
       <c r="AR15" t="s">
         <v>287</v>
@@ -7643,10 +7655,10 @@
         <v>526</v>
       </c>
       <c r="BC15">
-        <v>0.99174031680019514</v>
+        <v>0.99755731205629283</v>
       </c>
       <c r="BD15">
-        <v>151.42752532975524</v>
+        <v>44.782612301298634</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -7711,16 +7723,16 @@
         <v>300</v>
       </c>
       <c r="Y16" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="Z16" t="s">
         <v>369</v>
       </c>
       <c r="AA16">
-        <v>0.99769438809486533</v>
+        <v>0.99339354842512728</v>
       </c>
       <c r="AB16">
-        <v>42.269551594135834</v>
+        <v>121.1182788726671</v>
       </c>
       <c r="AD16" t="s">
         <v>287</v>
@@ -7747,16 +7759,16 @@
         <v>408</v>
       </c>
       <c r="AM16" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="AN16" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="AO16">
-        <v>0.9964390810242717</v>
+        <v>0.99740664776461363</v>
       </c>
       <c r="AP16">
-        <v>65.283514555019096</v>
+        <v>47.544790982083583</v>
       </c>
       <c r="AR16" t="s">
         <v>287</v>
@@ -7789,10 +7801,10 @@
         <v>528</v>
       </c>
       <c r="BC16">
-        <v>0.99246115999793105</v>
+        <v>0.9962053430710629</v>
       </c>
       <c r="BD16">
-        <v>138.21206670459694</v>
+        <v>69.568710363846861</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -7857,16 +7869,16 @@
         <v>302</v>
       </c>
       <c r="Y17" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="Z17" t="s">
         <v>370</v>
       </c>
       <c r="AA17">
-        <v>0.99489048613238573</v>
+        <v>0.99805028151894915</v>
       </c>
       <c r="AB17">
-        <v>93.674420906261602</v>
+        <v>35.744838819266263</v>
       </c>
       <c r="AD17" t="s">
         <v>287</v>
@@ -7893,16 +7905,16 @@
         <v>410</v>
       </c>
       <c r="AM17" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="AN17" t="s">
-        <v>378</v>
+        <v>463</v>
       </c>
       <c r="AO17">
-        <v>0.99592873360628342</v>
+        <v>0.9913636988912532</v>
       </c>
       <c r="AP17">
-        <v>74.639883884803922</v>
+        <v>158.33218699369189</v>
       </c>
       <c r="AR17" t="s">
         <v>287</v>
@@ -7935,10 +7947,10 @@
         <v>530</v>
       </c>
       <c r="BC17">
-        <v>0.99268778174342398</v>
+        <v>0.99794494286432878</v>
       </c>
       <c r="BD17">
-        <v>134.05733470389279</v>
+        <v>37.67604748730637</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8003,16 +8015,16 @@
         <v>304</v>
       </c>
       <c r="Y18" t="s">
-        <v>282</v>
+        <v>268</v>
       </c>
       <c r="Z18" t="s">
         <v>371</v>
       </c>
       <c r="AA18">
-        <v>0.99642867204968677</v>
+        <v>0.98395338050941106</v>
       </c>
       <c r="AB18">
-        <v>65.474345755743457</v>
+        <v>294.18802399413073</v>
       </c>
       <c r="AD18" t="s">
         <v>287</v>
@@ -8039,16 +8051,16 @@
         <v>412</v>
       </c>
       <c r="AM18" t="s">
+        <v>464</v>
+      </c>
+      <c r="AN18" t="s">
         <v>465</v>
       </c>
-      <c r="AN18" t="s">
-        <v>466</v>
-      </c>
       <c r="AO18">
-        <v>0.99534990870245532</v>
+        <v>0.9933445384762607</v>
       </c>
       <c r="AP18">
-        <v>85.251673788320105</v>
+        <v>122.01679460188713</v>
       </c>
       <c r="AR18" t="s">
         <v>287</v>
@@ -8081,10 +8093,10 @@
         <v>532</v>
       </c>
       <c r="BC18">
-        <v>0.99755731205629283</v>
+        <v>0.99371472191320109</v>
       </c>
       <c r="BD18">
-        <v>44.782612301298634</v>
+        <v>115.23009825798009</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8149,16 +8161,16 @@
         <v>306</v>
       </c>
       <c r="Y19" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="Z19" t="s">
         <v>372</v>
       </c>
       <c r="AA19">
-        <v>0.99514004796050048</v>
+        <v>0.993124380119488</v>
       </c>
       <c r="AB19">
-        <v>89.099120724157018</v>
+        <v>126.05303114271953</v>
       </c>
       <c r="AD19" t="s">
         <v>287</v>
@@ -8185,16 +8197,16 @@
         <v>414</v>
       </c>
       <c r="AM19" t="s">
+        <v>466</v>
+      </c>
+      <c r="AN19" t="s">
         <v>467</v>
       </c>
-      <c r="AN19" t="s">
-        <v>468</v>
-      </c>
       <c r="AO19">
-        <v>0.99283555585293171</v>
+        <v>0.9938298282896767</v>
       </c>
       <c r="AP19">
-        <v>131.34814269625272</v>
+        <v>113.11981468926018</v>
       </c>
       <c r="AR19" t="s">
         <v>287</v>
@@ -8224,7 +8236,7 @@
         <v>533</v>
       </c>
       <c r="BB19" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="BC19">
         <v>0.9888409065104441</v>
@@ -8295,16 +8307,16 @@
         <v>308</v>
       </c>
       <c r="Y20" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="Z20" t="s">
         <v>373</v>
       </c>
       <c r="AA20">
-        <v>0.99589467345586935</v>
+        <v>0.99769438809486533</v>
       </c>
       <c r="AB20">
-        <v>75.264319975727958</v>
+        <v>42.269551594135834</v>
       </c>
       <c r="AD20" t="s">
         <v>287</v>
@@ -8331,16 +8343,16 @@
         <v>416</v>
       </c>
       <c r="AM20" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AN20" t="s">
-        <v>470</v>
+        <v>393</v>
       </c>
       <c r="AO20">
-        <v>0.99429686126958916</v>
+        <v>0.99008544123370779</v>
       </c>
       <c r="AP20">
-        <v>104.55754339086491</v>
+        <v>181.76691071535706</v>
       </c>
       <c r="AR20" t="s">
         <v>287</v>
@@ -8370,7 +8382,7 @@
         <v>534</v>
       </c>
       <c r="BB20" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="BC20">
         <v>0.99132158137897763</v>
@@ -8441,16 +8453,16 @@
         <v>310</v>
       </c>
       <c r="Y21" t="s">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="Z21" t="s">
         <v>374</v>
       </c>
       <c r="AA21">
-        <v>0.99744993905722468</v>
+        <v>0.99489048613238573</v>
       </c>
       <c r="AB21">
-        <v>46.751117284213812</v>
+        <v>93.674420906261602</v>
       </c>
       <c r="AD21" t="s">
         <v>287</v>
@@ -8477,16 +8489,16 @@
         <v>418</v>
       </c>
       <c r="AM21" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="AN21" t="s">
-        <v>459</v>
+        <v>470</v>
       </c>
       <c r="AO21">
-        <v>0.9933445384762607</v>
+        <v>0.99562035686170025</v>
       </c>
       <c r="AP21">
-        <v>122.01679460188713</v>
+        <v>80.293457535494625</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8551,16 +8563,16 @@
         <v>312</v>
       </c>
       <c r="Y22" t="s">
-        <v>256</v>
+        <v>282</v>
       </c>
       <c r="Z22" t="s">
         <v>375</v>
       </c>
       <c r="AA22">
-        <v>0.99605704806429607</v>
+        <v>0.99642867204968677</v>
       </c>
       <c r="AB22">
-        <v>72.28745215457208</v>
+        <v>65.474345755743457</v>
       </c>
       <c r="AD22" t="s">
         <v>287</v>
@@ -8587,16 +8599,16 @@
         <v>420</v>
       </c>
       <c r="AM22" t="s">
+        <v>471</v>
+      </c>
+      <c r="AN22" t="s">
         <v>472</v>
       </c>
-      <c r="AN22" t="s">
-        <v>473</v>
-      </c>
       <c r="AO22">
-        <v>0.9938298282896767</v>
+        <v>0.99178855761800622</v>
       </c>
       <c r="AP22">
-        <v>113.11981468926018</v>
+        <v>150.54311033655213</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -8661,16 +8673,16 @@
         <v>314</v>
       </c>
       <c r="Y23" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="Z23" t="s">
         <v>376</v>
       </c>
       <c r="AA23">
-        <v>0.99167914755584141</v>
+        <v>0.99655017109874156</v>
       </c>
       <c r="AB23">
-        <v>152.54896147624135</v>
+        <v>63.246863189739024</v>
       </c>
       <c r="AD23" t="s">
         <v>287</v>
@@ -8697,16 +8709,16 @@
         <v>422</v>
       </c>
       <c r="AM23" t="s">
+        <v>473</v>
+      </c>
+      <c r="AN23" t="s">
         <v>474</v>
       </c>
-      <c r="AN23" t="s">
-        <v>380</v>
-      </c>
       <c r="AO23">
-        <v>0.99008544123370779</v>
+        <v>0.99296304108660982</v>
       </c>
       <c r="AP23">
-        <v>181.76691071535706</v>
+        <v>129.01091341215286</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -8771,16 +8783,16 @@
         <v>316</v>
       </c>
       <c r="Y24" t="s">
-        <v>283</v>
+        <v>253</v>
       </c>
       <c r="Z24" t="s">
         <v>377</v>
       </c>
       <c r="AA24">
-        <v>0.9963457067026108</v>
+        <v>0.99802162515875081</v>
       </c>
       <c r="AB24">
-        <v>66.99537711880258</v>
+        <v>36.270205422902137</v>
       </c>
       <c r="AD24" t="s">
         <v>287</v>
@@ -8813,10 +8825,10 @@
         <v>476</v>
       </c>
       <c r="AO24">
-        <v>0.99178855761800622</v>
+        <v>0.99152317643653909</v>
       </c>
       <c r="AP24">
-        <v>150.54311033655213</v>
+        <v>155.40843199678267</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -8881,16 +8893,16 @@
         <v>318</v>
       </c>
       <c r="Y25" t="s">
-        <v>277</v>
+        <v>252</v>
       </c>
       <c r="Z25" t="s">
         <v>378</v>
       </c>
       <c r="AA25">
-        <v>0.99644641159652714</v>
+        <v>0.99631349511992195</v>
       </c>
       <c r="AB25">
-        <v>65.149120730335611</v>
+        <v>67.585922801431252</v>
       </c>
       <c r="AD25" t="s">
         <v>287</v>
@@ -8923,10 +8935,10 @@
         <v>478</v>
       </c>
       <c r="AO25">
-        <v>0.99296304108660982</v>
+        <v>0.99475386493829931</v>
       </c>
       <c r="AP25">
-        <v>129.01091341215286</v>
+        <v>96.179142797845941</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -8991,16 +9003,16 @@
         <v>320</v>
       </c>
       <c r="Y26" t="s">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="Z26" t="s">
         <v>379</v>
       </c>
       <c r="AA26">
-        <v>0.99436579068013853</v>
+        <v>0.99832768028365393</v>
       </c>
       <c r="AB26">
-        <v>103.29383753079337</v>
+        <v>30.659194799678048</v>
       </c>
       <c r="AD26" t="s">
         <v>287</v>
@@ -9030,13 +9042,13 @@
         <v>479</v>
       </c>
       <c r="AN26" t="s">
-        <v>480</v>
+        <v>384</v>
       </c>
       <c r="AO26">
-        <v>0.99152317643653909</v>
+        <v>0.99671794291781168</v>
       </c>
       <c r="AP26">
-        <v>155.40843199678267</v>
+        <v>60.171046506785672</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -9101,16 +9113,16 @@
         <v>322</v>
       </c>
       <c r="Y27" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Z27" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="AA27">
-        <v>0.99262439568706373</v>
+        <v>0.99057172008573791</v>
       </c>
       <c r="AB27">
-        <v>135.21941240383219</v>
+        <v>172.85179842813815</v>
       </c>
       <c r="AD27" t="s">
         <v>287</v>
@@ -9137,16 +9149,16 @@
         <v>430</v>
       </c>
       <c r="AM27" t="s">
+        <v>480</v>
+      </c>
+      <c r="AN27" t="s">
         <v>481</v>
       </c>
-      <c r="AN27" t="s">
-        <v>482</v>
-      </c>
       <c r="AO27">
-        <v>0.99475386493829931</v>
+        <v>0.98839759805196303</v>
       </c>
       <c r="AP27">
-        <v>96.179142797845941</v>
+        <v>212.71070238067816</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -9211,16 +9223,16 @@
         <v>324</v>
       </c>
       <c r="Y28" t="s">
-        <v>253</v>
+        <v>273</v>
       </c>
       <c r="Z28" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AA28">
-        <v>0.99802162515875081</v>
+        <v>0.99095032933880767</v>
       </c>
       <c r="AB28">
-        <v>36.270205422902137</v>
+        <v>165.91062878852651</v>
       </c>
       <c r="AD28" t="s">
         <v>287</v>
@@ -9247,16 +9259,16 @@
         <v>432</v>
       </c>
       <c r="AM28" t="s">
+        <v>482</v>
+      </c>
+      <c r="AN28" t="s">
         <v>483</v>
       </c>
-      <c r="AN28" t="s">
-        <v>373</v>
-      </c>
       <c r="AO28">
-        <v>0.99671794291781168</v>
+        <v>0.9964390810242717</v>
       </c>
       <c r="AP28">
-        <v>60.171046506785672</v>
+        <v>65.283514555019096</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9321,16 +9333,16 @@
         <v>326</v>
       </c>
       <c r="Y29" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="Z29" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AA29">
-        <v>0.99631349511992195</v>
+        <v>0.99605704806429607</v>
       </c>
       <c r="AB29">
-        <v>67.585922801431252</v>
+        <v>72.28745215457208</v>
       </c>
       <c r="AD29" t="s">
         <v>287</v>
@@ -9360,13 +9372,13 @@
         <v>484</v>
       </c>
       <c r="AN29" t="s">
-        <v>485</v>
+        <v>391</v>
       </c>
       <c r="AO29">
-        <v>0.99562035686170025</v>
+        <v>0.99592873360628342</v>
       </c>
       <c r="AP29">
-        <v>80.293457535494625</v>
+        <v>74.639883884803922</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9431,16 +9443,16 @@
         <v>328</v>
       </c>
       <c r="Y30" t="s">
-        <v>254</v>
+        <v>278</v>
       </c>
       <c r="Z30" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AA30">
-        <v>0.99832768028365393</v>
+        <v>0.99167914755584141</v>
       </c>
       <c r="AB30">
-        <v>30.659194799678048</v>
+        <v>152.54896147624135</v>
       </c>
       <c r="AD30" t="s">
         <v>287</v>
@@ -9467,16 +9479,16 @@
         <v>436</v>
       </c>
       <c r="AM30" t="s">
+        <v>485</v>
+      </c>
+      <c r="AN30" t="s">
         <v>486</v>
       </c>
-      <c r="AN30" t="s">
-        <v>487</v>
-      </c>
       <c r="AO30">
-        <v>0.98839759805196303</v>
+        <v>0.99534990870245532</v>
       </c>
       <c r="AP30">
-        <v>212.71070238067816</v>
+        <v>85.251673788320105</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -9541,16 +9553,16 @@
         <v>330</v>
       </c>
       <c r="Y31" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="Z31" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AA31">
-        <v>0.99057172008573791</v>
+        <v>0.99514004796050048</v>
       </c>
       <c r="AB31">
-        <v>172.85179842813815</v>
+        <v>89.099120724157018</v>
       </c>
       <c r="AD31" t="s">
         <v>287</v>
@@ -9577,16 +9589,16 @@
         <v>438</v>
       </c>
       <c r="AM31" t="s">
+        <v>487</v>
+      </c>
+      <c r="AN31" t="s">
         <v>488</v>
       </c>
-      <c r="AN31" t="s">
-        <v>396</v>
-      </c>
       <c r="AO31">
-        <v>0.99354454384798807</v>
+        <v>0.99283555585293171</v>
       </c>
       <c r="AP31">
-        <v>118.35002945355123</v>
+        <v>131.34814269625272</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -9651,16 +9663,16 @@
         <v>332</v>
       </c>
       <c r="Y32" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="Z32" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AA32">
-        <v>0.99095032933880767</v>
+        <v>0.99589467345586935</v>
       </c>
       <c r="AB32">
-        <v>165.91062878852651</v>
+        <v>75.264319975727958</v>
       </c>
       <c r="AD32" t="s">
         <v>287</v>
@@ -9690,13 +9702,13 @@
         <v>489</v>
       </c>
       <c r="AN32" t="s">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="AO32">
-        <v>0.99069345154297106</v>
+        <v>0.99354454384798807</v>
       </c>
       <c r="AP32">
-        <v>170.62005504553079</v>
+        <v>118.35002945355123</v>
       </c>
     </row>
     <row r="33" spans="2:42">
@@ -9761,16 +9773,16 @@
         <v>334</v>
       </c>
       <c r="Y33" t="s">
-        <v>272</v>
+        <v>258</v>
       </c>
       <c r="Z33" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AA33">
-        <v>0.99655017109874156</v>
+        <v>0.99884992726149324</v>
       </c>
       <c r="AB33">
-        <v>63.246863189739024</v>
+        <v>21.084666872623977</v>
       </c>
       <c r="AD33" t="s">
         <v>287</v>
@@ -9800,13 +9812,13 @@
         <v>490</v>
       </c>
       <c r="AN33" t="s">
-        <v>491</v>
+        <v>380</v>
       </c>
       <c r="AO33">
-        <v>0.99207403494667001</v>
+        <v>0.99069345154297106</v>
       </c>
       <c r="AP33">
-        <v>145.30935931104892</v>
+        <v>170.62005504553079</v>
       </c>
     </row>
     <row r="34" spans="2:42">
@@ -9871,16 +9883,16 @@
         <v>336</v>
       </c>
       <c r="Y34" t="s">
-        <v>279</v>
+        <v>261</v>
       </c>
       <c r="Z34" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AA34">
-        <v>0.99133276722560904</v>
+        <v>0.99882431199806432</v>
       </c>
       <c r="AB34">
-        <v>158.89926753050145</v>
+        <v>21.554280035486567</v>
       </c>
       <c r="AD34" t="s">
         <v>287</v>
@@ -9907,16 +9919,16 @@
         <v>444</v>
       </c>
       <c r="AM34" t="s">
+        <v>491</v>
+      </c>
+      <c r="AN34" t="s">
         <v>492</v>
       </c>
-      <c r="AN34" t="s">
-        <v>493</v>
-      </c>
       <c r="AO34">
-        <v>0.99637613831578808</v>
+        <v>0.99795762496221851</v>
       </c>
       <c r="AP34">
-        <v>66.437464210551497</v>
+        <v>37.443542359327118</v>
       </c>
     </row>
     <row r="35" spans="2:42">
@@ -9981,16 +9993,16 @@
         <v>338</v>
       </c>
       <c r="Y35" t="s">
-        <v>260</v>
+        <v>279</v>
       </c>
       <c r="Z35" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AA35">
-        <v>0.99728758220200375</v>
+        <v>0.99133276722560904</v>
       </c>
       <c r="AB35">
-        <v>49.727659629930621</v>
+        <v>158.89926753050145</v>
       </c>
       <c r="AD35" t="s">
         <v>287</v>
@@ -10017,16 +10029,16 @@
         <v>446</v>
       </c>
       <c r="AM35" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AN35" t="s">
-        <v>495</v>
+        <v>465</v>
       </c>
       <c r="AO35">
-        <v>0.99501745221162918</v>
+        <v>0.99582871194680656</v>
       </c>
       <c r="AP35">
-        <v>91.346709453464783</v>
+        <v>76.473614308545862</v>
       </c>
     </row>
     <row r="36" spans="2:42">
@@ -10091,16 +10103,16 @@
         <v>340</v>
       </c>
       <c r="Y36" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="Z36" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AA36">
-        <v>0.99732710525923551</v>
+        <v>0.99728758220200375</v>
       </c>
       <c r="AB36">
-        <v>49.003070247349498</v>
+        <v>49.727659629930621</v>
       </c>
       <c r="AD36" t="s">
         <v>287</v>
@@ -10127,16 +10139,16 @@
         <v>448</v>
       </c>
       <c r="AM36" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="AN36" t="s">
-        <v>380</v>
+        <v>495</v>
       </c>
       <c r="AO36">
-        <v>0.99698529931119073</v>
+        <v>0.99555964959117016</v>
       </c>
       <c r="AP36">
-        <v>55.269512628170503</v>
+        <v>81.406424161880452</v>
       </c>
     </row>
     <row r="37" spans="2:42">
@@ -10201,16 +10213,16 @@
         <v>342</v>
       </c>
       <c r="Y37" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="Z37" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AA37">
-        <v>0.99601914721828588</v>
+        <v>0.99744993905722468</v>
       </c>
       <c r="AB37">
-        <v>72.982300998092228</v>
+        <v>46.751117284213812</v>
       </c>
       <c r="AD37" t="s">
         <v>287</v>
@@ -10237,16 +10249,16 @@
         <v>450</v>
       </c>
       <c r="AM37" t="s">
+        <v>496</v>
+      </c>
+      <c r="AN37" t="s">
         <v>497</v>
       </c>
-      <c r="AN37" t="s">
-        <v>373</v>
-      </c>
       <c r="AO37">
-        <v>0.99537626424805781</v>
+        <v>0.99429686126958916</v>
       </c>
       <c r="AP37">
-        <v>84.768488785605911</v>
+        <v>104.55754339086491</v>
       </c>
     </row>
     <row r="38" spans="2:42">
@@ -10311,16 +10323,16 @@
         <v>344</v>
       </c>
       <c r="Y38" t="s">
-        <v>263</v>
+        <v>283</v>
       </c>
       <c r="Z38" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AA38">
-        <v>0.99403967905190227</v>
+        <v>0.9963457067026108</v>
       </c>
       <c r="AB38">
-        <v>109.27255071512499</v>
+        <v>66.99537711880258</v>
       </c>
     </row>
     <row r="39" spans="2:42">
@@ -10385,16 +10397,16 @@
         <v>346</v>
       </c>
       <c r="Y39" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="Z39" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AA39">
-        <v>0.99339354842512728</v>
+        <v>0.99644641159652714</v>
       </c>
       <c r="AB39">
-        <v>121.1182788726671</v>
+        <v>65.149120730335611</v>
       </c>
     </row>
     <row r="40" spans="2:42">
@@ -10459,16 +10471,16 @@
         <v>348</v>
       </c>
       <c r="Y40" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="Z40" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AA40">
-        <v>0.99805028151894915</v>
+        <v>0.99436579068013853</v>
       </c>
       <c r="AB40">
-        <v>35.744838819266263</v>
+        <v>103.29383753079337</v>
       </c>
     </row>
     <row r="41" spans="2:42">
@@ -10533,16 +10545,16 @@
         <v>350</v>
       </c>
       <c r="Y41" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="Z41" t="s">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="AA41">
-        <v>0.98395338050941106</v>
+        <v>0.99262439568706373</v>
       </c>
       <c r="AB41">
-        <v>294.18802399413073</v>
+        <v>135.21941240383219</v>
       </c>
     </row>
     <row r="42" spans="2:42">
@@ -10906,7 +10918,7 @@
         <v>264</v>
       </c>
       <c r="Z46" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="AA46">
         <v>0.98416398409272543</v>
@@ -10921,7 +10933,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C649A00-0D04-454E-A807-475C15654135}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE9FCA86-FCC6-4D58-868C-61ADA2549298}">
   <dimension ref="B9:Z37"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -11033,7 +11045,7 @@
         <v>535</v>
       </c>
       <c r="K11" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L11">
         <v>10.088237612202811</v>
@@ -11066,7 +11078,7 @@
         <v>589</v>
       </c>
       <c r="X11" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="Y11">
         <v>0.16350000000000001</v>
@@ -11101,7 +11113,7 @@
         <v>537</v>
       </c>
       <c r="K12" t="s">
-        <v>497</v>
+        <v>459</v>
       </c>
       <c r="L12">
         <v>4.7527038630847755</v>
@@ -11134,7 +11146,7 @@
         <v>591</v>
       </c>
       <c r="X12" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="Y12">
         <v>13.40025</v>
@@ -11169,7 +11181,7 @@
         <v>539</v>
       </c>
       <c r="K13" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="L13">
         <v>1.4400913107240583</v>
@@ -11202,7 +11214,7 @@
         <v>593</v>
       </c>
       <c r="X13" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="Y13">
         <v>8.4097500000000007</v>
@@ -11237,7 +11249,7 @@
         <v>541</v>
       </c>
       <c r="K14" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="L14">
         <v>1.437273477445641</v>
@@ -11270,7 +11282,7 @@
         <v>595</v>
       </c>
       <c r="X14" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="Y14">
         <v>14.358750000000001</v>
@@ -11305,7 +11317,7 @@
         <v>543</v>
       </c>
       <c r="K15" t="s">
-        <v>484</v>
+        <v>469</v>
       </c>
       <c r="L15">
         <v>2.1922713563210485</v>
@@ -11373,7 +11385,7 @@
         <v>545</v>
       </c>
       <c r="K16" t="s">
-        <v>469</v>
+        <v>496</v>
       </c>
       <c r="L16">
         <v>0.73811583011208182</v>
@@ -11441,7 +11453,7 @@
         <v>547</v>
       </c>
       <c r="K17" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="L17">
         <v>5.5236145427785717</v>
@@ -11474,7 +11486,7 @@
         <v>601</v>
       </c>
       <c r="X17" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="Y17">
         <v>8.6609999999999996</v>
@@ -11509,7 +11521,7 @@
         <v>549</v>
       </c>
       <c r="K18" t="s">
-        <v>456</v>
+        <v>491</v>
       </c>
       <c r="L18">
         <v>5.5488357050452785E-3</v>
@@ -11577,7 +11589,7 @@
         <v>551</v>
       </c>
       <c r="K19" t="s">
-        <v>462</v>
+        <v>482</v>
       </c>
       <c r="L19">
         <v>6.6811161360847313</v>
@@ -11610,7 +11622,7 @@
         <v>605</v>
       </c>
       <c r="X19" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="Y19">
         <v>1.7250000000000001E-2</v>
@@ -11645,7 +11657,7 @@
         <v>553</v>
       </c>
       <c r="K20" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="L20">
         <v>18.094012332227912</v>
@@ -11678,7 +11690,7 @@
         <v>607</v>
       </c>
       <c r="X20" t="s">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="Y20">
         <v>6.8624999999999998</v>
@@ -11713,7 +11725,7 @@
         <v>555</v>
       </c>
       <c r="K21" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="L21">
         <v>1.3529085560597105</v>
@@ -11748,7 +11760,7 @@
         <v>557</v>
       </c>
       <c r="K22" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="L22">
         <v>3.7088360788644938</v>
@@ -11783,7 +11795,7 @@
         <v>559</v>
       </c>
       <c r="K23" t="s">
-        <v>490</v>
+        <v>452</v>
       </c>
       <c r="L23">
         <v>13.683903390107789</v>
@@ -11818,7 +11830,7 @@
         <v>561</v>
       </c>
       <c r="K24" t="s">
-        <v>458</v>
+        <v>493</v>
       </c>
       <c r="L24">
         <v>5.4676081362262012</v>
@@ -11853,7 +11865,7 @@
         <v>563</v>
       </c>
       <c r="K25" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="L25">
         <v>8.9064794695455216</v>
@@ -11888,7 +11900,7 @@
         <v>565</v>
       </c>
       <c r="K26" t="s">
-        <v>496</v>
+        <v>458</v>
       </c>
       <c r="L26">
         <v>14.189229081738485</v>
@@ -11923,7 +11935,7 @@
         <v>567</v>
       </c>
       <c r="K27" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="L27">
         <v>10.717982842540293</v>
@@ -11958,7 +11970,7 @@
         <v>569</v>
       </c>
       <c r="K28" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="L28">
         <v>9.6743476082482847</v>
@@ -11993,7 +12005,7 @@
         <v>571</v>
       </c>
       <c r="K29" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="L29">
         <v>23.206762484053751</v>
@@ -12028,7 +12040,7 @@
         <v>573</v>
       </c>
       <c r="K30" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="L30">
         <v>5.8372174437039801</v>
@@ -12063,7 +12075,7 @@
         <v>575</v>
       </c>
       <c r="K31" t="s">
-        <v>460</v>
+        <v>494</v>
       </c>
       <c r="L31">
         <v>1.8845590125315521</v>
@@ -12098,7 +12110,7 @@
         <v>577</v>
       </c>
       <c r="K32" t="s">
-        <v>464</v>
+        <v>484</v>
       </c>
       <c r="L32">
         <v>7.179650801796102</v>
@@ -12133,7 +12145,7 @@
         <v>579</v>
       </c>
       <c r="K33" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="L33">
         <v>14.559476964149322</v>
@@ -12168,7 +12180,7 @@
         <v>581</v>
       </c>
       <c r="K34" t="s">
-        <v>494</v>
+        <v>456</v>
       </c>
       <c r="L34">
         <v>1.3536151515148049</v>
@@ -12203,7 +12215,7 @@
         <v>583</v>
       </c>
       <c r="K35" t="s">
-        <v>492</v>
+        <v>454</v>
       </c>
       <c r="L35">
         <v>4.820514286595051</v>
@@ -12238,7 +12250,7 @@
         <v>585</v>
       </c>
       <c r="K36" t="s">
-        <v>467</v>
+        <v>487</v>
       </c>
       <c r="L36">
         <v>8.1474073379531564</v>
@@ -12273,7 +12285,7 @@
         <v>587</v>
       </c>
       <c r="K37" t="s">
-        <v>465</v>
+        <v>485</v>
       </c>
       <c r="L37">
         <v>9.9689850956014183</v>
@@ -12288,7 +12300,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D638586-4FF1-4DAC-8B30-A3EAD68996BA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A0FA040-256E-4DAA-9D4A-1B0CDB366AFD}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_NGA_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_NGA_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NGA_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D7DD1836-AF72-48BB-9A0F-E3C61723F9CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D07A35F9-5AD4-424A-B7C2-AD2948EC71FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2191" uniqueCount="632">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2191" uniqueCount="633">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -993,40 +993,208 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_034</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_036</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_035</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_002</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 2</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_008</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 8</t>
   </si>
   <si>
-    <t>distr_solelc_spv_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
+    <t>distr_solelc_spv_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_033</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
   </si>
   <si>
     <t>distr_solelc_spv_032</t>
@@ -1047,193 +1215,106 @@
     <t>connecting solar to buses in cluster 19</t>
   </si>
   <si>
-    <t>distr_solelc_spv_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_033</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_035</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_034</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_036</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w215459565-330,e_w563715917-330,e_w548724506-330,e_w565081403-330</t>
+  </si>
+  <si>
+    <t>e_NG18-330,e_w746582404-330,e_NG17-330</t>
+  </si>
+  <si>
+    <t>e_w564430566-330,e_w564429999-330</t>
+  </si>
+  <si>
+    <t>e_w564410486-330,e_w1226249784-330</t>
+  </si>
+  <si>
+    <t>e_NG13-330,e_NG15-330,e_w1057700475-330,e_w215459565-330,e_w671893504-330,e_w548724506-330,e_NG12-330</t>
+  </si>
+  <si>
+    <t>e_w565866986-330,e_NG11-330,e_w574152484-330</t>
+  </si>
+  <si>
+    <t>e_w565081403-330,e_w267122040-330</t>
+  </si>
+  <si>
+    <t>e_w565081403-330,e_w266617120-330,e_w266712817-330,e_w267122040-330</t>
+  </si>
+  <si>
+    <t>e_w108020974-330,e_w836122563-330,e_w559542338-330,e_NG9-330,e_w669957212-330,e_w1324578567-330,e_w565866986-330</t>
+  </si>
+  <si>
+    <t>e_NG8-330,e_w564445207-330,e_w1328602766-330</t>
+  </si>
+  <si>
+    <t>e_NG6-330,e_NG7-330,e_NG3-330,e_w565486405-330</t>
+  </si>
+  <si>
+    <t>e_w1226249784-330,e_NG1-330,e_NG2-330,e_w395182311-330</t>
+  </si>
+  <si>
+    <t>e_w266712817-330,e_w563723584-330,e_w267122040-330,e_w655273140-330</t>
+  </si>
+  <si>
+    <t>e_w563723584-330,e_w655273140-330</t>
+  </si>
+  <si>
+    <t>e_w1328602766-330,e_w695826179-330,e_w540463591-330,e_w481286430-330</t>
+  </si>
+  <si>
+    <t>e_w565847437-330,e_w565081403-330,e_w266617120-330</t>
+  </si>
+  <si>
+    <t>e_w565081403-330</t>
+  </si>
+  <si>
+    <t>e_w266617120-330,e_w395182311-330,e_w266712817-330,e_w563723584-330</t>
+  </si>
+  <si>
+    <t>e_w267122040-330</t>
+  </si>
+  <si>
+    <t>e_w564445207-330,e_w477596994-330,e_w565866986-330,e_NG11-330,e_w574152484-330,e_w215459565-330</t>
+  </si>
+  <si>
+    <t>e_w564429999-330,e_NG12-330</t>
+  </si>
+  <si>
+    <t>e_NG12-330,e_w565081403-330,e_w564429999-330</t>
+  </si>
+  <si>
+    <t>e_w695826179-330</t>
+  </si>
+  <si>
+    <t>e_w546666333-330,e_w565866986-330,e_NG18-330</t>
+  </si>
+  <si>
     <t>e_w1328602766-330,e_NG6-330</t>
   </si>
   <si>
     <t>e_w746582404-330,e_w563732518-330,e_NG20-330,e_NG21-330,e_w334825256-330,e_w564429999-330</t>
   </si>
   <si>
-    <t>e_w564445207-330,e_w477596994-330,e_w565866986-330,e_NG11-330,e_w574152484-330,e_w215459565-330</t>
-  </si>
-  <si>
-    <t>e_w564429999-330,e_NG12-330</t>
-  </si>
-  <si>
-    <t>e_NG12-330,e_w565081403-330,e_w564429999-330</t>
+    <t>e_w564410486-330,e_w695826179-330,e_w39469643-330,e_w1226249784-330</t>
+  </si>
+  <si>
+    <t>e_w565486405-330,e_NG3-330,e_NG4-330,e_NG5-330,e_w565847437-330</t>
+  </si>
+  <si>
+    <t>e_w563715917-330,e_NG5-330,e_w565081403-330</t>
+  </si>
+  <si>
+    <t>e_w556550171-330,e_w39469643-330,e_w266617120-330</t>
+  </si>
+  <si>
+    <t>e_w564430566-330</t>
+  </si>
+  <si>
+    <t>e_NG2-330,e_NG1-330,e_w395182311-330,e_w563723584-330</t>
   </si>
   <si>
     <t>e_w695826179-330,e_w564410486-330,e_NG3-330,e_w556550171-330,e_w39469643-330</t>
@@ -1242,85 +1323,76 @@
     <t>e_w546666333-330,e_NG17-330,e_w575706869-330</t>
   </si>
   <si>
-    <t>e_w565081403-330,e_w267122040-330</t>
-  </si>
-  <si>
-    <t>e_w564410486-330,e_w695826179-330,e_w39469643-330,e_w1226249784-330</t>
-  </si>
-  <si>
-    <t>e_w565486405-330,e_NG3-330,e_NG4-330,e_NG5-330,e_w565847437-330</t>
-  </si>
-  <si>
-    <t>e_w563715917-330,e_NG5-330,e_w565081403-330</t>
-  </si>
-  <si>
-    <t>e_w556550171-330,e_w39469643-330,e_w266617120-330</t>
-  </si>
-  <si>
-    <t>e_w215459565-330,e_w563715917-330,e_w548724506-330,e_w565081403-330</t>
-  </si>
-  <si>
-    <t>e_w108020974-330,e_w836122563-330,e_w559542338-330,e_NG9-330,e_w669957212-330,e_w1324578567-330,e_w565866986-330</t>
-  </si>
-  <si>
-    <t>e_NG8-330,e_w564445207-330,e_w1328602766-330</t>
-  </si>
-  <si>
-    <t>e_w565866986-330,e_NG11-330,e_w574152484-330</t>
-  </si>
-  <si>
-    <t>e_w565081403-330,e_w266617120-330,e_w266712817-330,e_w267122040-330</t>
-  </si>
-  <si>
-    <t>e_w564430566-330</t>
-  </si>
-  <si>
-    <t>e_NG2-330,e_NG1-330,e_w395182311-330,e_w563723584-330</t>
-  </si>
-  <si>
-    <t>e_w695826179-330</t>
-  </si>
-  <si>
-    <t>e_w267122040-330</t>
-  </si>
-  <si>
-    <t>e_NG18-330,e_w746582404-330,e_NG17-330</t>
-  </si>
-  <si>
-    <t>e_w564430566-330,e_w564429999-330</t>
-  </si>
-  <si>
-    <t>e_w564410486-330,e_w1226249784-330</t>
-  </si>
-  <si>
-    <t>e_NG13-330,e_NG15-330,e_w1057700475-330,e_w215459565-330,e_w671893504-330,e_w548724506-330,e_NG12-330</t>
-  </si>
-  <si>
-    <t>e_w546666333-330,e_w565866986-330,e_NG18-330</t>
-  </si>
-  <si>
-    <t>e_NG6-330,e_NG7-330,e_NG3-330,e_w565486405-330</t>
-  </si>
-  <si>
-    <t>e_w1226249784-330,e_NG1-330,e_NG2-330,e_w395182311-330</t>
-  </si>
-  <si>
-    <t>e_w266712817-330,e_w563723584-330,e_w267122040-330,e_w655273140-330</t>
-  </si>
-  <si>
-    <t>e_w563723584-330,e_w655273140-330</t>
-  </si>
-  <si>
-    <t>e_w1328602766-330,e_w695826179-330,e_w540463591-330,e_w481286430-330</t>
-  </si>
-  <si>
-    <t>e_w565847437-330,e_w565081403-330,e_w266617120-330</t>
-  </si>
-  <si>
-    <t>e_w565081403-330</t>
-  </si>
-  <si>
-    <t>e_w266617120-330,e_w395182311-330,e_w266712817-330,e_w563723584-330</t>
+    <t>distr_wonelc_won_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
   </si>
   <si>
     <t>distr_wonelc_won_013</t>
@@ -1347,40 +1419,28 @@
     <t>connecting wind onshore to buses in cluster 16</t>
   </si>
   <si>
-    <t>distr_wonelc_won_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
+    <t>distr_wonelc_won_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
   </si>
   <si>
     <t>distr_wonelc_won_005</t>
@@ -1389,28 +1449,10 @@
     <t>connecting wind onshore to buses in cluster 5</t>
   </si>
   <si>
-    <t>distr_wonelc_won_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
+    <t>distr_wonelc_won_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
   </si>
   <si>
     <t>distr_wonelc_won_003</t>
@@ -1419,12 +1461,6 @@
     <t>connecting wind onshore to buses in cluster 3</t>
   </si>
   <si>
-    <t>distr_wonelc_won_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_009</t>
   </si>
   <si>
@@ -1449,40 +1485,61 @@
     <t>connecting wind onshore to buses in cluster 26</t>
   </si>
   <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
+    <t>elc_won_002</t>
+  </si>
+  <si>
+    <t>elc_won_007</t>
+  </si>
+  <si>
+    <t>e_w1328602766-330,e_w540463591-330,e_NG6-330,e_w477596994-330,e_NG7-330</t>
+  </si>
+  <si>
+    <t>elc_won_012</t>
+  </si>
+  <si>
+    <t>e_w564410486-330,e_w695826179-330</t>
+  </si>
+  <si>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>e_w108020974-330</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>e_w564410486-330</t>
+  </si>
+  <si>
+    <t>elc_won_021</t>
+  </si>
+  <si>
+    <t>e_w266617120-330,e_w266712817-330</t>
+  </si>
+  <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>e_NG3-330,e_w556550171-330,e_w39469643-330,e_w266617120-330</t>
+  </si>
+  <si>
+    <t>elc_won_019</t>
+  </si>
+  <si>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>e_w695826179-330,e_w1328602766-330,e_w540463591-330</t>
   </si>
   <si>
     <t>elc_won_013</t>
@@ -1506,34 +1563,28 @@
     <t>elc_won_016</t>
   </si>
   <si>
-    <t>elc_won_002</t>
-  </si>
-  <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
-    <t>e_w1328602766-330,e_w540463591-330,e_NG6-330,e_w477596994-330,e_NG7-330</t>
-  </si>
-  <si>
-    <t>elc_won_012</t>
-  </si>
-  <si>
-    <t>e_w564410486-330,e_w695826179-330</t>
-  </si>
-  <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>e_w564410486-330</t>
-  </si>
-  <si>
-    <t>elc_won_010</t>
-  </si>
-  <si>
-    <t>e_NG3-330,e_w556550171-330,e_w39469643-330,e_w266617120-330</t>
-  </si>
-  <si>
-    <t>elc_won_019</t>
+    <t>elc_won_011</t>
+  </si>
+  <si>
+    <t>e_w695826179-330,e_w564410486-330</t>
+  </si>
+  <si>
+    <t>elc_won_023</t>
+  </si>
+  <si>
+    <t>e_w564410486-330,e_w1226249784-330,e_NG1-330</t>
+  </si>
+  <si>
+    <t>elc_won_020</t>
+  </si>
+  <si>
+    <t>e_w395182311-330,e_w266712817-330,e_w563723584-330</t>
+  </si>
+  <si>
+    <t>elc_won_017</t>
+  </si>
+  <si>
+    <t>e_w266712817-330,e_w563723584-330,e_w655273140-330</t>
   </si>
   <si>
     <t>elc_won_005</t>
@@ -1542,39 +1593,15 @@
     <t>e_w548724506-330,e_w563715917-330,e_w565081403-330</t>
   </si>
   <si>
-    <t>elc_won_011</t>
-  </si>
-  <si>
-    <t>e_w695826179-330,e_w564410486-330</t>
-  </si>
-  <si>
-    <t>elc_won_023</t>
-  </si>
-  <si>
-    <t>e_w564410486-330,e_w1226249784-330,e_NG1-330</t>
-  </si>
-  <si>
-    <t>elc_won_020</t>
-  </si>
-  <si>
-    <t>e_w395182311-330,e_w266712817-330,e_w563723584-330</t>
-  </si>
-  <si>
-    <t>elc_won_017</t>
-  </si>
-  <si>
-    <t>e_w266712817-330,e_w563723584-330,e_w655273140-330</t>
+    <t>elc_won_018</t>
+  </si>
+  <si>
+    <t>e_w395182311-330,e_w563723584-330</t>
   </si>
   <si>
     <t>elc_won_003</t>
   </si>
   <si>
-    <t>elc_won_018</t>
-  </si>
-  <si>
-    <t>e_w395182311-330,e_w563723584-330</t>
-  </si>
-  <si>
     <t>elc_won_009</t>
   </si>
   <si>
@@ -1596,144 +1623,117 @@
     <t>e_w266712817-330,e_w267122040-330,e_w655273140-330</t>
   </si>
   <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>e_w108020974-330</t>
-  </si>
-  <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>elc_won_021</t>
-  </si>
-  <si>
-    <t>e_w266617120-330,e_w266712817-330</t>
-  </si>
-  <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
-    <t>e_w695826179-330,e_w1328602766-330,e_w540463591-330</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_008</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 8</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_003</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 3</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
     <t>elc_wof_008</t>
   </si>
   <si>
+    <t>elc_wof_005</t>
+  </si>
+  <si>
+    <t>e_NG18-330,e_w746582404-330</t>
+  </si>
+  <si>
+    <t>elc_wof_006</t>
+  </si>
+  <si>
+    <t>e_w746582404-330</t>
+  </si>
+  <si>
+    <t>elc_wof_001</t>
+  </si>
+  <si>
+    <t>e_NG9-330,e_w1324578567-330,e_w565866986-330</t>
+  </si>
+  <si>
+    <t>elc_wof_010</t>
+  </si>
+  <si>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>elc_wof_004</t>
+  </si>
+  <si>
+    <t>e_NG18-330,e_w559542338-330</t>
+  </si>
+  <si>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>e_w746582404-330,e_w564430566-330</t>
+  </si>
+  <si>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>e_w706082453-330,e_w108020974-330,e_w559542338-330,e_w565866986-330,e_w546666333-330</t>
+  </si>
+  <si>
     <t>elc_wof_003</t>
   </si>
   <si>
     <t>e_NG18-330</t>
   </si>
   <si>
-    <t>elc_wof_004</t>
-  </si>
-  <si>
-    <t>e_NG18-330,e_w559542338-330</t>
-  </si>
-  <si>
-    <t>elc_wof_007</t>
-  </si>
-  <si>
-    <t>e_w746582404-330,e_w564430566-330</t>
-  </si>
-  <si>
-    <t>elc_wof_009</t>
-  </si>
-  <si>
-    <t>e_w746582404-330</t>
-  </si>
-  <si>
-    <t>elc_wof_002</t>
-  </si>
-  <si>
-    <t>e_w706082453-330,e_w108020974-330,e_w559542338-330,e_w565866986-330,e_w546666333-330</t>
-  </si>
-  <si>
-    <t>elc_wof_001</t>
-  </si>
-  <si>
-    <t>e_NG9-330,e_w1324578567-330,e_w565866986-330</t>
-  </si>
-  <si>
-    <t>elc_wof_010</t>
-  </si>
-  <si>
-    <t>e_NG18-330,e_w746582404-330</t>
-  </si>
-  <si>
-    <t>elc_wof_005</t>
-  </si>
-  <si>
-    <t>elc_wof_006</t>
-  </si>
-  <si>
     <t>e_won_001</t>
   </si>
   <si>
@@ -2023,6 +2023,9 @@
   </si>
   <si>
     <t>yes</t>
+  </si>
+  <si>
+    <t>e_NG10-330,e_w559542338-330,e_w669957212-330,e_w706082453-330,e_w746582404-330</t>
   </si>
 </sst>
 </file>
@@ -3916,7 +3919,7 @@
       </c>
       <c r="L27" t="str">
         <f>$V$28</f>
-        <v>ELC</v>
+        <v>e_NG10-330,e_w559542338-330,e_w669957212-330,e_w706082453-330,e_w746582404-330</v>
       </c>
       <c r="P27">
         <v>0</v>
@@ -3938,7 +3941,7 @@
       </c>
       <c r="K28" t="str">
         <f>$V$28</f>
-        <v>ELC</v>
+        <v>e_NG10-330,e_w559542338-330,e_w669957212-330,e_w706082453-330,e_w746582404-330</v>
       </c>
       <c r="P28">
         <v>0</v>
@@ -3953,7 +3956,7 @@
         <v>50</v>
       </c>
       <c r="V28" s="147" t="s">
-        <v>19</v>
+        <v>632</v>
       </c>
     </row>
   </sheetData>
@@ -6755,7 +6758,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6ABACE4-C695-4B11-9F5A-6500E6F1FF35}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BABD0492-5D5C-416F-A4C5-00AF7F150ED9}">
   <dimension ref="B9:BD46"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6993,16 +6996,16 @@
         <v>288</v>
       </c>
       <c r="Y11" t="s">
-        <v>251</v>
+        <v>272</v>
       </c>
       <c r="Z11" t="s">
         <v>364</v>
       </c>
       <c r="AA11">
-        <v>0.99723470592138874</v>
+        <v>0.99655017109874156</v>
       </c>
       <c r="AB11">
-        <v>50.697058107873339</v>
+        <v>63.246863189739024</v>
       </c>
       <c r="AD11" t="s">
         <v>287</v>
@@ -7032,13 +7035,13 @@
         <v>452</v>
       </c>
       <c r="AN11" t="s">
-        <v>453</v>
+        <v>382</v>
       </c>
       <c r="AO11">
-        <v>0.99207403494667001</v>
+        <v>0.99537626424805781</v>
       </c>
       <c r="AP11">
-        <v>145.30935931104892</v>
+        <v>84.768488785605911</v>
       </c>
       <c r="AR11" t="s">
         <v>287</v>
@@ -7068,7 +7071,7 @@
         <v>518</v>
       </c>
       <c r="BB11" t="s">
-        <v>381</v>
+        <v>394</v>
       </c>
       <c r="BC11">
         <v>0.99337755486839363</v>
@@ -7139,16 +7142,16 @@
         <v>292</v>
       </c>
       <c r="Y12" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Z12" t="s">
         <v>365</v>
       </c>
       <c r="AA12">
-        <v>0.99750455285561002</v>
+        <v>0.99884992726149324</v>
       </c>
       <c r="AB12">
-        <v>45.749864313816033</v>
+        <v>21.084666872623977</v>
       </c>
       <c r="AD12" t="s">
         <v>287</v>
@@ -7175,16 +7178,16 @@
         <v>400</v>
       </c>
       <c r="AM12" t="s">
+        <v>453</v>
+      </c>
+      <c r="AN12" t="s">
         <v>454</v>
       </c>
-      <c r="AN12" t="s">
-        <v>455</v>
-      </c>
       <c r="AO12">
-        <v>0.99637613831578808</v>
+        <v>0.99740664776461363</v>
       </c>
       <c r="AP12">
-        <v>66.437464210551497</v>
+        <v>47.544790982083583</v>
       </c>
       <c r="AR12" t="s">
         <v>287</v>
@@ -7217,10 +7220,10 @@
         <v>520</v>
       </c>
       <c r="BC12">
-        <v>0.99174031680019514</v>
+        <v>0.9888409065104441</v>
       </c>
       <c r="BD12">
-        <v>151.42752532975524</v>
+        <v>204.58338064185853</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -7285,16 +7288,16 @@
         <v>294</v>
       </c>
       <c r="Y13" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="Z13" t="s">
         <v>366</v>
       </c>
       <c r="AA13">
-        <v>0.99732710525923551</v>
+        <v>0.99882431199806432</v>
       </c>
       <c r="AB13">
-        <v>49.003070247349498</v>
+        <v>21.554280035486567</v>
       </c>
       <c r="AD13" t="s">
         <v>287</v>
@@ -7321,16 +7324,16 @@
         <v>402</v>
       </c>
       <c r="AM13" t="s">
+        <v>455</v>
+      </c>
+      <c r="AN13" t="s">
         <v>456</v>
       </c>
-      <c r="AN13" t="s">
-        <v>457</v>
-      </c>
       <c r="AO13">
-        <v>0.99501745221162918</v>
+        <v>0.9913636988912532</v>
       </c>
       <c r="AP13">
-        <v>91.346709453464783</v>
+        <v>158.33218699369189</v>
       </c>
       <c r="AR13" t="s">
         <v>287</v>
@@ -7363,10 +7366,10 @@
         <v>522</v>
       </c>
       <c r="BC13">
-        <v>0.99246115999793105</v>
+        <v>0.99132158137897763</v>
       </c>
       <c r="BD13">
-        <v>138.21206670459694</v>
+        <v>159.10434138541075</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -7431,16 +7434,16 @@
         <v>296</v>
       </c>
       <c r="Y14" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="Z14" t="s">
         <v>367</v>
       </c>
       <c r="AA14">
-        <v>0.99601914721828588</v>
+        <v>0.99133276722560904</v>
       </c>
       <c r="AB14">
-        <v>72.982300998092228</v>
+        <v>158.89926753050145</v>
       </c>
       <c r="AD14" t="s">
         <v>287</v>
@@ -7467,16 +7470,16 @@
         <v>404</v>
       </c>
       <c r="AM14" t="s">
+        <v>457</v>
+      </c>
+      <c r="AN14" t="s">
         <v>458</v>
       </c>
-      <c r="AN14" t="s">
-        <v>393</v>
-      </c>
       <c r="AO14">
-        <v>0.99698529931119073</v>
+        <v>0.99795762496221851</v>
       </c>
       <c r="AP14">
-        <v>55.269512628170503</v>
+        <v>37.443542359327118</v>
       </c>
       <c r="AR14" t="s">
         <v>287</v>
@@ -7509,10 +7512,10 @@
         <v>524</v>
       </c>
       <c r="BC14">
-        <v>0.99268778174342398</v>
+        <v>0.99794494286432878</v>
       </c>
       <c r="BD14">
-        <v>134.05733470389279</v>
+        <v>37.67604748730637</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7577,16 +7580,16 @@
         <v>298</v>
       </c>
       <c r="Y15" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="Z15" t="s">
         <v>368</v>
       </c>
       <c r="AA15">
-        <v>0.99403967905190227</v>
+        <v>0.99728758220200375</v>
       </c>
       <c r="AB15">
-        <v>109.27255071512499</v>
+        <v>49.727659629930621</v>
       </c>
       <c r="AD15" t="s">
         <v>287</v>
@@ -7616,13 +7619,13 @@
         <v>459</v>
       </c>
       <c r="AN15" t="s">
-        <v>384</v>
+        <v>460</v>
       </c>
       <c r="AO15">
-        <v>0.99537626424805781</v>
+        <v>0.99582871194680656</v>
       </c>
       <c r="AP15">
-        <v>84.768488785605911</v>
+        <v>76.473614308545862</v>
       </c>
       <c r="AR15" t="s">
         <v>287</v>
@@ -7652,13 +7655,13 @@
         <v>525</v>
       </c>
       <c r="BB15" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="BC15">
-        <v>0.99755731205629283</v>
+        <v>0.99371472191320109</v>
       </c>
       <c r="BD15">
-        <v>44.782612301298634</v>
+        <v>115.23009825798009</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -7723,16 +7726,16 @@
         <v>300</v>
       </c>
       <c r="Y16" t="s">
-        <v>281</v>
+        <v>254</v>
       </c>
       <c r="Z16" t="s">
         <v>369</v>
       </c>
       <c r="AA16">
-        <v>0.99339354842512728</v>
+        <v>0.99832768028365393</v>
       </c>
       <c r="AB16">
-        <v>121.1182788726671</v>
+        <v>30.659194799678048</v>
       </c>
       <c r="AD16" t="s">
         <v>287</v>
@@ -7759,16 +7762,16 @@
         <v>408</v>
       </c>
       <c r="AM16" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AN16" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AO16">
-        <v>0.99740664776461363</v>
+        <v>0.99555964959117016</v>
       </c>
       <c r="AP16">
-        <v>47.544790982083583</v>
+        <v>81.406424161880452</v>
       </c>
       <c r="AR16" t="s">
         <v>287</v>
@@ -7795,16 +7798,16 @@
         <v>508</v>
       </c>
       <c r="BA16" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="BB16" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="BC16">
-        <v>0.9962053430710629</v>
+        <v>0.99755731205629283</v>
       </c>
       <c r="BD16">
-        <v>69.568710363846861</v>
+        <v>44.782612301298634</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -7869,16 +7872,16 @@
         <v>302</v>
       </c>
       <c r="Y17" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="Z17" t="s">
         <v>370</v>
       </c>
       <c r="AA17">
-        <v>0.99805028151894915</v>
+        <v>0.99057172008573791</v>
       </c>
       <c r="AB17">
-        <v>35.744838819266263</v>
+        <v>172.85179842813815</v>
       </c>
       <c r="AD17" t="s">
         <v>287</v>
@@ -7905,16 +7908,16 @@
         <v>410</v>
       </c>
       <c r="AM17" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AN17" t="s">
-        <v>463</v>
+        <v>380</v>
       </c>
       <c r="AO17">
-        <v>0.9913636988912532</v>
+        <v>0.99354454384798807</v>
       </c>
       <c r="AP17">
-        <v>158.33218699369189</v>
+        <v>118.35002945355123</v>
       </c>
       <c r="AR17" t="s">
         <v>287</v>
@@ -7941,16 +7944,16 @@
         <v>510</v>
       </c>
       <c r="BA17" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="BB17" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="BC17">
-        <v>0.99794494286432878</v>
+        <v>0.99246115999793105</v>
       </c>
       <c r="BD17">
-        <v>37.67604748730637</v>
+        <v>138.21206670459694</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8015,16 +8018,16 @@
         <v>304</v>
       </c>
       <c r="Y18" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="Z18" t="s">
         <v>371</v>
       </c>
       <c r="AA18">
-        <v>0.98395338050941106</v>
+        <v>0.99095032933880767</v>
       </c>
       <c r="AB18">
-        <v>294.18802399413073</v>
+        <v>165.91062878852651</v>
       </c>
       <c r="AD18" t="s">
         <v>287</v>
@@ -8054,13 +8057,13 @@
         <v>464</v>
       </c>
       <c r="AN18" t="s">
-        <v>465</v>
+        <v>371</v>
       </c>
       <c r="AO18">
-        <v>0.9933445384762607</v>
+        <v>0.99069345154297106</v>
       </c>
       <c r="AP18">
-        <v>122.01679460188713</v>
+        <v>170.62005504553079</v>
       </c>
       <c r="AR18" t="s">
         <v>287</v>
@@ -8087,16 +8090,16 @@
         <v>512</v>
       </c>
       <c r="BA18" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="BB18" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="BC18">
-        <v>0.99371472191320109</v>
+        <v>0.99268778174342398</v>
       </c>
       <c r="BD18">
-        <v>115.23009825798009</v>
+        <v>134.05733470389279</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8161,16 +8164,16 @@
         <v>306</v>
       </c>
       <c r="Y19" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="Z19" t="s">
         <v>372</v>
       </c>
       <c r="AA19">
-        <v>0.993124380119488</v>
+        <v>0.99802162515875081</v>
       </c>
       <c r="AB19">
-        <v>126.05303114271953</v>
+        <v>36.270205422902137</v>
       </c>
       <c r="AD19" t="s">
         <v>287</v>
@@ -8197,16 +8200,16 @@
         <v>414</v>
       </c>
       <c r="AM19" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AN19" t="s">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="AO19">
-        <v>0.9938298282896767</v>
+        <v>0.9933445384762607</v>
       </c>
       <c r="AP19">
-        <v>113.11981468926018</v>
+        <v>122.01679460188713</v>
       </c>
       <c r="AR19" t="s">
         <v>287</v>
@@ -8233,16 +8236,16 @@
         <v>514</v>
       </c>
       <c r="BA19" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="BB19" t="s">
         <v>532</v>
       </c>
       <c r="BC19">
-        <v>0.9888409065104441</v>
+        <v>0.9962053430710629</v>
       </c>
       <c r="BD19">
-        <v>204.58338064185853</v>
+        <v>69.568710363846861</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8307,16 +8310,16 @@
         <v>308</v>
       </c>
       <c r="Y20" t="s">
-        <v>274</v>
+        <v>252</v>
       </c>
       <c r="Z20" t="s">
         <v>373</v>
       </c>
       <c r="AA20">
-        <v>0.99769438809486533</v>
+        <v>0.99631349511992195</v>
       </c>
       <c r="AB20">
-        <v>42.269551594135834</v>
+        <v>67.585922801431252</v>
       </c>
       <c r="AD20" t="s">
         <v>287</v>
@@ -8343,16 +8346,16 @@
         <v>416</v>
       </c>
       <c r="AM20" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="AN20" t="s">
-        <v>393</v>
+        <v>467</v>
       </c>
       <c r="AO20">
-        <v>0.99008544123370779</v>
+        <v>0.9938298282896767</v>
       </c>
       <c r="AP20">
-        <v>181.76691071535706</v>
+        <v>113.11981468926018</v>
       </c>
       <c r="AR20" t="s">
         <v>287</v>
@@ -8379,16 +8382,16 @@
         <v>516</v>
       </c>
       <c r="BA20" t="s">
+        <v>533</v>
+      </c>
+      <c r="BB20" t="s">
         <v>534</v>
       </c>
-      <c r="BB20" t="s">
-        <v>526</v>
-      </c>
       <c r="BC20">
-        <v>0.99132158137897763</v>
+        <v>0.99174031680019514</v>
       </c>
       <c r="BD20">
-        <v>159.10434138541075</v>
+        <v>151.42752532975524</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -8453,16 +8456,16 @@
         <v>310</v>
       </c>
       <c r="Y21" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="Z21" t="s">
         <v>374</v>
       </c>
       <c r="AA21">
-        <v>0.99489048613238573</v>
+        <v>0.9963457067026108</v>
       </c>
       <c r="AB21">
-        <v>93.674420906261602</v>
+        <v>66.99537711880258</v>
       </c>
       <c r="AD21" t="s">
         <v>287</v>
@@ -8489,16 +8492,16 @@
         <v>418</v>
       </c>
       <c r="AM21" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AN21" t="s">
-        <v>470</v>
+        <v>377</v>
       </c>
       <c r="AO21">
-        <v>0.99562035686170025</v>
+        <v>0.99008544123370779</v>
       </c>
       <c r="AP21">
-        <v>80.293457535494625</v>
+        <v>181.76691071535706</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8563,16 +8566,16 @@
         <v>312</v>
       </c>
       <c r="Y22" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="Z22" t="s">
         <v>375</v>
       </c>
       <c r="AA22">
-        <v>0.99642867204968677</v>
+        <v>0.99644641159652714</v>
       </c>
       <c r="AB22">
-        <v>65.474345755743457</v>
+        <v>65.149120730335611</v>
       </c>
       <c r="AD22" t="s">
         <v>287</v>
@@ -8599,16 +8602,16 @@
         <v>420</v>
       </c>
       <c r="AM22" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="AN22" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="AO22">
-        <v>0.99178855761800622</v>
+        <v>0.99429686126958916</v>
       </c>
       <c r="AP22">
-        <v>150.54311033655213</v>
+        <v>104.55754339086491</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -8673,16 +8676,16 @@
         <v>314</v>
       </c>
       <c r="Y23" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="Z23" t="s">
         <v>376</v>
       </c>
       <c r="AA23">
-        <v>0.99655017109874156</v>
+        <v>0.99436579068013853</v>
       </c>
       <c r="AB23">
-        <v>63.246863189739024</v>
+        <v>103.29383753079337</v>
       </c>
       <c r="AD23" t="s">
         <v>287</v>
@@ -8709,16 +8712,16 @@
         <v>422</v>
       </c>
       <c r="AM23" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="AN23" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="AO23">
-        <v>0.99296304108660982</v>
+        <v>0.99207403494667001</v>
       </c>
       <c r="AP23">
-        <v>129.01091341215286</v>
+        <v>145.30935931104892</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -8783,16 +8786,16 @@
         <v>316</v>
       </c>
       <c r="Y24" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="Z24" t="s">
         <v>377</v>
       </c>
       <c r="AA24">
-        <v>0.99802162515875081</v>
+        <v>0.99262439568706373</v>
       </c>
       <c r="AB24">
-        <v>36.270205422902137</v>
+        <v>135.21941240383219</v>
       </c>
       <c r="AD24" t="s">
         <v>287</v>
@@ -8819,16 +8822,16 @@
         <v>424</v>
       </c>
       <c r="AM24" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="AN24" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="AO24">
-        <v>0.99152317643653909</v>
+        <v>0.99637613831578808</v>
       </c>
       <c r="AP24">
-        <v>155.40843199678267</v>
+        <v>66.437464210551497</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -8893,16 +8896,16 @@
         <v>318</v>
       </c>
       <c r="Y25" t="s">
-        <v>252</v>
+        <v>285</v>
       </c>
       <c r="Z25" t="s">
         <v>378</v>
       </c>
       <c r="AA25">
-        <v>0.99631349511992195</v>
+        <v>0.996629171401053</v>
       </c>
       <c r="AB25">
-        <v>67.585922801431252</v>
+        <v>61.798524314027716</v>
       </c>
       <c r="AD25" t="s">
         <v>287</v>
@@ -8929,16 +8932,16 @@
         <v>426</v>
       </c>
       <c r="AM25" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="AN25" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="AO25">
-        <v>0.99475386493829931</v>
+        <v>0.99501745221162918</v>
       </c>
       <c r="AP25">
-        <v>96.179142797845941</v>
+        <v>91.346709453464783</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -9003,16 +9006,16 @@
         <v>320</v>
       </c>
       <c r="Y26" t="s">
-        <v>254</v>
+        <v>275</v>
       </c>
       <c r="Z26" t="s">
         <v>379</v>
       </c>
       <c r="AA26">
-        <v>0.99832768028365393</v>
+        <v>0.9940266623681554</v>
       </c>
       <c r="AB26">
-        <v>30.659194799678048</v>
+        <v>109.51118991715018</v>
       </c>
       <c r="AD26" t="s">
         <v>287</v>
@@ -9039,16 +9042,16 @@
         <v>428</v>
       </c>
       <c r="AM26" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="AN26" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="AO26">
-        <v>0.99671794291781168</v>
+        <v>0.99698529931119073</v>
       </c>
       <c r="AP26">
-        <v>60.171046506785672</v>
+        <v>55.269512628170503</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -9113,16 +9116,16 @@
         <v>322</v>
       </c>
       <c r="Y27" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Z27" t="s">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="AA27">
-        <v>0.99057172008573791</v>
+        <v>0.99629635001073991</v>
       </c>
       <c r="AB27">
-        <v>172.85179842813815</v>
+        <v>67.900249803101318</v>
       </c>
       <c r="AD27" t="s">
         <v>287</v>
@@ -9149,16 +9152,16 @@
         <v>430</v>
       </c>
       <c r="AM27" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="AN27" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="AO27">
-        <v>0.98839759805196303</v>
+        <v>0.99178855761800622</v>
       </c>
       <c r="AP27">
-        <v>212.71070238067816</v>
+        <v>150.54311033655213</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -9223,16 +9226,16 @@
         <v>324</v>
       </c>
       <c r="Y28" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Z28" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AA28">
-        <v>0.99095032933880767</v>
+        <v>0.99383936956194807</v>
       </c>
       <c r="AB28">
-        <v>165.91062878852651</v>
+        <v>112.94489136428538</v>
       </c>
       <c r="AD28" t="s">
         <v>287</v>
@@ -9259,16 +9262,16 @@
         <v>432</v>
       </c>
       <c r="AM28" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="AN28" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="AO28">
-        <v>0.9964390810242717</v>
+        <v>0.99296304108660982</v>
       </c>
       <c r="AP28">
-        <v>65.283514555019096</v>
+        <v>129.01091341215286</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9333,16 +9336,16 @@
         <v>326</v>
       </c>
       <c r="Y29" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="Z29" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AA29">
-        <v>0.99605704806429607</v>
+        <v>0.98416398409272543</v>
       </c>
       <c r="AB29">
-        <v>72.28745215457208</v>
+        <v>290.32695830003399</v>
       </c>
       <c r="AD29" t="s">
         <v>287</v>
@@ -9369,16 +9372,16 @@
         <v>434</v>
       </c>
       <c r="AM29" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="AN29" t="s">
-        <v>391</v>
+        <v>483</v>
       </c>
       <c r="AO29">
-        <v>0.99592873360628342</v>
+        <v>0.99152317643653909</v>
       </c>
       <c r="AP29">
-        <v>74.639883884803922</v>
+        <v>155.40843199678267</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9443,16 +9446,16 @@
         <v>328</v>
       </c>
       <c r="Y30" t="s">
-        <v>278</v>
+        <v>250</v>
       </c>
       <c r="Z30" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AA30">
-        <v>0.99167914755584141</v>
+        <v>0.99732710525923551</v>
       </c>
       <c r="AB30">
-        <v>152.54896147624135</v>
+        <v>49.003070247349498</v>
       </c>
       <c r="AD30" t="s">
         <v>287</v>
@@ -9479,16 +9482,16 @@
         <v>436</v>
       </c>
       <c r="AM30" t="s">
+        <v>484</v>
+      </c>
+      <c r="AN30" t="s">
         <v>485</v>
       </c>
-      <c r="AN30" t="s">
-        <v>486</v>
-      </c>
       <c r="AO30">
-        <v>0.99534990870245532</v>
+        <v>0.99475386493829931</v>
       </c>
       <c r="AP30">
-        <v>85.251673788320105</v>
+        <v>96.179142797845941</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -9553,16 +9556,16 @@
         <v>330</v>
       </c>
       <c r="Y31" t="s">
-        <v>284</v>
+        <v>262</v>
       </c>
       <c r="Z31" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AA31">
-        <v>0.99514004796050048</v>
+        <v>0.99601914721828588</v>
       </c>
       <c r="AB31">
-        <v>89.099120724157018</v>
+        <v>72.982300998092228</v>
       </c>
       <c r="AD31" t="s">
         <v>287</v>
@@ -9589,16 +9592,16 @@
         <v>438</v>
       </c>
       <c r="AM31" t="s">
+        <v>486</v>
+      </c>
+      <c r="AN31" t="s">
         <v>487</v>
       </c>
-      <c r="AN31" t="s">
-        <v>488</v>
-      </c>
       <c r="AO31">
-        <v>0.99283555585293171</v>
+        <v>0.99562035686170025</v>
       </c>
       <c r="AP31">
-        <v>131.34814269625272</v>
+        <v>80.293457535494625</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -9663,16 +9666,16 @@
         <v>332</v>
       </c>
       <c r="Y32" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="Z32" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AA32">
-        <v>0.99589467345586935</v>
+        <v>0.99403967905190227</v>
       </c>
       <c r="AB32">
-        <v>75.264319975727958</v>
+        <v>109.27255071512499</v>
       </c>
       <c r="AD32" t="s">
         <v>287</v>
@@ -9699,16 +9702,16 @@
         <v>440</v>
       </c>
       <c r="AM32" t="s">
+        <v>488</v>
+      </c>
+      <c r="AN32" t="s">
         <v>489</v>
       </c>
-      <c r="AN32" t="s">
-        <v>396</v>
-      </c>
       <c r="AO32">
-        <v>0.99354454384798807</v>
+        <v>0.98839759805196303</v>
       </c>
       <c r="AP32">
-        <v>118.35002945355123</v>
+        <v>212.71070238067816</v>
       </c>
     </row>
     <row r="33" spans="2:42">
@@ -9773,16 +9776,16 @@
         <v>334</v>
       </c>
       <c r="Y33" t="s">
-        <v>258</v>
+        <v>284</v>
       </c>
       <c r="Z33" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AA33">
-        <v>0.99884992726149324</v>
+        <v>0.99514004796050048</v>
       </c>
       <c r="AB33">
-        <v>21.084666872623977</v>
+        <v>89.099120724157018</v>
       </c>
       <c r="AD33" t="s">
         <v>287</v>
@@ -9812,13 +9815,13 @@
         <v>490</v>
       </c>
       <c r="AN33" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AO33">
-        <v>0.99069345154297106</v>
+        <v>0.99671794291781168</v>
       </c>
       <c r="AP33">
-        <v>170.62005504553079</v>
+        <v>60.171046506785672</v>
       </c>
     </row>
     <row r="34" spans="2:42">
@@ -9883,16 +9886,16 @@
         <v>336</v>
       </c>
       <c r="Y34" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="Z34" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="AA34">
-        <v>0.99882431199806432</v>
+        <v>0.99589467345586935</v>
       </c>
       <c r="AB34">
-        <v>21.554280035486567</v>
+        <v>75.264319975727958</v>
       </c>
       <c r="AD34" t="s">
         <v>287</v>
@@ -9925,10 +9928,10 @@
         <v>492</v>
       </c>
       <c r="AO34">
-        <v>0.99795762496221851</v>
+        <v>0.9964390810242717</v>
       </c>
       <c r="AP34">
-        <v>37.443542359327118</v>
+        <v>65.283514555019096</v>
       </c>
     </row>
     <row r="35" spans="2:42">
@@ -9993,16 +9996,16 @@
         <v>338</v>
       </c>
       <c r="Y35" t="s">
-        <v>279</v>
+        <v>255</v>
       </c>
       <c r="Z35" t="s">
         <v>387</v>
       </c>
       <c r="AA35">
-        <v>0.99133276722560904</v>
+        <v>0.99744993905722468</v>
       </c>
       <c r="AB35">
-        <v>158.89926753050145</v>
+        <v>46.751117284213812</v>
       </c>
       <c r="AD35" t="s">
         <v>287</v>
@@ -10032,13 +10035,13 @@
         <v>493</v>
       </c>
       <c r="AN35" t="s">
-        <v>465</v>
+        <v>375</v>
       </c>
       <c r="AO35">
-        <v>0.99582871194680656</v>
+        <v>0.99592873360628342</v>
       </c>
       <c r="AP35">
-        <v>76.473614308545862</v>
+        <v>74.639883884803922</v>
       </c>
     </row>
     <row r="36" spans="2:42">
@@ -10103,16 +10106,16 @@
         <v>340</v>
       </c>
       <c r="Y36" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Z36" t="s">
         <v>388</v>
       </c>
       <c r="AA36">
-        <v>0.99728758220200375</v>
+        <v>0.99723470592138874</v>
       </c>
       <c r="AB36">
-        <v>49.727659629930621</v>
+        <v>50.697058107873339</v>
       </c>
       <c r="AD36" t="s">
         <v>287</v>
@@ -10145,10 +10148,10 @@
         <v>495</v>
       </c>
       <c r="AO36">
-        <v>0.99555964959117016</v>
+        <v>0.99534990870245532</v>
       </c>
       <c r="AP36">
-        <v>81.406424161880452</v>
+        <v>85.251673788320105</v>
       </c>
     </row>
     <row r="37" spans="2:42">
@@ -10213,16 +10216,16 @@
         <v>342</v>
       </c>
       <c r="Y37" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Z37" t="s">
         <v>389</v>
       </c>
       <c r="AA37">
-        <v>0.99744993905722468</v>
+        <v>0.99750455285561002</v>
       </c>
       <c r="AB37">
-        <v>46.751117284213812</v>
+        <v>45.749864313816033</v>
       </c>
       <c r="AD37" t="s">
         <v>287</v>
@@ -10255,10 +10258,10 @@
         <v>497</v>
       </c>
       <c r="AO37">
-        <v>0.99429686126958916</v>
+        <v>0.99283555585293171</v>
       </c>
       <c r="AP37">
-        <v>104.55754339086491</v>
+        <v>131.34814269625272</v>
       </c>
     </row>
     <row r="38" spans="2:42">
@@ -10323,16 +10326,16 @@
         <v>344</v>
       </c>
       <c r="Y38" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="Z38" t="s">
         <v>390</v>
       </c>
       <c r="AA38">
-        <v>0.9963457067026108</v>
+        <v>0.993124380119488</v>
       </c>
       <c r="AB38">
-        <v>66.99537711880258</v>
+        <v>126.05303114271953</v>
       </c>
     </row>
     <row r="39" spans="2:42">
@@ -10397,16 +10400,16 @@
         <v>346</v>
       </c>
       <c r="Y39" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="Z39" t="s">
         <v>391</v>
       </c>
       <c r="AA39">
-        <v>0.99644641159652714</v>
+        <v>0.99769438809486533</v>
       </c>
       <c r="AB39">
-        <v>65.149120730335611</v>
+        <v>42.269551594135834</v>
       </c>
     </row>
     <row r="40" spans="2:42">
@@ -10471,16 +10474,16 @@
         <v>348</v>
       </c>
       <c r="Y40" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="Z40" t="s">
         <v>392</v>
       </c>
       <c r="AA40">
-        <v>0.99436579068013853</v>
+        <v>0.99489048613238573</v>
       </c>
       <c r="AB40">
-        <v>103.29383753079337</v>
+        <v>93.674420906261602</v>
       </c>
     </row>
     <row r="41" spans="2:42">
@@ -10545,16 +10548,16 @@
         <v>350</v>
       </c>
       <c r="Y41" t="s">
-        <v>266</v>
+        <v>282</v>
       </c>
       <c r="Z41" t="s">
         <v>393</v>
       </c>
       <c r="AA41">
-        <v>0.99262439568706373</v>
+        <v>0.99642867204968677</v>
       </c>
       <c r="AB41">
-        <v>135.21941240383219</v>
+        <v>65.474345755743457</v>
       </c>
     </row>
     <row r="42" spans="2:42">
@@ -10619,16 +10622,16 @@
         <v>352</v>
       </c>
       <c r="Y42" t="s">
-        <v>285</v>
+        <v>256</v>
       </c>
       <c r="Z42" t="s">
         <v>394</v>
       </c>
       <c r="AA42">
-        <v>0.996629171401053</v>
+        <v>0.99605704806429607</v>
       </c>
       <c r="AB42">
-        <v>61.798524314027716</v>
+        <v>72.28745215457208</v>
       </c>
     </row>
     <row r="43" spans="2:42">
@@ -10693,16 +10696,16 @@
         <v>354</v>
       </c>
       <c r="Y43" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Z43" t="s">
         <v>395</v>
       </c>
       <c r="AA43">
-        <v>0.9940266623681554</v>
+        <v>0.99167914755584141</v>
       </c>
       <c r="AB43">
-        <v>109.51118991715018</v>
+        <v>152.54896147624135</v>
       </c>
     </row>
     <row r="44" spans="2:42">
@@ -10767,16 +10770,16 @@
         <v>356</v>
       </c>
       <c r="Y44" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="Z44" t="s">
         <v>396</v>
       </c>
       <c r="AA44">
-        <v>0.99629635001073991</v>
+        <v>0.99339354842512728</v>
       </c>
       <c r="AB44">
-        <v>67.900249803101318</v>
+        <v>121.1182788726671</v>
       </c>
     </row>
     <row r="45" spans="2:42">
@@ -10841,16 +10844,16 @@
         <v>358</v>
       </c>
       <c r="Y45" t="s">
-        <v>276</v>
+        <v>259</v>
       </c>
       <c r="Z45" t="s">
         <v>397</v>
       </c>
       <c r="AA45">
-        <v>0.99383936956194807</v>
+        <v>0.99805028151894915</v>
       </c>
       <c r="AB45">
-        <v>112.94489136428538</v>
+        <v>35.744838819266263</v>
       </c>
     </row>
     <row r="46" spans="2:42">
@@ -10915,16 +10918,16 @@
         <v>360</v>
       </c>
       <c r="Y46" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="Z46" t="s">
-        <v>384</v>
+        <v>370</v>
       </c>
       <c r="AA46">
-        <v>0.98416398409272543</v>
+        <v>0.98395338050941106</v>
       </c>
       <c r="AB46">
-        <v>290.32695830003399</v>
+        <v>294.18802399413073</v>
       </c>
     </row>
   </sheetData>
@@ -10933,7 +10936,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE9FCA86-FCC6-4D58-868C-61ADA2549298}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B2E1F52-E250-4FB5-BE2D-804E82B1F9E4}">
   <dimension ref="B9:Z37"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -11045,7 +11048,7 @@
         <v>535</v>
       </c>
       <c r="K11" t="s">
-        <v>490</v>
+        <v>464</v>
       </c>
       <c r="L11">
         <v>10.088237612202811</v>
@@ -11078,7 +11081,7 @@
         <v>589</v>
       </c>
       <c r="X11" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="Y11">
         <v>0.16350000000000001</v>
@@ -11113,7 +11116,7 @@
         <v>537</v>
       </c>
       <c r="K12" t="s">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="L12">
         <v>4.7527038630847755</v>
@@ -11146,7 +11149,7 @@
         <v>591</v>
       </c>
       <c r="X12" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="Y12">
         <v>13.40025</v>
@@ -11181,7 +11184,7 @@
         <v>539</v>
       </c>
       <c r="K13" t="s">
-        <v>479</v>
+        <v>490</v>
       </c>
       <c r="L13">
         <v>1.4400913107240583</v>
@@ -11214,7 +11217,7 @@
         <v>593</v>
       </c>
       <c r="X13" t="s">
-        <v>519</v>
+        <v>533</v>
       </c>
       <c r="Y13">
         <v>8.4097500000000007</v>
@@ -11249,7 +11252,7 @@
         <v>541</v>
       </c>
       <c r="K14" t="s">
-        <v>489</v>
+        <v>463</v>
       </c>
       <c r="L14">
         <v>1.437273477445641</v>
@@ -11282,7 +11285,7 @@
         <v>595</v>
       </c>
       <c r="X14" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="Y14">
         <v>14.358750000000001</v>
@@ -11317,7 +11320,7 @@
         <v>543</v>
       </c>
       <c r="K15" t="s">
-        <v>469</v>
+        <v>486</v>
       </c>
       <c r="L15">
         <v>2.1922713563210485</v>
@@ -11350,7 +11353,7 @@
         <v>597</v>
       </c>
       <c r="X15" t="s">
-        <v>533</v>
+        <v>519</v>
       </c>
       <c r="Y15">
         <v>12.78825</v>
@@ -11385,7 +11388,7 @@
         <v>545</v>
       </c>
       <c r="K16" t="s">
-        <v>496</v>
+        <v>469</v>
       </c>
       <c r="L16">
         <v>0.73811583011208182</v>
@@ -11418,7 +11421,7 @@
         <v>599</v>
       </c>
       <c r="X16" t="s">
-        <v>534</v>
+        <v>521</v>
       </c>
       <c r="Y16">
         <v>24.802499999999998</v>
@@ -11453,7 +11456,7 @@
         <v>547</v>
       </c>
       <c r="K17" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="L17">
         <v>5.5236145427785717</v>
@@ -11486,7 +11489,7 @@
         <v>601</v>
       </c>
       <c r="X17" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="Y17">
         <v>8.6609999999999996</v>
@@ -11521,7 +11524,7 @@
         <v>549</v>
       </c>
       <c r="K18" t="s">
-        <v>491</v>
+        <v>457</v>
       </c>
       <c r="L18">
         <v>5.5488357050452785E-3</v>
@@ -11589,7 +11592,7 @@
         <v>551</v>
       </c>
       <c r="K19" t="s">
-        <v>482</v>
+        <v>491</v>
       </c>
       <c r="L19">
         <v>6.6811161360847313</v>
@@ -11622,7 +11625,7 @@
         <v>605</v>
       </c>
       <c r="X19" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="Y19">
         <v>1.7250000000000001E-2</v>
@@ -11690,7 +11693,7 @@
         <v>607</v>
       </c>
       <c r="X20" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="Y20">
         <v>6.8624999999999998</v>
@@ -11725,7 +11728,7 @@
         <v>555</v>
       </c>
       <c r="K21" t="s">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="L21">
         <v>1.3529085560597105</v>
@@ -11760,7 +11763,7 @@
         <v>557</v>
       </c>
       <c r="K22" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="L22">
         <v>3.7088360788644938</v>
@@ -11795,7 +11798,7 @@
         <v>559</v>
       </c>
       <c r="K23" t="s">
-        <v>452</v>
+        <v>471</v>
       </c>
       <c r="L23">
         <v>13.683903390107789</v>
@@ -11830,7 +11833,7 @@
         <v>561</v>
       </c>
       <c r="K24" t="s">
-        <v>493</v>
+        <v>459</v>
       </c>
       <c r="L24">
         <v>5.4676081362262012</v>
@@ -11865,7 +11868,7 @@
         <v>563</v>
       </c>
       <c r="K25" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="L25">
         <v>8.9064794695455216</v>
@@ -11900,7 +11903,7 @@
         <v>565</v>
       </c>
       <c r="K26" t="s">
-        <v>458</v>
+        <v>477</v>
       </c>
       <c r="L26">
         <v>14.189229081738485</v>
@@ -11935,7 +11938,7 @@
         <v>567</v>
       </c>
       <c r="K27" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="L27">
         <v>10.717982842540293</v>
@@ -11970,7 +11973,7 @@
         <v>569</v>
       </c>
       <c r="K28" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="L28">
         <v>9.6743476082482847</v>
@@ -12040,7 +12043,7 @@
         <v>573</v>
       </c>
       <c r="K30" t="s">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c r="L30">
         <v>5.8372174437039801</v>
@@ -12075,7 +12078,7 @@
         <v>575</v>
       </c>
       <c r="K31" t="s">
-        <v>494</v>
+        <v>461</v>
       </c>
       <c r="L31">
         <v>1.8845590125315521</v>
@@ -12110,7 +12113,7 @@
         <v>577</v>
       </c>
       <c r="K32" t="s">
-        <v>484</v>
+        <v>493</v>
       </c>
       <c r="L32">
         <v>7.179650801796102</v>
@@ -12145,7 +12148,7 @@
         <v>579</v>
       </c>
       <c r="K33" t="s">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="L33">
         <v>14.559476964149322</v>
@@ -12180,7 +12183,7 @@
         <v>581</v>
       </c>
       <c r="K34" t="s">
-        <v>456</v>
+        <v>475</v>
       </c>
       <c r="L34">
         <v>1.3536151515148049</v>
@@ -12215,7 +12218,7 @@
         <v>583</v>
       </c>
       <c r="K35" t="s">
-        <v>454</v>
+        <v>473</v>
       </c>
       <c r="L35">
         <v>4.820514286595051</v>
@@ -12250,7 +12253,7 @@
         <v>585</v>
       </c>
       <c r="K36" t="s">
-        <v>487</v>
+        <v>496</v>
       </c>
       <c r="L36">
         <v>8.1474073379531564</v>
@@ -12285,7 +12288,7 @@
         <v>587</v>
       </c>
       <c r="K37" t="s">
-        <v>485</v>
+        <v>494</v>
       </c>
       <c r="L37">
         <v>9.9689850956014183</v>
@@ -12300,7 +12303,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A0FA040-256E-4DAA-9D4A-1B0CDB366AFD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43C8E981-C887-472F-A6FC-78226CDA79D0}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_NGA_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_NGA_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NGA_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D07A35F9-5AD4-424A-B7C2-AD2948EC71FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71EC37CB-4556-4746-A103-B99E1EF4FF09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misc" sheetId="7" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2191" uniqueCount="633">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2192" uniqueCount="634">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -2026,6 +2026,9 @@
   </si>
   <si>
     <t>e_NG10-330,e_w559542338-330,e_w669957212-330,e_w706082453-330,e_w746582404-330</t>
+  </si>
+  <si>
+    <t>ELC_BatIn</t>
   </si>
 </sst>
 </file>
@@ -5433,9 +5436,8 @@
     <row r="8" spans="2:25" ht="17.649999999999999">
       <c r="B8" s="20"/>
       <c r="E8" s="26"/>
-      <c r="F8" t="str">
-        <f>C5</f>
-        <v>ELC</v>
+      <c r="F8" t="s">
+        <v>633</v>
       </c>
       <c r="G8" t="str">
         <f>E7</f>

--- a/VerveStacks_NGA_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_NGA_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NGA_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0468281A-993D-46DE-ABED-5EE5151BCBFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D1538259-833C-423A-BD2A-4B97CC84B8F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -996,28 +996,118 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_035</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_034</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_032</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_023</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 23</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
   </si>
   <si>
     <t>distr_solelc_spv_006</t>
@@ -1026,30 +1116,6 @@
     <t>connecting solar to buses in cluster 6</t>
   </si>
   <si>
-    <t>distr_solelc_spv_034</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_036</t>
   </si>
   <si>
@@ -1080,6 +1146,48 @@
     <t>connecting solar to buses in cluster 15</t>
   </si>
   <si>
+    <t>distr_solelc_spv_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_033</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 33</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_002</t>
   </si>
   <si>
@@ -1092,36 +1200,6 @@
     <t>connecting solar to buses in cluster 8</t>
   </si>
   <si>
-    <t>distr_solelc_spv_032</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_001</t>
   </si>
   <si>
@@ -1140,114 +1218,69 @@
     <t>connecting solar to buses in cluster 14</t>
   </si>
   <si>
-    <t>distr_solelc_spv_035</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_033</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_NG18-330,e_w746582404-330,e_NG17-330</t>
+  </si>
+  <si>
+    <t>e_w564430566-330,e_w564429999-330</t>
+  </si>
+  <si>
+    <t>e_w108020974-330,e_w836122563-330,e_w559542338-330,e_NG9-330,e_w669957212-330,e_w1324578567-330,e_w565866986-330</t>
+  </si>
+  <si>
+    <t>e_NG8-330,e_w564445207-330,e_w1328602766-330</t>
+  </si>
+  <si>
+    <t>e_w564410486-330,e_w1226249784-330</t>
+  </si>
+  <si>
+    <t>e_NG13-330,e_NG15-330,e_w1057700475-330,e_w215459565-330,e_w671893504-330,e_w548724506-330,e_NG12-330</t>
+  </si>
+  <si>
+    <t>e_w695826179-330</t>
+  </si>
+  <si>
+    <t>e_w267122040-330</t>
+  </si>
+  <si>
+    <t>e_NG6-330,e_NG7-330,e_NG3-330,e_w565486405-330</t>
+  </si>
+  <si>
+    <t>e_w1226249784-330,e_NG1-330,e_NG2-330,e_w395182311-330</t>
+  </si>
+  <si>
+    <t>e_w266712817-330,e_w563723584-330,e_w267122040-330,e_w655273140-330</t>
+  </si>
+  <si>
+    <t>e_w563723584-330,e_w655273140-330</t>
+  </si>
+  <si>
+    <t>e_w695826179-330,e_w564410486-330,e_NG3-330,e_w556550171-330,e_w39469643-330</t>
+  </si>
+  <si>
+    <t>e_w546666333-330,e_NG17-330,e_w575706869-330</t>
+  </si>
+  <si>
+    <t>e_w565081403-330,e_w267122040-330</t>
+  </si>
+  <si>
     <t>e_w215459565-330,e_w563715917-330,e_w548724506-330,e_w565081403-330</t>
   </si>
   <si>
-    <t>e_NG18-330,e_w746582404-330,e_NG17-330</t>
-  </si>
-  <si>
-    <t>e_w564430566-330,e_w564429999-330</t>
+    <t>e_w564430566-330</t>
+  </si>
+  <si>
+    <t>e_NG2-330,e_NG1-330,e_w395182311-330,e_w563723584-330</t>
   </si>
   <si>
     <t>e_w546666333-330,e_w565866986-330,e_NG18-330</t>
   </si>
   <si>
-    <t>e_NG6-330,e_NG7-330,e_NG3-330,e_w565486405-330</t>
-  </si>
-  <si>
-    <t>e_w1226249784-330,e_NG1-330,e_NG2-330,e_w395182311-330</t>
-  </si>
-  <si>
-    <t>e_w266712817-330,e_w563723584-330,e_w267122040-330,e_w655273140-330</t>
-  </si>
-  <si>
-    <t>e_w563723584-330,e_w655273140-330</t>
-  </si>
-  <si>
     <t>e_w1328602766-330,e_w695826179-330,e_w540463591-330,e_w481286430-330</t>
   </si>
   <si>
@@ -1260,7 +1293,22 @@
     <t>e_w266617120-330,e_w395182311-330,e_w266712817-330,e_w563723584-330</t>
   </si>
   <si>
-    <t>e_w267122040-330</t>
+    <t>e_w565866986-330,e_NG11-330,e_w574152484-330</t>
+  </si>
+  <si>
+    <t>e_w565081403-330,e_w266617120-330,e_w266712817-330,e_w267122040-330</t>
+  </si>
+  <si>
+    <t>e_w564410486-330,e_w695826179-330,e_w39469643-330,e_w1226249784-330</t>
+  </si>
+  <si>
+    <t>e_w565486405-330,e_NG3-330,e_NG4-330,e_NG5-330,e_w565847437-330</t>
+  </si>
+  <si>
+    <t>e_w563715917-330,e_NG5-330,e_w565081403-330</t>
+  </si>
+  <si>
+    <t>e_w556550171-330,e_w39469643-330,e_w266617120-330</t>
   </si>
   <si>
     <t>e_w1328602766-330,e_NG6-330</t>
@@ -1269,21 +1317,6 @@
     <t>e_w746582404-330,e_w563732518-330,e_NG20-330,e_NG21-330,e_w334825256-330,e_w564429999-330</t>
   </si>
   <si>
-    <t>e_w695826179-330,e_w564410486-330,e_NG3-330,e_w556550171-330,e_w39469643-330</t>
-  </si>
-  <si>
-    <t>e_w546666333-330,e_NG17-330,e_w575706869-330</t>
-  </si>
-  <si>
-    <t>e_w565081403-330,e_w267122040-330</t>
-  </si>
-  <si>
-    <t>e_w564430566-330</t>
-  </si>
-  <si>
-    <t>e_NG2-330,e_NG1-330,e_w395182311-330,e_w563723584-330</t>
-  </si>
-  <si>
     <t>e_w564445207-330,e_w477596994-330,e_w565866986-330,e_NG11-330,e_w574152484-330,e_w215459565-330</t>
   </si>
   <si>
@@ -1293,37 +1326,112 @@
     <t>e_NG12-330,e_w565081403-330,e_w564429999-330</t>
   </si>
   <si>
-    <t>e_w695826179-330</t>
-  </si>
-  <si>
-    <t>e_w564410486-330,e_w695826179-330,e_w39469643-330,e_w1226249784-330</t>
-  </si>
-  <si>
-    <t>e_w565486405-330,e_NG3-330,e_NG4-330,e_NG5-330,e_w565847437-330</t>
-  </si>
-  <si>
-    <t>e_w563715917-330,e_NG5-330,e_w565081403-330</t>
-  </si>
-  <si>
-    <t>e_w556550171-330,e_w39469643-330,e_w266617120-330</t>
-  </si>
-  <si>
-    <t>e_w108020974-330,e_w836122563-330,e_w559542338-330,e_NG9-330,e_w669957212-330,e_w1324578567-330,e_w565866986-330</t>
-  </si>
-  <si>
-    <t>e_NG8-330,e_w564445207-330,e_w1328602766-330</t>
-  </si>
-  <si>
-    <t>e_w564410486-330,e_w1226249784-330</t>
-  </si>
-  <si>
-    <t>e_NG13-330,e_NG15-330,e_w1057700475-330,e_w215459565-330,e_w671893504-330,e_w548724506-330,e_NG12-330</t>
-  </si>
-  <si>
-    <t>e_w565866986-330,e_NG11-330,e_w574152484-330</t>
-  </si>
-  <si>
-    <t>e_w565081403-330,e_w266617120-330,e_w266712817-330,e_w267122040-330</t>
+    <t>distr_wonelc_won_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
   </si>
   <si>
     <t>distr_wonelc_won_015</t>
@@ -1344,108 +1452,12 @@
     <t>connecting wind onshore to buses in cluster 19</t>
   </si>
   <si>
-    <t>distr_wonelc_won_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_006</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 6</t>
   </si>
   <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_011</t>
   </si>
   <si>
@@ -1476,24 +1488,99 @@
     <t>connecting wind onshore to buses in cluster 5</t>
   </si>
   <si>
-    <t>distr_wonelc_won_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>e_NG3-330,e_w556550171-330,e_w39469643-330</t>
+  </si>
+  <si>
+    <t>elc_won_022</t>
+  </si>
+  <si>
+    <t>elc_won_027</t>
+  </si>
+  <si>
+    <t>e_w266617120-330,e_w266712817-330,e_w267122040-330</t>
+  </si>
+  <si>
+    <t>elc_won_026</t>
+  </si>
+  <si>
+    <t>e_w266712817-330,e_w267122040-330,e_w655273140-330</t>
+  </si>
+  <si>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>e_w108020974-330</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>e_w564410486-330</t>
+  </si>
+  <si>
+    <t>elc_won_021</t>
+  </si>
+  <si>
+    <t>e_w266617120-330,e_w266712817-330</t>
+  </si>
+  <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>elc_won_013</t>
+  </si>
+  <si>
+    <t>e_w564410486-330,e_w39469643-330,e_w1226249784-330,e_NG1-330,e_NG2-330</t>
+  </si>
+  <si>
+    <t>elc_won_025</t>
+  </si>
+  <si>
+    <t>e_w395182311-330,e_NG2-330,e_w266617120-330</t>
+  </si>
+  <si>
+    <t>elc_won_024</t>
+  </si>
+  <si>
+    <t>e_w266617120-330,e_w395182311-330</t>
+  </si>
+  <si>
+    <t>elc_won_016</t>
+  </si>
+  <si>
+    <t>elc_won_018</t>
+  </si>
+  <si>
+    <t>e_w395182311-330,e_w563723584-330</t>
+  </si>
+  <si>
+    <t>elc_won_007</t>
+  </si>
+  <si>
+    <t>e_w1328602766-330,e_w540463591-330,e_NG6-330,e_w477596994-330,e_NG7-330</t>
+  </si>
+  <si>
+    <t>elc_won_012</t>
+  </si>
+  <si>
+    <t>e_w564410486-330,e_w695826179-330</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>elc_won_002</t>
   </si>
   <si>
     <t>elc_won_015</t>
   </si>
   <si>
-    <t>e_w564410486-330</t>
-  </si>
-  <si>
     <t>elc_won_010</t>
   </si>
   <si>
@@ -1503,90 +1590,12 @@
     <t>elc_won_019</t>
   </si>
   <si>
-    <t>elc_won_013</t>
-  </si>
-  <si>
-    <t>e_w564410486-330,e_w39469643-330,e_w1226249784-330,e_NG1-330,e_NG2-330</t>
-  </si>
-  <si>
-    <t>elc_won_025</t>
-  </si>
-  <si>
-    <t>e_w395182311-330,e_NG2-330,e_w266617120-330</t>
-  </si>
-  <si>
-    <t>elc_won_024</t>
-  </si>
-  <si>
-    <t>e_w266617120-330,e_w395182311-330</t>
-  </si>
-  <si>
-    <t>elc_won_016</t>
-  </si>
-  <si>
     <t>elc_won_006</t>
   </si>
   <si>
     <t>e_w695826179-330,e_w1328602766-330,e_w540463591-330</t>
   </si>
   <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>e_NG3-330,e_w556550171-330,e_w39469643-330</t>
-  </si>
-  <si>
-    <t>elc_won_022</t>
-  </si>
-  <si>
-    <t>elc_won_027</t>
-  </si>
-  <si>
-    <t>e_w266617120-330,e_w266712817-330,e_w267122040-330</t>
-  </si>
-  <si>
-    <t>elc_won_026</t>
-  </si>
-  <si>
-    <t>e_w266712817-330,e_w267122040-330,e_w655273140-330</t>
-  </si>
-  <si>
-    <t>elc_won_002</t>
-  </si>
-  <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>e_w108020974-330</t>
-  </si>
-  <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>elc_won_021</t>
-  </si>
-  <si>
-    <t>e_w266617120-330,e_w266712817-330</t>
-  </si>
-  <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
-    <t>e_w1328602766-330,e_w540463591-330,e_NG6-330,e_w477596994-330,e_NG7-330</t>
-  </si>
-  <si>
-    <t>elc_won_012</t>
-  </si>
-  <si>
-    <t>e_w564410486-330,e_w695826179-330</t>
-  </si>
-  <si>
     <t>elc_won_011</t>
   </si>
   <si>
@@ -1617,13 +1626,22 @@
     <t>e_w548724506-330,e_w563715917-330,e_w565081403-330</t>
   </si>
   <si>
-    <t>elc_won_003</t>
-  </si>
-  <si>
-    <t>elc_won_018</t>
-  </si>
-  <si>
-    <t>e_w395182311-330,e_w563723584-330</t>
+    <t>distr_wofelc_wof_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
   </si>
   <si>
     <t>distr_wofelc_wof_002</t>
@@ -1632,6 +1650,30 @@
     <t>connecting wind offshore to buses in cluster 2</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_004</t>
   </si>
   <si>
@@ -1644,46 +1686,19 @@
     <t>connecting wind offshore to buses in cluster 7</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
+    <t>e_NG18-330</t>
+  </si>
+  <si>
+    <t>elc_wof_010</t>
+  </si>
+  <si>
+    <t>e_NG18-330,e_w746582404-330</t>
+  </si>
+  <si>
+    <t>elc_wof_008</t>
   </si>
   <si>
     <t>elc_wof_002</t>
@@ -1692,6 +1707,24 @@
     <t>e_w706082453-330,e_w108020974-330,e_w559542338-330,e_w565866986-330,e_w546666333-330</t>
   </si>
   <si>
+    <t>elc_wof_005</t>
+  </si>
+  <si>
+    <t>elc_wof_006</t>
+  </si>
+  <si>
+    <t>e_w746582404-330</t>
+  </si>
+  <si>
+    <t>elc_wof_001</t>
+  </si>
+  <si>
+    <t>e_NG9-330,e_w1324578567-330,e_w565866986-330</t>
+  </si>
+  <si>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
     <t>elc_wof_004</t>
   </si>
   <si>
@@ -1702,39 +1735,6 @@
   </si>
   <si>
     <t>e_w746582404-330,e_w564430566-330</t>
-  </si>
-  <si>
-    <t>elc_wof_001</t>
-  </si>
-  <si>
-    <t>e_NG9-330,e_w1324578567-330,e_w565866986-330</t>
-  </si>
-  <si>
-    <t>elc_wof_005</t>
-  </si>
-  <si>
-    <t>e_NG18-330,e_w746582404-330</t>
-  </si>
-  <si>
-    <t>elc_wof_006</t>
-  </si>
-  <si>
-    <t>e_w746582404-330</t>
-  </si>
-  <si>
-    <t>elc_wof_003</t>
-  </si>
-  <si>
-    <t>e_NG18-330</t>
-  </si>
-  <si>
-    <t>elc_wof_009</t>
-  </si>
-  <si>
-    <t>elc_wof_008</t>
-  </si>
-  <si>
-    <t>elc_wof_010</t>
   </si>
   <si>
     <t>e_won_001</t>
@@ -6760,7 +6760,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58EF654F-100F-4B4A-8516-78C36C6A4BB2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFE3BF03-E18A-4BA6-9453-C46036847123}">
   <dimension ref="B9:BD46"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6998,16 +6998,16 @@
         <v>289</v>
       </c>
       <c r="Y11" t="s">
-        <v>273</v>
+        <v>259</v>
       </c>
       <c r="Z11" t="s">
         <v>365</v>
       </c>
       <c r="AA11">
-        <v>0.99655017109874156</v>
+        <v>0.99884992726149324</v>
       </c>
       <c r="AB11">
-        <v>63.246863189739024</v>
+        <v>21.084666872623977</v>
       </c>
       <c r="AD11" t="s">
         <v>288</v>
@@ -7040,10 +7040,10 @@
         <v>454</v>
       </c>
       <c r="AO11">
-        <v>0.9933445384762607</v>
+        <v>0.9964390810242717</v>
       </c>
       <c r="AP11">
-        <v>122.01679460188713</v>
+        <v>65.283514555019096</v>
       </c>
       <c r="AR11" t="s">
         <v>288</v>
@@ -7076,10 +7076,10 @@
         <v>520</v>
       </c>
       <c r="BC11">
-        <v>0.9962053430710629</v>
+        <v>0.99174031680019514</v>
       </c>
       <c r="BD11">
-        <v>69.568710363846861</v>
+        <v>151.42752532975524</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7144,16 +7144,16 @@
         <v>293</v>
       </c>
       <c r="Y12" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Z12" t="s">
         <v>366</v>
       </c>
       <c r="AA12">
-        <v>0.99884992726149324</v>
+        <v>0.99882431199806432</v>
       </c>
       <c r="AB12">
-        <v>21.084666872623977</v>
+        <v>21.554280035486567</v>
       </c>
       <c r="AD12" t="s">
         <v>288</v>
@@ -7183,13 +7183,13 @@
         <v>455</v>
       </c>
       <c r="AN12" t="s">
-        <v>456</v>
+        <v>374</v>
       </c>
       <c r="AO12">
-        <v>0.9938298282896767</v>
+        <v>0.99592873360628342</v>
       </c>
       <c r="AP12">
-        <v>113.11981468926018</v>
+        <v>74.639883884803922</v>
       </c>
       <c r="AR12" t="s">
         <v>288</v>
@@ -7222,10 +7222,10 @@
         <v>522</v>
       </c>
       <c r="BC12">
-        <v>0.99246115999793105</v>
+        <v>0.99371472191320109</v>
       </c>
       <c r="BD12">
-        <v>138.21206670459694</v>
+        <v>115.23009825798009</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -7290,16 +7290,16 @@
         <v>295</v>
       </c>
       <c r="Y13" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="Z13" t="s">
         <v>367</v>
       </c>
       <c r="AA13">
-        <v>0.99882431199806432</v>
+        <v>0.99802162515875081</v>
       </c>
       <c r="AB13">
-        <v>21.554280035486567</v>
+        <v>36.270205422902137</v>
       </c>
       <c r="AD13" t="s">
         <v>288</v>
@@ -7326,16 +7326,16 @@
         <v>403</v>
       </c>
       <c r="AM13" t="s">
+        <v>456</v>
+      </c>
+      <c r="AN13" t="s">
         <v>457</v>
       </c>
-      <c r="AN13" t="s">
-        <v>372</v>
-      </c>
       <c r="AO13">
-        <v>0.99008544123370779</v>
+        <v>0.99534990870245532</v>
       </c>
       <c r="AP13">
-        <v>181.76691071535706</v>
+        <v>85.251673788320105</v>
       </c>
       <c r="AR13" t="s">
         <v>288</v>
@@ -7365,13 +7365,13 @@
         <v>523</v>
       </c>
       <c r="BB13" t="s">
-        <v>524</v>
+        <v>381</v>
       </c>
       <c r="BC13">
-        <v>0.99268778174342398</v>
+        <v>0.99337755486839363</v>
       </c>
       <c r="BD13">
-        <v>134.05733470389279</v>
+        <v>121.41149407945062</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -7436,16 +7436,16 @@
         <v>297</v>
       </c>
       <c r="Y14" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="Z14" t="s">
         <v>368</v>
       </c>
       <c r="AA14">
-        <v>0.99744993905722468</v>
+        <v>0.99631349511992195</v>
       </c>
       <c r="AB14">
-        <v>46.751117284213812</v>
+        <v>67.585922801431252</v>
       </c>
       <c r="AD14" t="s">
         <v>288</v>
@@ -7478,10 +7478,10 @@
         <v>459</v>
       </c>
       <c r="AO14">
-        <v>0.99207403494667001</v>
+        <v>0.99283555585293171</v>
       </c>
       <c r="AP14">
-        <v>145.30935931104892</v>
+        <v>131.34814269625272</v>
       </c>
       <c r="AR14" t="s">
         <v>288</v>
@@ -7508,16 +7508,16 @@
         <v>505</v>
       </c>
       <c r="BA14" t="s">
+        <v>524</v>
+      </c>
+      <c r="BB14" t="s">
         <v>525</v>
       </c>
-      <c r="BB14" t="s">
-        <v>526</v>
-      </c>
       <c r="BC14">
-        <v>0.99794494286432878</v>
+        <v>0.9962053430710629</v>
       </c>
       <c r="BD14">
-        <v>37.67604748730637</v>
+        <v>69.568710363846861</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7582,16 +7582,16 @@
         <v>299</v>
       </c>
       <c r="Y15" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="Z15" t="s">
         <v>369</v>
       </c>
       <c r="AA15">
-        <v>0.9963457067026108</v>
+        <v>0.99133276722560904</v>
       </c>
       <c r="AB15">
-        <v>66.99537711880258</v>
+        <v>158.89926753050145</v>
       </c>
       <c r="AD15" t="s">
         <v>288</v>
@@ -7624,10 +7624,10 @@
         <v>461</v>
       </c>
       <c r="AO15">
-        <v>0.99637613831578808</v>
+        <v>0.99795762496221851</v>
       </c>
       <c r="AP15">
-        <v>66.437464210551497</v>
+        <v>37.443542359327118</v>
       </c>
       <c r="AR15" t="s">
         <v>288</v>
@@ -7654,10 +7654,10 @@
         <v>507</v>
       </c>
       <c r="BA15" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="BB15" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="BC15">
         <v>0.9888409065104441</v>
@@ -7728,16 +7728,16 @@
         <v>301</v>
       </c>
       <c r="Y16" t="s">
-        <v>278</v>
+        <v>261</v>
       </c>
       <c r="Z16" t="s">
         <v>370</v>
       </c>
       <c r="AA16">
-        <v>0.99644641159652714</v>
+        <v>0.99728758220200375</v>
       </c>
       <c r="AB16">
-        <v>65.149120730335611</v>
+        <v>49.727659629930621</v>
       </c>
       <c r="AD16" t="s">
         <v>288</v>
@@ -7770,10 +7770,10 @@
         <v>463</v>
       </c>
       <c r="AO16">
-        <v>0.99501745221162918</v>
+        <v>0.99582871194680656</v>
       </c>
       <c r="AP16">
-        <v>91.346709453464783</v>
+        <v>76.473614308545862</v>
       </c>
       <c r="AR16" t="s">
         <v>288</v>
@@ -7800,10 +7800,10 @@
         <v>509</v>
       </c>
       <c r="BA16" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="BB16" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="BC16">
         <v>0.99132158137897763</v>
@@ -7874,16 +7874,16 @@
         <v>303</v>
       </c>
       <c r="Y17" t="s">
-        <v>268</v>
+        <v>285</v>
       </c>
       <c r="Z17" t="s">
         <v>371</v>
       </c>
       <c r="AA17">
-        <v>0.99436579068013853</v>
+        <v>0.99514004796050048</v>
       </c>
       <c r="AB17">
-        <v>103.29383753079337</v>
+        <v>89.099120724157018</v>
       </c>
       <c r="AD17" t="s">
         <v>288</v>
@@ -7913,13 +7913,13 @@
         <v>464</v>
       </c>
       <c r="AN17" t="s">
-        <v>372</v>
+        <v>465</v>
       </c>
       <c r="AO17">
-        <v>0.99698529931119073</v>
+        <v>0.99555964959117016</v>
       </c>
       <c r="AP17">
-        <v>55.269512628170503</v>
+        <v>81.406424161880452</v>
       </c>
       <c r="AR17" t="s">
         <v>288</v>
@@ -7946,16 +7946,16 @@
         <v>511</v>
       </c>
       <c r="BA17" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="BB17" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="BC17">
-        <v>0.99174031680019514</v>
+        <v>0.99794494286432878</v>
       </c>
       <c r="BD17">
-        <v>151.42752532975524</v>
+        <v>37.67604748730637</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8020,16 +8020,16 @@
         <v>305</v>
       </c>
       <c r="Y18" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="Z18" t="s">
         <v>372</v>
       </c>
       <c r="AA18">
-        <v>0.99262439568706373</v>
+        <v>0.99589467345586935</v>
       </c>
       <c r="AB18">
-        <v>135.21941240383219</v>
+        <v>75.264319975727958</v>
       </c>
       <c r="AD18" t="s">
         <v>288</v>
@@ -8056,16 +8056,16 @@
         <v>413</v>
       </c>
       <c r="AM18" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AN18" t="s">
-        <v>466</v>
+        <v>386</v>
       </c>
       <c r="AO18">
-        <v>0.99429686126958916</v>
+        <v>0.99354454384798807</v>
       </c>
       <c r="AP18">
-        <v>104.55754339086491</v>
+        <v>118.35002945355123</v>
       </c>
       <c r="AR18" t="s">
         <v>288</v>
@@ -8092,10 +8092,10 @@
         <v>513</v>
       </c>
       <c r="BA18" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="BB18" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="BC18">
         <v>0.99755731205629283</v>
@@ -8166,16 +8166,16 @@
         <v>307</v>
       </c>
       <c r="Y19" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="Z19" t="s">
         <v>373</v>
       </c>
       <c r="AA19">
-        <v>0.996629171401053</v>
+        <v>0.9963457067026108</v>
       </c>
       <c r="AB19">
-        <v>61.798524314027716</v>
+        <v>66.99537711880258</v>
       </c>
       <c r="AD19" t="s">
         <v>288</v>
@@ -8205,13 +8205,13 @@
         <v>467</v>
       </c>
       <c r="AN19" t="s">
-        <v>375</v>
+        <v>389</v>
       </c>
       <c r="AO19">
-        <v>0.99354454384798807</v>
+        <v>0.99069345154297106</v>
       </c>
       <c r="AP19">
-        <v>118.35002945355123</v>
+        <v>170.62005504553079</v>
       </c>
       <c r="AR19" t="s">
         <v>288</v>
@@ -8238,16 +8238,16 @@
         <v>515</v>
       </c>
       <c r="BA19" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="BB19" t="s">
-        <v>383</v>
+        <v>533</v>
       </c>
       <c r="BC19">
-        <v>0.99337755486839363</v>
+        <v>0.99246115999793105</v>
       </c>
       <c r="BD19">
-        <v>121.41149407945062</v>
+        <v>138.21206670459694</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8312,16 +8312,16 @@
         <v>309</v>
       </c>
       <c r="Y20" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Z20" t="s">
         <v>374</v>
       </c>
       <c r="AA20">
-        <v>0.9940266623681554</v>
+        <v>0.99644641159652714</v>
       </c>
       <c r="AB20">
-        <v>109.51118991715018</v>
+        <v>65.149120730335611</v>
       </c>
       <c r="AD20" t="s">
         <v>288</v>
@@ -8351,13 +8351,13 @@
         <v>468</v>
       </c>
       <c r="AN20" t="s">
-        <v>398</v>
+        <v>469</v>
       </c>
       <c r="AO20">
-        <v>0.99069345154297106</v>
+        <v>0.99207403494667001</v>
       </c>
       <c r="AP20">
-        <v>170.62005504553079</v>
+        <v>145.30935931104892</v>
       </c>
       <c r="AR20" t="s">
         <v>288</v>
@@ -8384,16 +8384,16 @@
         <v>517</v>
       </c>
       <c r="BA20" t="s">
+        <v>534</v>
+      </c>
+      <c r="BB20" t="s">
         <v>535</v>
       </c>
-      <c r="BB20" t="s">
-        <v>528</v>
-      </c>
       <c r="BC20">
-        <v>0.99371472191320109</v>
+        <v>0.99268778174342398</v>
       </c>
       <c r="BD20">
-        <v>115.23009825798009</v>
+        <v>134.05733470389279</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -8458,16 +8458,16 @@
         <v>311</v>
       </c>
       <c r="Y21" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="Z21" t="s">
         <v>375</v>
       </c>
       <c r="AA21">
-        <v>0.99629635001073991</v>
+        <v>0.99436579068013853</v>
       </c>
       <c r="AB21">
-        <v>67.900249803101318</v>
+        <v>103.29383753079337</v>
       </c>
       <c r="AD21" t="s">
         <v>288</v>
@@ -8494,16 +8494,16 @@
         <v>419</v>
       </c>
       <c r="AM21" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AN21" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AO21">
-        <v>0.9964390810242717</v>
+        <v>0.99637613831578808</v>
       </c>
       <c r="AP21">
-        <v>65.283514555019096</v>
+        <v>66.437464210551497</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8568,16 +8568,16 @@
         <v>313</v>
       </c>
       <c r="Y22" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="Z22" t="s">
         <v>376</v>
       </c>
       <c r="AA22">
-        <v>0.99383936956194807</v>
+        <v>0.99262439568706373</v>
       </c>
       <c r="AB22">
-        <v>112.94489136428538</v>
+        <v>135.21941240383219</v>
       </c>
       <c r="AD22" t="s">
         <v>288</v>
@@ -8604,16 +8604,16 @@
         <v>421</v>
       </c>
       <c r="AM22" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AN22" t="s">
-        <v>370</v>
+        <v>473</v>
       </c>
       <c r="AO22">
-        <v>0.99592873360628342</v>
+        <v>0.99501745221162918</v>
       </c>
       <c r="AP22">
-        <v>74.639883884803922</v>
+        <v>91.346709453464783</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -8678,16 +8678,16 @@
         <v>315</v>
       </c>
       <c r="Y23" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="Z23" t="s">
         <v>377</v>
       </c>
       <c r="AA23">
-        <v>0.98416398409272543</v>
+        <v>0.99339354842512728</v>
       </c>
       <c r="AB23">
-        <v>290.32695830003399</v>
+        <v>121.1182788726671</v>
       </c>
       <c r="AD23" t="s">
         <v>288</v>
@@ -8714,16 +8714,16 @@
         <v>423</v>
       </c>
       <c r="AM23" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AN23" t="s">
-        <v>473</v>
+        <v>376</v>
       </c>
       <c r="AO23">
-        <v>0.99534990870245532</v>
+        <v>0.99698529931119073</v>
       </c>
       <c r="AP23">
-        <v>85.251673788320105</v>
+        <v>55.269512628170503</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -8788,16 +8788,16 @@
         <v>317</v>
       </c>
       <c r="Y24" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="Z24" t="s">
         <v>378</v>
       </c>
       <c r="AA24">
-        <v>0.99723470592138874</v>
+        <v>0.99805028151894915</v>
       </c>
       <c r="AB24">
-        <v>50.697058107873339</v>
+        <v>35.744838819266263</v>
       </c>
       <c r="AD24" t="s">
         <v>288</v>
@@ -8824,16 +8824,16 @@
         <v>425</v>
       </c>
       <c r="AM24" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AN24" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AO24">
-        <v>0.99283555585293171</v>
+        <v>0.98839759805196303</v>
       </c>
       <c r="AP24">
-        <v>131.34814269625272</v>
+        <v>212.71070238067816</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -8898,16 +8898,16 @@
         <v>319</v>
       </c>
       <c r="Y25" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="Z25" t="s">
         <v>379</v>
       </c>
       <c r="AA25">
-        <v>0.99750455285561002</v>
+        <v>0.98395338050941106</v>
       </c>
       <c r="AB25">
-        <v>45.749864313816033</v>
+        <v>294.18802399413073</v>
       </c>
       <c r="AD25" t="s">
         <v>288</v>
@@ -8934,16 +8934,16 @@
         <v>427</v>
       </c>
       <c r="AM25" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AN25" t="s">
-        <v>377</v>
+        <v>478</v>
       </c>
       <c r="AO25">
-        <v>0.99537626424805781</v>
+        <v>0.99740664776461363</v>
       </c>
       <c r="AP25">
-        <v>84.768488785605911</v>
+        <v>47.544790982083583</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -9008,16 +9008,16 @@
         <v>321</v>
       </c>
       <c r="Y26" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="Z26" t="s">
         <v>380</v>
       </c>
       <c r="AA26">
-        <v>0.99339354842512728</v>
+        <v>0.99655017109874156</v>
       </c>
       <c r="AB26">
-        <v>121.1182788726671</v>
+        <v>63.246863189739024</v>
       </c>
       <c r="AD26" t="s">
         <v>288</v>
@@ -9044,16 +9044,16 @@
         <v>429</v>
       </c>
       <c r="AM26" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AN26" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="AO26">
-        <v>0.99795762496221851</v>
+        <v>0.9913636988912532</v>
       </c>
       <c r="AP26">
-        <v>37.443542359327118</v>
+        <v>158.33218699369189</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -9118,16 +9118,16 @@
         <v>323</v>
       </c>
       <c r="Y27" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="Z27" t="s">
         <v>381</v>
       </c>
       <c r="AA27">
-        <v>0.99805028151894915</v>
+        <v>0.99605704806429607</v>
       </c>
       <c r="AB27">
-        <v>35.744838819266263</v>
+        <v>72.28745215457208</v>
       </c>
       <c r="AD27" t="s">
         <v>288</v>
@@ -9154,16 +9154,16 @@
         <v>431</v>
       </c>
       <c r="AM27" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="AN27" t="s">
-        <v>454</v>
+        <v>372</v>
       </c>
       <c r="AO27">
-        <v>0.99582871194680656</v>
+        <v>0.99671794291781168</v>
       </c>
       <c r="AP27">
-        <v>76.473614308545862</v>
+        <v>60.171046506785672</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -9228,16 +9228,16 @@
         <v>325</v>
       </c>
       <c r="Y28" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="Z28" t="s">
         <v>382</v>
       </c>
       <c r="AA28">
-        <v>0.98395338050941106</v>
+        <v>0.99167914755584141</v>
       </c>
       <c r="AB28">
-        <v>294.18802399413073</v>
+        <v>152.54896147624135</v>
       </c>
       <c r="AD28" t="s">
         <v>288</v>
@@ -9264,16 +9264,16 @@
         <v>433</v>
       </c>
       <c r="AM28" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AN28" t="s">
-        <v>481</v>
+        <v>372</v>
       </c>
       <c r="AO28">
-        <v>0.99555964959117016</v>
+        <v>0.99537626424805781</v>
       </c>
       <c r="AP28">
-        <v>81.406424161880452</v>
+        <v>84.768488785605911</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9338,16 +9338,16 @@
         <v>327</v>
       </c>
       <c r="Y29" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="Z29" t="s">
         <v>383</v>
       </c>
       <c r="AA29">
-        <v>0.99605704806429607</v>
+        <v>0.99744993905722468</v>
       </c>
       <c r="AB29">
-        <v>72.28745215457208</v>
+        <v>46.751117284213812</v>
       </c>
       <c r="AD29" t="s">
         <v>288</v>
@@ -9374,16 +9374,16 @@
         <v>435</v>
       </c>
       <c r="AM29" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AN29" t="s">
-        <v>483</v>
+        <v>463</v>
       </c>
       <c r="AO29">
-        <v>0.99740664776461363</v>
+        <v>0.9933445384762607</v>
       </c>
       <c r="AP29">
-        <v>47.544790982083583</v>
+        <v>122.01679460188713</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9448,16 +9448,16 @@
         <v>329</v>
       </c>
       <c r="Y30" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="Z30" t="s">
         <v>384</v>
       </c>
       <c r="AA30">
-        <v>0.99167914755584141</v>
+        <v>0.996629171401053</v>
       </c>
       <c r="AB30">
-        <v>152.54896147624135</v>
+        <v>61.798524314027716</v>
       </c>
       <c r="AD30" t="s">
         <v>288</v>
@@ -9490,10 +9490,10 @@
         <v>485</v>
       </c>
       <c r="AO30">
-        <v>0.9913636988912532</v>
+        <v>0.9938298282896767</v>
       </c>
       <c r="AP30">
-        <v>158.33218699369189</v>
+        <v>113.11981468926018</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -9558,16 +9558,16 @@
         <v>331</v>
       </c>
       <c r="Y31" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="Z31" t="s">
         <v>385</v>
       </c>
       <c r="AA31">
-        <v>0.99732710525923551</v>
+        <v>0.9940266623681554</v>
       </c>
       <c r="AB31">
-        <v>49.003070247349498</v>
+        <v>109.51118991715018</v>
       </c>
       <c r="AD31" t="s">
         <v>288</v>
@@ -9597,13 +9597,13 @@
         <v>486</v>
       </c>
       <c r="AN31" t="s">
-        <v>487</v>
+        <v>376</v>
       </c>
       <c r="AO31">
-        <v>0.99178855761800622</v>
+        <v>0.99008544123370779</v>
       </c>
       <c r="AP31">
-        <v>150.54311033655213</v>
+        <v>181.76691071535706</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -9668,16 +9668,16 @@
         <v>333</v>
       </c>
       <c r="Y32" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="Z32" t="s">
         <v>386</v>
       </c>
       <c r="AA32">
-        <v>0.99601914721828588</v>
+        <v>0.99629635001073991</v>
       </c>
       <c r="AB32">
-        <v>72.982300998092228</v>
+        <v>67.900249803101318</v>
       </c>
       <c r="AD32" t="s">
         <v>288</v>
@@ -9704,16 +9704,16 @@
         <v>441</v>
       </c>
       <c r="AM32" t="s">
+        <v>487</v>
+      </c>
+      <c r="AN32" t="s">
         <v>488</v>
       </c>
-      <c r="AN32" t="s">
-        <v>489</v>
-      </c>
       <c r="AO32">
-        <v>0.99296304108660982</v>
+        <v>0.99429686126958916</v>
       </c>
       <c r="AP32">
-        <v>129.01091341215286</v>
+        <v>104.55754339086491</v>
       </c>
     </row>
     <row r="33" spans="2:42">
@@ -9778,16 +9778,16 @@
         <v>335</v>
       </c>
       <c r="Y33" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="Z33" t="s">
         <v>387</v>
       </c>
       <c r="AA33">
-        <v>0.99403967905190227</v>
+        <v>0.99383936956194807</v>
       </c>
       <c r="AB33">
-        <v>109.27255071512499</v>
+        <v>112.94489136428538</v>
       </c>
       <c r="AD33" t="s">
         <v>288</v>
@@ -9814,16 +9814,16 @@
         <v>443</v>
       </c>
       <c r="AM33" t="s">
+        <v>489</v>
+      </c>
+      <c r="AN33" t="s">
         <v>490</v>
       </c>
-      <c r="AN33" t="s">
-        <v>491</v>
-      </c>
       <c r="AO33">
-        <v>0.99152317643653909</v>
+        <v>0.99178855761800622</v>
       </c>
       <c r="AP33">
-        <v>155.40843199678267</v>
+        <v>150.54311033655213</v>
       </c>
     </row>
     <row r="34" spans="2:42">
@@ -9888,16 +9888,16 @@
         <v>337</v>
       </c>
       <c r="Y34" t="s">
-        <v>285</v>
+        <v>265</v>
       </c>
       <c r="Z34" t="s">
-        <v>388</v>
+        <v>372</v>
       </c>
       <c r="AA34">
-        <v>0.99514004796050048</v>
+        <v>0.98416398409272543</v>
       </c>
       <c r="AB34">
-        <v>89.099120724157018</v>
+        <v>290.32695830003399</v>
       </c>
       <c r="AD34" t="s">
         <v>288</v>
@@ -9924,16 +9924,16 @@
         <v>445</v>
       </c>
       <c r="AM34" t="s">
+        <v>491</v>
+      </c>
+      <c r="AN34" t="s">
         <v>492</v>
       </c>
-      <c r="AN34" t="s">
-        <v>493</v>
-      </c>
       <c r="AO34">
-        <v>0.99475386493829931</v>
+        <v>0.99296304108660982</v>
       </c>
       <c r="AP34">
-        <v>96.179142797845941</v>
+        <v>129.01091341215286</v>
       </c>
     </row>
     <row r="35" spans="2:42">
@@ -9998,16 +9998,16 @@
         <v>339</v>
       </c>
       <c r="Y35" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="Z35" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="AA35">
-        <v>0.99589467345586935</v>
+        <v>0.99832768028365393</v>
       </c>
       <c r="AB35">
-        <v>75.264319975727958</v>
+        <v>30.659194799678048</v>
       </c>
       <c r="AD35" t="s">
         <v>288</v>
@@ -10034,16 +10034,16 @@
         <v>447</v>
       </c>
       <c r="AM35" t="s">
+        <v>493</v>
+      </c>
+      <c r="AN35" t="s">
         <v>494</v>
       </c>
-      <c r="AN35" t="s">
-        <v>495</v>
-      </c>
       <c r="AO35">
-        <v>0.99562035686170025</v>
+        <v>0.99152317643653909</v>
       </c>
       <c r="AP35">
-        <v>80.293457535494625</v>
+        <v>155.40843199678267</v>
       </c>
     </row>
     <row r="36" spans="2:42">
@@ -10108,16 +10108,16 @@
         <v>341</v>
       </c>
       <c r="Y36" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="Z36" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="AA36">
-        <v>0.993124380119488</v>
+        <v>0.99057172008573791</v>
       </c>
       <c r="AB36">
-        <v>126.05303114271953</v>
+        <v>172.85179842813815</v>
       </c>
       <c r="AD36" t="s">
         <v>288</v>
@@ -10144,16 +10144,16 @@
         <v>449</v>
       </c>
       <c r="AM36" t="s">
+        <v>495</v>
+      </c>
+      <c r="AN36" t="s">
         <v>496</v>
       </c>
-      <c r="AN36" t="s">
-        <v>377</v>
-      </c>
       <c r="AO36">
-        <v>0.99671794291781168</v>
+        <v>0.99475386493829931</v>
       </c>
       <c r="AP36">
-        <v>60.171046506785672</v>
+        <v>96.179142797845941</v>
       </c>
     </row>
     <row r="37" spans="2:42">
@@ -10218,16 +10218,16 @@
         <v>343</v>
       </c>
       <c r="Y37" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="Z37" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AA37">
-        <v>0.99769438809486533</v>
+        <v>0.99095032933880767</v>
       </c>
       <c r="AB37">
-        <v>42.269551594135834</v>
+        <v>165.91062878852651</v>
       </c>
       <c r="AD37" t="s">
         <v>288</v>
@@ -10260,10 +10260,10 @@
         <v>498</v>
       </c>
       <c r="AO37">
-        <v>0.98839759805196303</v>
+        <v>0.99562035686170025</v>
       </c>
       <c r="AP37">
-        <v>212.71070238067816</v>
+        <v>80.293457535494625</v>
       </c>
     </row>
     <row r="38" spans="2:42">
@@ -10328,16 +10328,16 @@
         <v>345</v>
       </c>
       <c r="Y38" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="Z38" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AA38">
-        <v>0.99489048613238573</v>
+        <v>0.993124380119488</v>
       </c>
       <c r="AB38">
-        <v>93.674420906261602</v>
+        <v>126.05303114271953</v>
       </c>
     </row>
     <row r="39" spans="2:42">
@@ -10402,16 +10402,16 @@
         <v>347</v>
       </c>
       <c r="Y39" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="Z39" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AA39">
-        <v>0.99642867204968677</v>
+        <v>0.99769438809486533</v>
       </c>
       <c r="AB39">
-        <v>65.474345755743457</v>
+        <v>42.269551594135834</v>
       </c>
     </row>
     <row r="40" spans="2:42">
@@ -10476,16 +10476,16 @@
         <v>349</v>
       </c>
       <c r="Y40" t="s">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="Z40" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AA40">
-        <v>0.99802162515875081</v>
+        <v>0.99489048613238573</v>
       </c>
       <c r="AB40">
-        <v>36.270205422902137</v>
+        <v>93.674420906261602</v>
       </c>
     </row>
     <row r="41" spans="2:42">
@@ -10550,16 +10550,16 @@
         <v>351</v>
       </c>
       <c r="Y41" t="s">
-        <v>253</v>
+        <v>283</v>
       </c>
       <c r="Z41" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AA41">
-        <v>0.99631349511992195</v>
+        <v>0.99642867204968677</v>
       </c>
       <c r="AB41">
-        <v>67.585922801431252</v>
+        <v>65.474345755743457</v>
       </c>
     </row>
     <row r="42" spans="2:42">
@@ -10624,16 +10624,16 @@
         <v>353</v>
       </c>
       <c r="Y42" t="s">
-        <v>280</v>
+        <v>252</v>
       </c>
       <c r="Z42" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AA42">
-        <v>0.99133276722560904</v>
+        <v>0.99723470592138874</v>
       </c>
       <c r="AB42">
-        <v>158.89926753050145</v>
+        <v>50.697058107873339</v>
       </c>
     </row>
     <row r="43" spans="2:42">
@@ -10698,16 +10698,16 @@
         <v>355</v>
       </c>
       <c r="Y43" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="Z43" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AA43">
-        <v>0.99728758220200375</v>
+        <v>0.99750455285561002</v>
       </c>
       <c r="AB43">
-        <v>49.727659629930621</v>
+        <v>45.749864313816033</v>
       </c>
     </row>
     <row r="44" spans="2:42">
@@ -10772,16 +10772,16 @@
         <v>357</v>
       </c>
       <c r="Y44" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="Z44" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AA44">
-        <v>0.99832768028365393</v>
+        <v>0.99732710525923551</v>
       </c>
       <c r="AB44">
-        <v>30.659194799678048</v>
+        <v>49.003070247349498</v>
       </c>
     </row>
     <row r="45" spans="2:42">
@@ -10846,16 +10846,16 @@
         <v>359</v>
       </c>
       <c r="Y45" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="Z45" t="s">
-        <v>382</v>
+        <v>397</v>
       </c>
       <c r="AA45">
-        <v>0.99057172008573791</v>
+        <v>0.99601914721828588</v>
       </c>
       <c r="AB45">
-        <v>172.85179842813815</v>
+        <v>72.982300998092228</v>
       </c>
     </row>
     <row r="46" spans="2:42">
@@ -10920,16 +10920,16 @@
         <v>361</v>
       </c>
       <c r="Y46" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="Z46" t="s">
         <v>398</v>
       </c>
       <c r="AA46">
-        <v>0.99095032933880767</v>
+        <v>0.99403967905190227</v>
       </c>
       <c r="AB46">
-        <v>165.91062878852651</v>
+        <v>109.27255071512499</v>
       </c>
     </row>
   </sheetData>
@@ -10938,7 +10938,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22BBEE40-A54E-4F80-8FB1-43E28AD293D6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9D8FA56-4D35-4C30-B47A-E61A7AEB3C9E}">
   <dimension ref="B9:Z37"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -11050,7 +11050,7 @@
         <v>536</v>
       </c>
       <c r="K11" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="L11">
         <v>10.088237612202811</v>
@@ -11083,7 +11083,7 @@
         <v>590</v>
       </c>
       <c r="X11" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="Y11">
         <v>0.16350000000000001</v>
@@ -11118,7 +11118,7 @@
         <v>538</v>
       </c>
       <c r="K12" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="L12">
         <v>4.7527038630847755</v>
@@ -11151,7 +11151,7 @@
         <v>592</v>
       </c>
       <c r="X12" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="Y12">
         <v>13.40025</v>
@@ -11186,7 +11186,7 @@
         <v>540</v>
       </c>
       <c r="K13" t="s">
-        <v>496</v>
+        <v>481</v>
       </c>
       <c r="L13">
         <v>1.4400913107240583</v>
@@ -11219,7 +11219,7 @@
         <v>594</v>
       </c>
       <c r="X13" t="s">
-        <v>531</v>
+        <v>519</v>
       </c>
       <c r="Y13">
         <v>8.4097500000000007</v>
@@ -11254,7 +11254,7 @@
         <v>542</v>
       </c>
       <c r="K14" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="L14">
         <v>1.437273477445641</v>
@@ -11287,7 +11287,7 @@
         <v>596</v>
       </c>
       <c r="X14" t="s">
-        <v>521</v>
+        <v>532</v>
       </c>
       <c r="Y14">
         <v>14.358750000000001</v>
@@ -11322,7 +11322,7 @@
         <v>544</v>
       </c>
       <c r="K15" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="L15">
         <v>2.1922713563210485</v>
@@ -11355,7 +11355,7 @@
         <v>598</v>
       </c>
       <c r="X15" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="Y15">
         <v>12.78825</v>
@@ -11390,7 +11390,7 @@
         <v>546</v>
       </c>
       <c r="K16" t="s">
-        <v>465</v>
+        <v>487</v>
       </c>
       <c r="L16">
         <v>0.73811583011208182</v>
@@ -11423,7 +11423,7 @@
         <v>600</v>
       </c>
       <c r="X16" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="Y16">
         <v>24.802499999999998</v>
@@ -11458,7 +11458,7 @@
         <v>548</v>
       </c>
       <c r="K17" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="L17">
         <v>5.5236145427785717</v>
@@ -11491,7 +11491,7 @@
         <v>602</v>
       </c>
       <c r="X17" t="s">
-        <v>523</v>
+        <v>534</v>
       </c>
       <c r="Y17">
         <v>8.6609999999999996</v>
@@ -11526,7 +11526,7 @@
         <v>550</v>
       </c>
       <c r="K18" t="s">
-        <v>477</v>
+        <v>460</v>
       </c>
       <c r="L18">
         <v>5.5488357050452785E-3</v>
@@ -11559,7 +11559,7 @@
         <v>604</v>
       </c>
       <c r="X18" t="s">
-        <v>534</v>
+        <v>523</v>
       </c>
       <c r="Y18">
         <v>3.4147500000000002</v>
@@ -11594,7 +11594,7 @@
         <v>552</v>
       </c>
       <c r="K19" t="s">
-        <v>469</v>
+        <v>453</v>
       </c>
       <c r="L19">
         <v>6.6811161360847313</v>
@@ -11627,7 +11627,7 @@
         <v>606</v>
       </c>
       <c r="X19" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="Y19">
         <v>1.7250000000000001E-2</v>
@@ -11662,7 +11662,7 @@
         <v>554</v>
       </c>
       <c r="K20" t="s">
-        <v>455</v>
+        <v>484</v>
       </c>
       <c r="L20">
         <v>18.094012332227912</v>
@@ -11695,7 +11695,7 @@
         <v>608</v>
       </c>
       <c r="X20" t="s">
-        <v>535</v>
+        <v>521</v>
       </c>
       <c r="Y20">
         <v>6.8624999999999998</v>
@@ -11730,7 +11730,7 @@
         <v>556</v>
       </c>
       <c r="K21" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="L21">
         <v>1.3529085560597105</v>
@@ -11765,7 +11765,7 @@
         <v>558</v>
       </c>
       <c r="K22" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="L22">
         <v>3.7088360788644938</v>
@@ -11800,7 +11800,7 @@
         <v>560</v>
       </c>
       <c r="K23" t="s">
-        <v>458</v>
+        <v>468</v>
       </c>
       <c r="L23">
         <v>13.683903390107789</v>
@@ -11835,7 +11835,7 @@
         <v>562</v>
       </c>
       <c r="K24" t="s">
-        <v>479</v>
+        <v>462</v>
       </c>
       <c r="L24">
         <v>5.4676081362262012</v>
@@ -11870,7 +11870,7 @@
         <v>564</v>
       </c>
       <c r="K25" t="s">
-        <v>453</v>
+        <v>483</v>
       </c>
       <c r="L25">
         <v>8.9064794695455216</v>
@@ -11905,7 +11905,7 @@
         <v>566</v>
       </c>
       <c r="K26" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
       <c r="L26">
         <v>14.189229081738485</v>
@@ -11940,7 +11940,7 @@
         <v>568</v>
       </c>
       <c r="K27" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="L27">
         <v>10.717982842540293</v>
@@ -11975,7 +11975,7 @@
         <v>570</v>
       </c>
       <c r="K28" t="s">
-        <v>497</v>
+        <v>475</v>
       </c>
       <c r="L28">
         <v>9.6743476082482847</v>
@@ -12010,7 +12010,7 @@
         <v>572</v>
       </c>
       <c r="K29" t="s">
-        <v>457</v>
+        <v>486</v>
       </c>
       <c r="L29">
         <v>23.206762484053751</v>
@@ -12045,7 +12045,7 @@
         <v>574</v>
       </c>
       <c r="K30" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="L30">
         <v>5.8372174437039801</v>
@@ -12080,7 +12080,7 @@
         <v>576</v>
       </c>
       <c r="K31" t="s">
-        <v>480</v>
+        <v>464</v>
       </c>
       <c r="L31">
         <v>1.8845590125315521</v>
@@ -12115,7 +12115,7 @@
         <v>578</v>
       </c>
       <c r="K32" t="s">
-        <v>471</v>
+        <v>455</v>
       </c>
       <c r="L32">
         <v>7.179650801796102</v>
@@ -12150,7 +12150,7 @@
         <v>580</v>
       </c>
       <c r="K33" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="L33">
         <v>14.559476964149322</v>
@@ -12185,7 +12185,7 @@
         <v>582</v>
       </c>
       <c r="K34" t="s">
-        <v>462</v>
+        <v>472</v>
       </c>
       <c r="L34">
         <v>1.3536151515148049</v>
@@ -12220,7 +12220,7 @@
         <v>584</v>
       </c>
       <c r="K35" t="s">
-        <v>460</v>
+        <v>470</v>
       </c>
       <c r="L35">
         <v>4.820514286595051</v>
@@ -12255,7 +12255,7 @@
         <v>586</v>
       </c>
       <c r="K36" t="s">
-        <v>474</v>
+        <v>458</v>
       </c>
       <c r="L36">
         <v>8.1474073379531564</v>
@@ -12290,7 +12290,7 @@
         <v>588</v>
       </c>
       <c r="K37" t="s">
-        <v>472</v>
+        <v>456</v>
       </c>
       <c r="L37">
         <v>9.9689850956014183</v>
@@ -12305,7 +12305,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0839A53-BD0B-4711-BB02-F579271C53FD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A3E657C-2307-4226-88B5-D6276A35E9B4}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
